--- a/tame_output/ON/bt/strategyON_20240902.xlsx
+++ b/tame_output/ON/bt/strategyON_20240902.xlsx
@@ -48626,7 +48626,7 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760313</v>
+        <v>3.646857607760312</v>
       </c>
       <c r="C2047" t="n">
         <v>3.775332178009633</v>
@@ -49253,16 +49253,16 @@
         <v>4.182816723047583</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.270986412938649</v>
+        <v>-5.270954236006471</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.074065733558375</v>
+        <v>2.074078604331247</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.5945671748906174</v>
+        <v>0.5946188402262161</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.539557027981953</v>
+        <v>4.539588027183313</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240902.xlsx
+++ b/tame_output/ON/bt/strategyON_20240902.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.6%</t>
+          <t>-79.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-688.7%</t>
+          <t>-690.5%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.1%</t>
+          <t>-32.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-168.8%</t>
+          <t>-169.6%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-13.3%</t>
+          <t>-13.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-6.9%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>589.8%</t>
+          <t>590.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-164.5%</t>
+          <t>-167.0%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>90.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-20.7%</t>
+          <t>-20.8%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>81.6%</t>
+          <t>81.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>7.9%</t>
+          <t>6.5%</t>
         </is>
       </c>
     </row>
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.699015115152822</v>
+        <v>3.699015115152823</v>
       </c>
       <c r="C2074" t="n">
         <v>4.182816723047583</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.270954236006471</v>
+        <v>-5.28938210192938</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.074078604331247</v>
+        <v>2.066707457962083</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.5946188402262161</v>
+        <v>0.570342794430586</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.539588027183313</v>
+        <v>4.525022399705934</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240902.xlsx
+++ b/tame_output/ON/bt/strategyON_20240902.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.2%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>34.7%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>76.5%</t>
+          <t>76.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.7%</t>
+          <t>-79.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.6%</t>
+          <t>108.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.4%</t>
+          <t>91.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-46.5%</t>
+          <t>-50.9%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.6%</t>
+          <t>-49.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.2%</t>
+          <t>-76.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>89.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.1%</t>
+          <t>421.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-690.5%</t>
+          <t>-696.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>50.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.2%</t>
+          <t>-32.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-169.6%</t>
+          <t>-171.9%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-13.6%</t>
+          <t>-13.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-7.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>590.2%</t>
+          <t>588.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-167.0%</t>
+          <t>-164.7%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>90.1%</t>
+          <t>90.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-20.8%</t>
+          <t>-20.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>81.1%</t>
+          <t>81.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>7.8%</t>
         </is>
       </c>
     </row>
@@ -48626,7 +48626,7 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760312</v>
+        <v>3.646857607760313</v>
       </c>
       <c r="C2047" t="n">
         <v>3.775332178009633</v>
@@ -49069,10 +49069,10 @@
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.212310757061613</v>
+        <v>-5.285466811946408</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.01794028742735</v>
+        <v>1.988677865473432</v>
       </c>
       <c r="F2066" t="n">
         <v>0.6361203177205446</v>
@@ -49092,10 +49092,10 @@
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.029099093928518</v>
+        <v>-5.102255148813313</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.093655902144634</v>
+        <v>2.064393480190716</v>
       </c>
       <c r="F2067" t="n">
         <v>0.6361203177205446</v>
@@ -49115,10 +49115,10 @@
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.957377646914667</v>
+        <v>-5.030533701799462</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.088135666798064</v>
+        <v>2.058873244844146</v>
       </c>
       <c r="F2068" t="n">
         <v>0.7078417647343952</v>
@@ -49138,10 +49138,10 @@
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.086756429554445</v>
+        <v>-5.15991248443924</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.983299899663324</v>
+        <v>1.954037477709406</v>
       </c>
       <c r="F2069" t="n">
         <v>0.6657399920271918</v>
@@ -49161,10 +49161,10 @@
         <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.119772725465189</v>
+        <v>-5.192928780349985</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.155291586184382</v>
+        <v>2.126029164230464</v>
       </c>
       <c r="F2070" t="n">
         <v>0.5963026153604403</v>
@@ -49184,10 +49184,10 @@
         <v>4.195478326512454</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.108245089815581</v>
+        <v>-5.181401144700376</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.151823866272474</v>
+        <v>2.122561444318556</v>
       </c>
       <c r="F2071" t="n">
         <v>0.6553032735618027</v>
@@ -49207,10 +49207,10 @@
         <v>4.199146439034243</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.20558659115795</v>
+        <v>-5.278742646042745</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.116555378257316</v>
+        <v>2.087292956303398</v>
       </c>
       <c r="F2072" t="n">
         <v>0.6108830913963144</v>
@@ -49230,10 +49230,10 @@
         <v>4.200397521227081</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.291442620497916</v>
+        <v>-5.364598675382712</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.083464048714167</v>
+        <v>2.054201626760249</v>
       </c>
       <c r="F2073" t="n">
         <v>0.5685070221701793</v>
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.699015115152823</v>
+        <v>3.628237910300335</v>
       </c>
       <c r="C2074" t="n">
         <v>4.182816723047583</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.28938210192938</v>
+        <v>-5.34778975098344</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.066707457962083</v>
+        <v>2.043344398340459</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.570342794430586</v>
+        <v>0.5925731178585595</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.525022399705934</v>
+        <v>4.538360593762718</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240902.xlsx
+++ b/tame_output/ON/bt/strategyON_20240902.xlsx
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2071</v>
+        <v>2072</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>92.6%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2071</v>
+        <v>2072</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-9.4%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-6.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>76.8%</t>
+          <t>74.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>106.7%</t>
+          <t>98.4%</t>
         </is>
       </c>
     </row>
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2071</v>
+        <v>2072</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.7%</t>
+          <t>124.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2071</v>
+        <v>2072</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2071</v>
+        <v>2072</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>588.7%</t>
+          <t>588.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>90.5%</t>
+          <t>71.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2071</v>
+        <v>2072</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1456,12 +1456,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-7.7%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-20.7%</t>
+          <t>-24.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>-14.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>-36.7%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2074"/>
+  <dimension ref="A1:G2075"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49247,7 +49247,7 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.628237910300335</v>
+        <v>3.691855684893107</v>
       </c>
       <c r="C2074" t="n">
         <v>4.182816723047583</v>
@@ -49263,6 +49263,29 @@
       </c>
       <c r="G2074" t="n">
         <v>4.538360593762718</v>
+      </c>
+    </row>
+    <row r="2075">
+      <c r="A2075" s="2" t="n">
+        <v>45537</v>
+      </c>
+      <c r="B2075" t="n">
+        <v>3.627376103306048</v>
+      </c>
+      <c r="C2075" t="n">
+        <v>4.100568731184579</v>
+      </c>
+      <c r="D2075" t="n">
+        <v>-5.34778975098344</v>
+      </c>
+      <c r="E2075" t="n">
+        <v>2.043344398340459</v>
+      </c>
+      <c r="F2075" t="n">
+        <v>0.5925731178585595</v>
+      </c>
+      <c r="G2075" t="n">
+        <v>4.093632528170946</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240902.xlsx
+++ b/tame_output/ON/bt/strategyON_20240902.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>51.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>30.5%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>89.7%</t>
+          <t>91.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.1%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-9.4%</t>
+          <t>-7.7%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.5%</t>
+          <t>-6.1%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>74.0%</t>
+          <t>76.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-7.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>98.4%</t>
+          <t>103.9%</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.4%</t>
+          <t>108.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.6%</t>
+          <t>124.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.0%</t>
+          <t>91.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-50.9%</t>
+          <t>-49.6%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.9%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>421.3%</t>
+          <t>420.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-696.4%</t>
+          <t>-694.2%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-171.9%</t>
+          <t>-172.7%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-7.0%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>588.6%</t>
+          <t>587.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>71.7%</t>
+          <t>74.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-24.4%</t>
+          <t>-23.8%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.8%</t>
+          <t>-15.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-36.7%</t>
+          <t>-31.2%</t>
         </is>
       </c>
     </row>
@@ -48626,7 +48626,7 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760313</v>
+        <v>3.645256780013423</v>
       </c>
       <c r="C2047" t="n">
         <v>3.775332178009633</v>
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781702</v>
+        <v>3.666747201498968</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.775332178009633</v>
+        <v>3.758938414076515</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.756016533120698</v>
+        <v>-4.807829082898062</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.872569140447607</v>
+        <v>1.835450356603543</v>
       </c>
       <c r="F2048" t="n">
         <v>0.9425251867244809</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.340847290044322</v>
+        <v>4.324453526111204</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082831</v>
+        <v>3.670048702800097</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.7355840916031</v>
+        <v>3.719190327669982</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.931123365697143</v>
+        <v>-4.982935915474506</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.762778321010495</v>
+        <v>1.725659537166432</v>
       </c>
       <c r="F2049" t="n">
         <v>0.9425251867244809</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.301099203637789</v>
+        <v>4.284705439704671</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943583</v>
+        <v>3.745573148660848</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.74260671060004</v>
+        <v>3.726212946666922</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.899837345156688</v>
+        <v>-4.951649894934051</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.782315348223618</v>
+        <v>1.745196564379554</v>
       </c>
       <c r="F2050" t="n">
         <v>0.9738112072649363</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.326893434959002</v>
+        <v>4.310499671025884</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.73059065867782</v>
+        <v>3.730570473395086</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.841777710172944</v>
+        <v>3.825383946239826</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.746811953043403</v>
+        <v>-4.798624502820767</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.942696504641836</v>
+        <v>1.905577720797773</v>
       </c>
       <c r="F2051" t="n">
         <v>1.12683659937822</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.517879669799877</v>
+        <v>4.501485905866759</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073879</v>
+        <v>3.741278332791145</v>
       </c>
       <c r="C2052" t="n">
-        <v>4.029243935081237</v>
+        <v>4.012850171148119</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.775119266916674</v>
+        <v>-4.826931816694037</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.11883980400082</v>
+        <v>2.081721020156757</v>
       </c>
       <c r="F2052" t="n">
         <v>1.12683659937822</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.705345894708169</v>
+        <v>4.688952130775052</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903164</v>
+        <v>3.69911561562043</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.998646886435319</v>
+        <v>3.982253122502201</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.941712492030196</v>
+        <v>-4.993525041807559</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.021605465309493</v>
+        <v>1.98448668146543</v>
       </c>
       <c r="F2053" t="n">
         <v>0.9602433742646979</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.574792910994137</v>
+        <v>4.55839914706102</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568379</v>
+        <v>3.708182519285645</v>
       </c>
       <c r="C2054" t="n">
-        <v>4.002323289097037</v>
+        <v>3.985929525163919</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.768648112647896</v>
+        <v>-4.820460662425259</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.094507619724131</v>
+        <v>2.057388835880068</v>
       </c>
       <c r="F2054" t="n">
         <v>0.9602433742646979</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.578469313655855</v>
+        <v>4.562075549722738</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.7406015866822</v>
+        <v>3.740581401399466</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.999941344220532</v>
+        <v>3.983547580287414</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.7394021321922</v>
+        <v>-4.791214681969563</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.103824067029905</v>
+        <v>2.066705283185842</v>
       </c>
       <c r="F2055" t="n">
         <v>0.9602433742646979</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.57608736877935</v>
+        <v>4.559693604846233</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539104</v>
+        <v>3.699404642256369</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.997234583378167</v>
+        <v>3.980840819445049</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.846327680070051</v>
+        <v>-4.898140229847414</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.058347087036399</v>
+        <v>2.021228303192337</v>
       </c>
       <c r="F2056" t="n">
         <v>0.8533178263868465</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.509225279210275</v>
+        <v>4.492831515277158</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983734</v>
+        <v>3.689942600700999</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.998663385521401</v>
+        <v>3.982269621588284</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.991346238577299</v>
+        <v>-5.043158788354662</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.001768465776734</v>
+        <v>1.964649681932671</v>
       </c>
       <c r="F2057" t="n">
         <v>0.708299267879598</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.42364294624916</v>
+        <v>4.407249182316042</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969745</v>
+        <v>3.711852429687011</v>
       </c>
       <c r="C2058" t="n">
-        <v>4.098594624779154</v>
+        <v>4.082200860846037</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.109688004362017</v>
+        <v>-5.16150055413938</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.0543629987206</v>
+        <v>2.017244214876537</v>
       </c>
       <c r="F2058" t="n">
         <v>0.718985306442488</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.529985808644647</v>
+        <v>4.51359204471153</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073535</v>
+        <v>3.714879051790801</v>
       </c>
       <c r="C2059" t="n">
-        <v>4.096380321905093</v>
+        <v>4.079986557971975</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.161098426682725</v>
+        <v>-5.212910976460088</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.031584526918256</v>
+        <v>1.994465743074193</v>
       </c>
       <c r="F2059" t="n">
         <v>0.718985306442488</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.527771505770586</v>
+        <v>4.511377741837468</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720063</v>
+        <v>3.704757949437329</v>
       </c>
       <c r="C2060" t="n">
-        <v>4.096283449979382</v>
+        <v>4.079889686046265</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.240517877890476</v>
+        <v>-5.29233042766784</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.999719874509445</v>
+        <v>1.962601090665382</v>
       </c>
       <c r="F2060" t="n">
         <v>0.718985306442488</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.527674633844875</v>
+        <v>4.511280869911758</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.73682513758113</v>
+        <v>3.736804952298396</v>
       </c>
       <c r="C2061" t="n">
-        <v>4.096277343537426</v>
+        <v>4.079883579604308</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.335980875807694</v>
+        <v>-5.387793425585057</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.961528568900601</v>
+        <v>1.924409785056538</v>
       </c>
       <c r="F2061" t="n">
         <v>0.718985306442488</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.527668527402919</v>
+        <v>4.511274763469801</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715393145500732</v>
+        <v>3.715372960217998</v>
       </c>
       <c r="C2062" t="n">
-        <v>4.094373740100036</v>
+        <v>4.077979976166919</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.376000873851478</v>
+        <v>-5.427813423628841</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.943616966245698</v>
+        <v>1.906498182401635</v>
       </c>
       <c r="F2062" t="n">
         <v>0.6789653083987042</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.501752925139259</v>
+        <v>4.485359161206142</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736109598636268</v>
+        <v>3.736089413353533</v>
       </c>
       <c r="C2063" t="n">
-        <v>4.100107557847763</v>
+        <v>4.083713793914646</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.431370035983671</v>
+        <v>-5.483182585761035</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.927203119140547</v>
+        <v>1.890084335296484</v>
       </c>
       <c r="F2063" t="n">
         <v>0.6789653083987042</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.507486742886986</v>
+        <v>4.491092978953868</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736843055396011</v>
+        <v>3.736822870113277</v>
       </c>
       <c r="C2064" t="n">
-        <v>4.099645921190696</v>
+        <v>4.083252157257578</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.476807815814499</v>
+        <v>-5.528620365591862</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.908566370551149</v>
+        <v>1.871447586707085</v>
       </c>
       <c r="F2064" t="n">
         <v>0.6361203177205446</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.481318111823023</v>
+        <v>4.464924347889904</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.79029268539642</v>
+        <v>3.790272500113685</v>
       </c>
       <c r="C2065" t="n">
-        <v>4.119520314041015</v>
+        <v>4.103126550107897</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.38860098166692</v>
+        <v>-5.440413531444284</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.9637234970605</v>
+        <v>1.926604713216436</v>
       </c>
       <c r="F2065" t="n">
         <v>0.6361203177205446</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.501192504673342</v>
+        <v>4.484798740740223</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794507029299173</v>
+        <v>3.794486844016439</v>
       </c>
       <c r="C2066" t="n">
-        <v>4.103221014565743</v>
+        <v>4.086827250632624</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.285466811946408</v>
+        <v>-5.264123306838976</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.988677865473432</v>
+        <v>1.980821503583287</v>
       </c>
       <c r="F2066" t="n">
         <v>0.6361203177205446</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.48489320519807</v>
+        <v>4.468499441264951</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794725278590404</v>
+        <v>3.79470509330767</v>
       </c>
       <c r="C2067" t="n">
-        <v>4.105651964029788</v>
+        <v>4.08925820009667</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.102255148813313</v>
+        <v>-5.080911643705881</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.064393480190716</v>
+        <v>2.05653711830057</v>
       </c>
       <c r="F2067" t="n">
         <v>0.6361203177205446</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.487324154662115</v>
+        <v>4.470930390728997</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776866743146282</v>
+        <v>3.776846557863548</v>
       </c>
       <c r="C2068" t="n">
-        <v>4.071443149877678</v>
+        <v>4.055049385944559</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.030533701799462</v>
+        <v>-5.00919019669203</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.058873244844146</v>
+        <v>2.051016882954</v>
       </c>
       <c r="F2068" t="n">
         <v>0.7078417647343952</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.496148208718315</v>
+        <v>4.479754444785197</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723809890676845</v>
+        <v>3.723789705394111</v>
       </c>
       <c r="C2069" t="n">
-        <v>4.018358895798849</v>
+        <v>4.001965131865731</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.15991248443924</v>
+        <v>-5.138568979331808</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.954037477709406</v>
+        <v>1.946181115819261</v>
       </c>
       <c r="F2069" t="n">
         <v>0.6657399920271918</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.417802891015165</v>
+        <v>4.401409127082046</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715627631739462</v>
+        <v>3.715607446456728</v>
       </c>
       <c r="C2070" t="n">
-        <v>4.203557100684205</v>
+        <v>4.187163336751087</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.192928780349985</v>
+        <v>-5.171585275242553</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.126029164230464</v>
+        <v>2.118172802340318</v>
       </c>
       <c r="F2070" t="n">
         <v>0.5963026153604403</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.561338669900469</v>
+        <v>4.544944905967351</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713782722166409</v>
+        <v>3.713762536883674</v>
       </c>
       <c r="C2071" t="n">
-        <v>4.195478326512454</v>
+        <v>4.179084562579336</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.181401144700376</v>
+        <v>-5.160057639592944</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.122561444318556</v>
+        <v>2.114705082428411</v>
       </c>
       <c r="F2071" t="n">
         <v>0.6553032735618027</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.588660290649536</v>
+        <v>4.572266526716417</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717170884519029</v>
+        <v>3.717150699236295</v>
       </c>
       <c r="C2072" t="n">
-        <v>4.199146439034243</v>
+        <v>4.182752675101124</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.278742646042745</v>
+        <v>-5.257399140935313</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.087292956303398</v>
+        <v>2.079436594413252</v>
       </c>
       <c r="F2072" t="n">
         <v>0.6108830913963144</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.565676293872031</v>
+        <v>4.549282529938913</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705221264710415</v>
+        <v>3.705201079427681</v>
       </c>
       <c r="C2073" t="n">
-        <v>4.200397521227081</v>
+        <v>4.184003757293962</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.364598675382712</v>
+        <v>-5.343255170275279</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.054201626760249</v>
+        <v>2.046345264870103</v>
       </c>
       <c r="F2073" t="n">
         <v>0.5685070221701793</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.541501734529189</v>
+        <v>4.52510797059607</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691855684893107</v>
+        <v>3.68994055732922</v>
       </c>
       <c r="C2074" t="n">
-        <v>4.182816723047583</v>
+        <v>4.166422959114464</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.34778975098344</v>
+        <v>-5.326446245876008</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.043344398340459</v>
+        <v>2.035488036450313</v>
       </c>
       <c r="F2074" t="n">
         <v>0.5925731178585595</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.538360593762718</v>
+        <v>4.5219668298296</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.627376103306048</v>
+        <v>3.586030342184975</v>
       </c>
       <c r="C2075" t="n">
-        <v>4.100568731184579</v>
+        <v>4.155064803320291</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.34778975098344</v>
+        <v>-5.326446245876008</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.043344398340459</v>
+        <v>2.035488036450313</v>
       </c>
       <c r="F2075" t="n">
         <v>0.5925731178585595</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.093632528170946</v>
+        <v>4.148128600306659</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240902.xlsx
+++ b/tame_output/ON/bt/strategyON_20240902.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>51.8%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>91.6%</t>
+          <t>91.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -829,17 +829,17 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-6.3%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>76.1%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.2%</t>
+          <t>-7.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>103.9%</t>
+          <t>106.1%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.8%</t>
+          <t>-80.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.6%</t>
+          <t>108.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.7%</t>
+          <t>124.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.4%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-49.6%</t>
+          <t>-51.6%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>20.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.8%</t>
+          <t>-49.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>89.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>420.8%</t>
+          <t>422.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-694.2%</t>
+          <t>-701.1%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.4%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.1%</t>
+          <t>-32.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-12.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-172.7%</t>
+          <t>-185.9%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-13.3%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>72.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-6.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>587.9%</t>
+          <t>170.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-308.4%</t>
+          <t>-307.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-164.7%</t>
+          <t>-161.5%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>74.9%</t>
+          <t>77.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-23.8%</t>
+          <t>-22.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>70.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.0%</t>
+          <t>-16.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-31.2%</t>
+          <t>-29.0%</t>
         </is>
       </c>
     </row>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279812</v>
+        <v>3.385382209279813</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511403</v>
+        <v>3.367379938511404</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386092</v>
+        <v>3.376932391386093</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998559</v>
+        <v>3.36737053999856</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082123</v>
+        <v>3.299560092082124</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757921</v>
+        <v>3.293490533757922</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760739</v>
+        <v>3.29376671976074</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706667</v>
+        <v>3.298730590706668</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537425</v>
+        <v>3.271168579537424</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.27276013138219</v>
+        <v>3.272760131382189</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074621</v>
+        <v>3.25147557607462</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911637</v>
+        <v>3.233800325911636</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213493</v>
+        <v>3.223539378213492</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382325</v>
+        <v>3.235981977382324</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347051</v>
+        <v>3.29913614634705</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130013</v>
+        <v>3.287377576130012</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178239</v>
+        <v>3.315884374178238</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207809</v>
+        <v>3.305316798207808</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310978</v>
+        <v>3.284619513310977</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.31108639130942</v>
+        <v>3.311086391309419</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970901</v>
+        <v>3.3047157169709</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330519</v>
+        <v>3.300815818330518</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191733</v>
+        <v>3.302618194191732</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097816</v>
+        <v>3.341378723097815</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094111</v>
+        <v>3.37443904309411</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.40596051119928</v>
+        <v>3.405960511199279</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969588</v>
+        <v>3.424633354969587</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392308</v>
+        <v>3.419979433923079</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297743</v>
+        <v>3.458100091297742</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.44775050131761</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737165</v>
+        <v>3.503515506737164</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341308</v>
+        <v>3.503170282341307</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539459</v>
+        <v>3.501052558539458</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937497</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440633</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -45389,16 +45389,16 @@
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.797918741924919</v>
+        <v>-6.813770518289574</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.3404109394599812</v>
+        <v>0.3340702289141193</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.314373103356599</v>
+        <v>-0.3302248797212535</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.871310998529737</v>
+        <v>2.861799932710944</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.712954075195599</v>
+        <v>-6.728805851560255</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.3873031473753676</v>
+        <v>0.3809624368295057</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.2294084366272794</v>
+        <v>-0.2452602129919339</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.935196139790988</v>
+        <v>2.925685073972195</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.818544064968703</v>
+        <v>-6.834395841333359</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.2170912218669074</v>
+        <v>0.2107505113210451</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.3349984264003837</v>
+        <v>-0.3508502027650383</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.743866216327906</v>
+        <v>2.734355150509113</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.750309480343276</v>
+        <v>-6.766161256707932</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.2929293975941647</v>
+        <v>0.2865886870483023</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.3165831035278477</v>
+        <v>-0.3324348798925023</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.803459751928514</v>
+        <v>2.793948686109721</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.602369438935677</v>
+        <v>-6.618221215300332</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.2354846055187974</v>
+        <v>0.229143894972935</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.2962621876192902</v>
+        <v>-0.3121139639839447</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.699031492835242</v>
+        <v>2.689520427016449</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409203</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.549399916681688</v>
+        <v>-6.565251693046344</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.2479584281669145</v>
+        <v>0.2416177176210521</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.2432926653653013</v>
+        <v>-0.2591444417299558</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.722099219934157</v>
+        <v>2.712588154115364</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.383611720721397</v>
+        <v>-6.399463497086053</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.3073130944559379</v>
+        <v>0.3009723839100755</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.2432926653653013</v>
+        <v>-0.2591444417299558</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.715138607839064</v>
+        <v>2.705627542020271</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493418</v>
+        <v>3.782922533493419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.350248514242629</v>
+        <v>-6.366100290607284</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.3351207314285882</v>
+        <v>0.3287800208827258</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.2432926653653013</v>
+        <v>-0.2591444417299558</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.729600962220207</v>
+        <v>2.720089896401414</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.241989377120107</v>
+        <v>-6.257841153484763</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.3729565067367919</v>
+        <v>0.3666157961909295</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.2432926653653013</v>
+        <v>-0.2591444417299558</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.724133082679402</v>
+        <v>2.714622016860609</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.118698242302976</v>
+        <v>-6.134550018667632</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.419771054674221</v>
+        <v>0.4134303441283591</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.1200015305481708</v>
+        <v>-0.1358533069128253</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.795605857580257</v>
+        <v>2.786094791761464</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.066001375171685</v>
+        <v>-6.081853151536341</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.4485507797640631</v>
+        <v>0.4422100692182007</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.06730466341687963</v>
+        <v>-0.08315643978153414</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.834924956096357</v>
+        <v>2.825413890277564</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.74832840831809</v>
+        <v>3.748328408318089</v>
       </c>
       <c r="C1917" t="n">
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.822235933188241</v>
+        <v>-5.838087709552896</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.5418376649044916</v>
+        <v>0.5354969543586292</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.06730466341687963</v>
+        <v>-0.08315643978153414</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.830705664443407</v>
+        <v>2.821194598624615</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057523</v>
+        <v>3.824311233057522</v>
       </c>
       <c r="C1918" t="n">
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.732460260811768</v>
+        <v>-5.748312037176424</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.5798722477750964</v>
+        <v>0.573531537229234</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.005705218502569609</v>
+        <v>-0.02155699486722412</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.86978964531201</v>
+        <v>2.860278579493217</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279182</v>
+        <v>3.82635497427918</v>
       </c>
       <c r="C1919" t="n">
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.482609866862694</v>
+        <v>-5.498461643227349</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.6725544803384285</v>
+        <v>0.6662137697925661</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.005705218502569609</v>
+        <v>-0.02155699486722412</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.862531720295712</v>
+        <v>2.853020654476919</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011494</v>
+        <v>3.835957987011493</v>
       </c>
       <c r="C1920" t="n">
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.306717774395262</v>
+        <v>-5.322569550759917</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.7465104408460497</v>
+        <v>0.7401697303001877</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.005705218502569609</v>
+        <v>-0.02155699486722412</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.86613084381636</v>
+        <v>2.856619777997567</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392983</v>
+        <v>3.780933911392981</v>
       </c>
       <c r="C1921" t="n">
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.135271311372798</v>
+        <v>-5.151123087737454</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8284165321095891</v>
+        <v>0.8220758215637267</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.1657412445198935</v>
+        <v>0.149889468155239</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.982326227684392</v>
+        <v>2.972815161865599</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632777</v>
+        <v>3.773765222632775</v>
       </c>
       <c r="C1922" t="n">
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.055249024263677</v>
+        <v>-5.071100800628333</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.8594459245695343</v>
+        <v>0.8531052140236719</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.2457635316290145</v>
+        <v>0.22991175526436</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.029360077566162</v>
+        <v>3.019849011747369</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883071</v>
+        <v>3.764617879883069</v>
       </c>
       <c r="C1923" t="n">
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.991613282029743</v>
+        <v>-5.007465058394398</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.8895950225174254</v>
+        <v>0.883254311971563</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.309399273862949</v>
+        <v>0.2935474974982945</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.072236323960839</v>
+        <v>3.062725258142047</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074779</v>
+        <v>3.798814771074777</v>
       </c>
       <c r="C1924" t="n">
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.897915963813348</v>
+        <v>-4.913767740178003</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9082682085877791</v>
+        <v>0.9019274980419167</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.309399273862949</v>
+        <v>0.2935474974982945</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.053430582744635</v>
+        <v>3.043919516925842</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242291</v>
+        <v>3.797694884242289</v>
       </c>
       <c r="C1925" t="n">
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.908418586878637</v>
+        <v>-4.924270363243292</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9058102359865408</v>
+        <v>0.8994695254406786</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.2988966507976601</v>
+        <v>0.2830448744330056</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.048872085530339</v>
+        <v>3.039361019711547</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367679</v>
       </c>
       <c r="C1926" t="n">
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.836176018707442</v>
+        <v>-4.852027795072098</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9386365770898388</v>
+        <v>0.9322958665439767</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.2988966507976601</v>
+        <v>0.2830448744330056</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.052801399365159</v>
+        <v>3.043290333546366</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879961</v>
+        <v>3.822326997879959</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.818462331829577</v>
+        <v>-4.834314108194232</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.946400635758325</v>
+        <v>0.9400599252124628</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.3020779796945769</v>
+        <v>0.2862262033299224</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.055388780620649</v>
+        <v>3.045877714801857</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502333</v>
+        <v>3.848616626502332</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.694988060516558</v>
+        <v>-4.710839836881214</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9927884155035258</v>
+        <v>0.9864477049576634</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.3020779796945769</v>
+        <v>0.2862262033299224</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.052386851840643</v>
+        <v>3.04287578602185</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675935</v>
+        <v>3.818668951675933</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.474967262479548</v>
+        <v>-4.490819038844204</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.082375771728944</v>
+        <v>1.076035061183082</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.4432978247625572</v>
+        <v>0.4274460483979027</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.138697795892045</v>
+        <v>3.129186730073252</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.843274527539945</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.34209957341627</v>
+        <v>-4.357951349780926</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.151417030156078</v>
+        <v>1.145076319610216</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.4432978247625572</v>
+        <v>0.4274460483979027</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.154591978693869</v>
+        <v>3.145080912875076</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496259</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.221926490051771</v>
+        <v>-4.237778266416427</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.20063210794218</v>
+        <v>1.194291397396318</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.5634709081270561</v>
+        <v>0.5476191317624016</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.22784167315287</v>
+        <v>3.218330607334077</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576997</v>
+        <v>3.791273551576996</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.086673128721794</v>
+        <v>-4.10252490508645</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.264821555035611</v>
+        <v>1.258480844489748</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.6987242694570333</v>
+        <v>0.6828724930923787</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.319081792512296</v>
+        <v>3.309570726693503</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.146547956079487</v>
+        <v>-4.162399732444142</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.22690911549396</v>
+        <v>1.220568404948097</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.6388494420993411</v>
+        <v>0.6229976657346866</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.269194387499106</v>
+        <v>3.259683321680314</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674512</v>
+        <v>3.762647477674511</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.02672772516865</v>
+        <v>-4.042579501533305</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.290126377092503</v>
+        <v>1.283785666546641</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.6388494420993411</v>
+        <v>0.6229976657346866</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.284483556733315</v>
+        <v>3.274972490914522</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.72914639843069</v>
+        <v>3.729146398430689</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.029197431630456</v>
+        <v>-4.045049207995111</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.196782693830222</v>
+        <v>1.19044198328436</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.6363797356375349</v>
+        <v>0.6205279592728805</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.190645932178673</v>
+        <v>3.18113486635988</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003597</v>
+        <v>3.743220196003596</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.097567617954466</v>
+        <v>-4.113419394319122</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.088696480785919</v>
+        <v>1.082355770240057</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.6456554346737499</v>
+        <v>0.6298036583090955</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.115473213085703</v>
+        <v>3.105962147266911</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.209439897580617</v>
+        <v>-4.225291673945272</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.03438427756735</v>
+        <v>1.028043567021488</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.6456554346737499</v>
+        <v>0.6298036583090955</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.105909921717594</v>
+        <v>3.096398855898802</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.7109067314177</v>
+        <v>3.710906731417699</v>
       </c>
       <c r="C1938" t="n">
         <v>2.855547497605547</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.264959973473206</v>
+        <v>-4.280811749837862</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.149207083902517</v>
+        <v>1.142866373356655</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.6456554346737499</v>
+        <v>0.6298036583090955</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.242940758409797</v>
+        <v>3.233429692591004</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205895</v>
+        <v>3.746042526205894</v>
       </c>
       <c r="C1939" t="n">
         <v>2.860114729597334</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.089485713680737</v>
+        <v>-4.105337490045393</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.223964019811292</v>
+        <v>1.21762330926543</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.6456554346737499</v>
+        <v>0.6298036583090955</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.247507990401584</v>
+        <v>3.237996924582792</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225439</v>
+        <v>3.765024323225438</v>
       </c>
       <c r="C1940" t="n">
         <v>2.835856758358541</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.081561339095823</v>
+        <v>-4.097413115460479</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.202875798406465</v>
+        <v>1.196535087860603</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.6456554346737499</v>
+        <v>0.6298036583090955</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.223250019162792</v>
+        <v>3.213738953343999</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111293</v>
+        <v>3.773210297111292</v>
       </c>
       <c r="C1941" t="n">
         <v>2.764395071759991</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.075283136525974</v>
+        <v>-4.09113491289063</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.133925392835854</v>
+        <v>1.127584682289992</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.6519336372435989</v>
+        <v>0.6360818608789445</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.155555254106151</v>
+        <v>3.146044188287358</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264161</v>
       </c>
       <c r="C1942" t="n">
         <v>2.774567458192124</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.015430517322251</v>
+        <v>-4.031282293686907</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.168038826949476</v>
+        <v>1.161698116403614</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.6519336372435989</v>
+        <v>0.6360818608789445</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.165727640538283</v>
+        <v>3.15621657471949</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.786949957742297</v>
       </c>
       <c r="C1943" t="n">
         <v>2.769513728765984</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.929187054295873</v>
+        <v>-3.945038830660529</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.197482482733887</v>
+        <v>1.191141772188025</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.6519336372435989</v>
+        <v>0.6360818608789445</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.160673911112144</v>
+        <v>3.151162845293351</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316044</v>
       </c>
       <c r="C1944" t="n">
         <v>2.761289504210509</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.974493873694853</v>
+        <v>-3.990345650059509</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.171135530418821</v>
+        <v>1.164794819872959</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.6111234742343681</v>
+        <v>0.5952716978697137</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.127963588751131</v>
+        <v>3.118452522932338</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.761841377243611</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.003526978397154</v>
+        <v>-4.01937875476181</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.160074161571002</v>
+        <v>1.15373345102514</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.6111234742343681</v>
+        <v>0.5952716978697137</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.128515461784232</v>
+        <v>3.119004395965439</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809498</v>
+        <v>3.733390600809496</v>
       </c>
       <c r="C1946" t="n">
         <v>2.691114069134977</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.910716496946295</v>
+        <v>-3.926568273310951</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.126471046042711</v>
+        <v>1.120130335496849</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.7039339556852274</v>
+        <v>0.688082179320573</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.113474442546113</v>
+        <v>3.103963376727321</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560425</v>
+        <v>3.748285816560423</v>
       </c>
       <c r="C1947" t="n">
         <v>2.692987545059577</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.955105966275723</v>
+        <v>-3.970957742640378</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.110588734235541</v>
+        <v>1.104248023689679</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.6595444863557998</v>
+        <v>0.6436927099911454</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.088714236873058</v>
+        <v>3.079203171054265</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.721077195472733</v>
       </c>
       <c r="C1948" t="n">
         <v>2.6880632535713</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.071647571381066</v>
+        <v>-4.087499347745721</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.059047800705127</v>
+        <v>1.052707090159265</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.543002881250457</v>
+        <v>0.5271511048858026</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.013864982321575</v>
+        <v>3.004353916502782</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798532</v>
       </c>
       <c r="C1949" t="n">
         <v>2.693554549401968</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.111571665963638</v>
+        <v>-4.127423442328293</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.048569458702765</v>
+        <v>1.042228748156903</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.543002881250457</v>
+        <v>0.5271511048858026</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.019356278152242</v>
+        <v>3.009845212333449</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498862</v>
+        <v>3.689597840498858</v>
       </c>
       <c r="C1950" t="n">
         <v>2.705051751170507</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.13935206386499</v>
+        <v>-4.155203840229646</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.048954501310763</v>
+        <v>1.042613790764901</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.5152224833491039</v>
+        <v>0.4993707069844495</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.014185241179969</v>
+        <v>3.004674175361177</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.643069621705318</v>
       </c>
       <c r="C1951" t="n">
         <v>2.54340747117116</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.257732736595129</v>
+        <v>-4.273584512959784</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8399579522193612</v>
+        <v>0.833617241673499</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.4480046311981277</v>
+        <v>0.4321528548334733</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.812210249890037</v>
+        <v>2.802699184071244</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729266</v>
+        <v>3.682716310729262</v>
       </c>
       <c r="C1952" t="n">
         <v>2.663557131890366</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.36634681503846</v>
+        <v>-4.382198591403116</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9166619815612345</v>
+        <v>0.9103212710153721</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.4480046311981277</v>
+        <v>0.4321528548334733</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.932359910609243</v>
+        <v>2.92284884479045</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190766</v>
+        <v>3.733012441190763</v>
       </c>
       <c r="C1953" t="n">
         <v>2.678070157992689</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.330937776790317</v>
+        <v>-4.346789553154973</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9453386229628147</v>
+        <v>0.9389979124169523</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.4480046311981277</v>
+        <v>0.4321528548334733</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.946872936711566</v>
+        <v>2.937361870892773</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.74117406991342</v>
       </c>
       <c r="C1954" t="n">
         <v>2.675489599335057</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.292554114232166</v>
+        <v>-4.308405890596822</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9581115293284437</v>
+        <v>0.9517708187825815</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4863882937562789</v>
+        <v>0.4705365173916245</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.967322575588825</v>
+        <v>2.957811509770032</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532484</v>
+        <v>3.751147197532481</v>
       </c>
       <c r="C1955" t="n">
         <v>2.672218628180359</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.115437784197</v>
+        <v>-4.131289560561656</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.025687090187812</v>
+        <v>1.01934637964195</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4863882937562789</v>
+        <v>0.4705365173916245</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.964051604434127</v>
+        <v>2.954540538615334</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793897</v>
       </c>
       <c r="C1956" t="n">
         <v>2.672902019942272</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.160530029030546</v>
+        <v>-4.176381805395201</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.008333584016307</v>
+        <v>1.001992873470445</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.4244922505868891</v>
+        <v>0.4086404742222347</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.927597370294406</v>
+        <v>2.918086304475613</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011229</v>
       </c>
       <c r="C1957" t="n">
         <v>2.666688995248687</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.981154607791778</v>
+        <v>-3.997006384156434</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.073870727818228</v>
+        <v>1.067530017272366</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.5812690087576078</v>
+        <v>0.5654172323929534</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.015450400503252</v>
+        <v>3.005939334684459</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982227</v>
+        <v>3.716991718982223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.647496450580276</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.026168821312384</v>
+        <v>-4.042020597677039</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.036672497741576</v>
+        <v>1.030331787195713</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.5509201134430032</v>
+        <v>0.5350683370783488</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.978048518646079</v>
+        <v>2.968537452827286</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509535</v>
+        <v>3.737026608509532</v>
       </c>
       <c r="C1959" t="n">
         <v>2.653188012919222</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.293173331584819</v>
+        <v>-4.309025107949474</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9355622559715475</v>
+        <v>0.9292215454256851</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.3565570754000546</v>
+        <v>0.3407052990354002</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.867122258159255</v>
+        <v>2.857611192340463</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.702309454760808</v>
       </c>
       <c r="C1960" t="n">
         <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.394371113021991</v>
+        <v>-4.410222889386647</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8942870652931798</v>
+        <v>0.8879463547473176</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2881482618547354</v>
+        <v>0.272296485490081</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.825280891928565</v>
+        <v>2.815769826109773</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815453</v>
       </c>
       <c r="C1961" t="n">
         <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.387860146407679</v>
+        <v>-4.403711922772334</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8944914134932216</v>
+        <v>0.8881507029473594</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2881482618547354</v>
+        <v>0.272296485490081</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.822880853482882</v>
+        <v>2.813369787664089</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.368822018700381</v>
+        <v>-4.384673795065037</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8986313837843856</v>
+        <v>0.8922906732385232</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.2299646505235409</v>
+        <v>0.2141128741588865</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.78449540589241</v>
+        <v>2.774984340073618</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106447313125</v>
+        <v>3.731064473131246</v>
       </c>
       <c r="C1963" t="n">
         <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.421337820975202</v>
+        <v>-4.437189597339858</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9969194645086477</v>
+        <v>0.9905787539627853</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.2299646505235409</v>
+        <v>0.2141128741588865</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.9037898075266</v>
+        <v>2.894278741707808</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067863</v>
+        <v>3.722447362067859</v>
       </c>
       <c r="C1964" t="n">
         <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.43520458230912</v>
+        <v>-4.451056358673775</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9922060889612141</v>
+        <v>0.9858653784153517</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.1921067337897179</v>
+        <v>0.1762549574250635</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.88190838647244</v>
+        <v>2.872397320653648</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.78742558078912</v>
+        <v>3.787425580789116</v>
       </c>
       <c r="C1965" t="n">
         <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.39040041076919</v>
+        <v>-4.406252187133846</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.016136287974112</v>
+        <v>1.00979557742825</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.1921067337897179</v>
+        <v>0.1762549574250635</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.887916916869366</v>
+        <v>2.878405851050573</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519903</v>
       </c>
       <c r="C1966" t="n">
         <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.242657440534187</v>
+        <v>-4.258509216898843</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9731836973453125</v>
+        <v>0.9668429867994501</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.3599140910246011</v>
+        <v>0.3440623146599467</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.886551552487496</v>
+        <v>2.877040486668703</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.802245929181165</v>
       </c>
       <c r="C1967" t="n">
         <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.326478661808886</v>
+        <v>-4.342330438173541</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9424488303669141</v>
+        <v>0.9361081198210517</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.3599140910246011</v>
+        <v>0.3440623146599467</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.889345174018977</v>
+        <v>2.879834108200184</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394728</v>
+        <v>3.805608985394724</v>
       </c>
       <c r="C1968" t="n">
         <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.320325955756101</v>
+        <v>-4.336177732120757</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9455722611796862</v>
+        <v>0.9392315506338238</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.3660667970773854</v>
+        <v>0.350215020712731</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.893699146042306</v>
+        <v>2.884188080223513</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890612</v>
+        <v>3.798239794890608</v>
       </c>
       <c r="C1969" t="n">
         <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.337135253906603</v>
+        <v>-4.352987030271259</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9379290186595957</v>
+        <v>0.9315883081137333</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.3492574989268837</v>
+        <v>0.3334057225622293</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.882694043892115</v>
+        <v>2.873182978073322</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798423</v>
+        <v>3.867362636798419</v>
       </c>
       <c r="C1970" t="n">
         <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.274837255130481</v>
+        <v>-4.290689031495137</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.029183771966866</v>
+        <v>1.022843061421003</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.3945517632013258</v>
+        <v>0.3786999868366714</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.976206156253601</v>
+        <v>2.966695090434808</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992189</v>
+        <v>3.848729139992185</v>
       </c>
       <c r="C1971" t="n">
         <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.073047057465323</v>
+        <v>-4.088898833829979</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9121918527470556</v>
+        <v>0.9058511422011934</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.5925699553704802</v>
+        <v>0.5767181790058258</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.89730907326922</v>
+        <v>2.887798007450428</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852423</v>
+        <v>3.84144481785242</v>
       </c>
       <c r="C1972" t="n">
         <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.123933770151518</v>
+        <v>-4.139785546516173</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9621273999947531</v>
+        <v>0.9557866894488907</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.5416832426842857</v>
+        <v>0.5258314663196313</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.937067277979679</v>
+        <v>2.927556212160886</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319542</v>
+        <v>3.819063300319539</v>
       </c>
       <c r="C1973" t="n">
         <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.037323027501711</v>
+        <v>-4.053174803866367</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.011399433170719</v>
+        <v>1.005058722624857</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.6203089738894439</v>
+        <v>0.6044571975247895</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.998870452818818</v>
+        <v>2.989359387000025</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489382</v>
+        <v>3.831819032489379</v>
       </c>
       <c r="C1974" t="n">
         <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.097532325506996</v>
+        <v>-4.113384101871651</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9858516947932772</v>
+        <v>0.9795109842474148</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.5600996758841594</v>
+        <v>0.544247899519505</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.961280854840318</v>
+        <v>2.951769789021526</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397792</v>
+        <v>3.836411672397788</v>
       </c>
       <c r="C1975" t="n">
         <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.048345676822644</v>
+        <v>-4.0641974531873</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.004017972306946</v>
+        <v>0.9976772617610838</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.5600996758841594</v>
+        <v>0.544247899519505</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.959772472880247</v>
+        <v>2.950261407061455</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316246</v>
+        <v>3.833513460316243</v>
       </c>
       <c r="C1976" t="n">
         <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.003972545184076</v>
+        <v>-4.019824321548731</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.02163009239781</v>
+        <v>1.015289381851948</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.604472807522728</v>
+        <v>0.5886210311580736</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.986259219298824</v>
+        <v>2.976748153480032</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105965</v>
+        <v>3.821562117105961</v>
       </c>
       <c r="C1977" t="n">
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.026452896042961</v>
+        <v>-4.042304672407616</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.007031746192846</v>
+        <v>1.000691035646984</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.604472807522728</v>
+        <v>0.5886210311580736</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.980653013437415</v>
+        <v>2.971141947618622</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190323</v>
+        <v>3.83301114819032</v>
       </c>
       <c r="C1978" t="n">
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.978797165481905</v>
+        <v>-3.99464894184656</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.032475795445073</v>
+        <v>1.026135084899211</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.6521285380837837</v>
+        <v>0.6362767617191293</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.015628208801853</v>
+        <v>3.006117142983061</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569616</v>
+        <v>3.822678210569613</v>
       </c>
       <c r="C1979" t="n">
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.87827900698315</v>
+        <v>-3.894130783347806</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.0775754322193</v>
+        <v>1.071234721673438</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.7526466965825382</v>
+        <v>0.7367949202178838</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.080831477275831</v>
+        <v>3.071320411457038</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557292</v>
+        <v>3.828808877557289</v>
       </c>
       <c r="C1980" t="n">
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.862373677550798</v>
+        <v>-3.878225453915453</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.070692236468113</v>
+        <v>1.064351525922251</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.6735340358732993</v>
+        <v>0.6576822595086449</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.02011855332616</v>
+        <v>3.010607487507367</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932767</v>
+        <v>3.816837033932764</v>
       </c>
       <c r="C1981" t="n">
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.817535275942399</v>
+        <v>-3.833387052307055</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.092725299722101</v>
+        <v>1.086384589176239</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.6780774688181688</v>
+        <v>0.6622256924535144</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.02694231570371</v>
+        <v>3.017431249884917</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.817932354917046</v>
       </c>
       <c r="C1982" t="n">
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.837033732184408</v>
+        <v>-3.852885508549063</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.089086856856376</v>
+        <v>1.082746146310514</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.6299928275382645</v>
+        <v>0.6141410511736101</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.002252470566845</v>
+        <v>2.992741404748053</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405954</v>
       </c>
       <c r="C1983" t="n">
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.792830895098507</v>
+        <v>-3.808682671463163</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.112647594218573</v>
+        <v>1.106306883672711</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.6741956646241649</v>
+        <v>0.6583438882595105</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.034653775346222</v>
+        <v>3.02514270952743</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265642</v>
+        <v>3.838199629265638</v>
       </c>
       <c r="C1984" t="n">
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.800390560935554</v>
+        <v>-3.81624233730021</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.108033728353002</v>
+        <v>1.10169301780714</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.7289990686339842</v>
+        <v>0.7131472922693298</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.065945818221362</v>
+        <v>3.056434752402569</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.863895080284873</v>
       </c>
       <c r="C1985" t="n">
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.642099143396282</v>
+        <v>-3.657950919760938</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.222598060551751</v>
+        <v>1.216257350005888</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.7289990686339842</v>
+        <v>0.7131472922693298</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.117193583404402</v>
+        <v>3.107682517585609</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321017</v>
       </c>
       <c r="C1986" t="n">
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.434457139761806</v>
+        <v>-3.450308916126462</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.304095566599794</v>
+        <v>1.297754856053932</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.9366410722684604</v>
+        <v>0.920789295903806</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.24021949017934</v>
+        <v>3.230708424360548</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475133</v>
       </c>
       <c r="C1987" t="n">
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.383425047039278</v>
+        <v>-3.399276823403933</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.319456631927075</v>
+        <v>1.313115921381213</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.9876731649909883</v>
+        <v>0.9718213886263339</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.265786974051127</v>
+        <v>3.256275908232334</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.842547360404847</v>
       </c>
       <c r="C1988" t="n">
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.318200865912072</v>
+        <v>-3.334052642276728</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.362733708470663</v>
+        <v>1.3563929979248</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.052897346118194</v>
+        <v>1.037045569753539</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.322108886820155</v>
+        <v>3.312597821001363</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882555</v>
+        <v>3.840061186882552</v>
       </c>
       <c r="C1989" t="n">
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.280773845840938</v>
+        <v>-3.296625622205594</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.373665488798397</v>
+        <v>1.367324778252534</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.058148884147375</v>
+        <v>1.042297107782721</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.321220781936944</v>
+        <v>3.311709716118152</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992658</v>
+        <v>3.845169808992654</v>
       </c>
       <c r="C1990" t="n">
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.300885501875646</v>
+        <v>-3.316737278240302</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.366877618715753</v>
+        <v>1.360536908169891</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.069176229144795</v>
+        <v>1.05332445278014</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.329093981266636</v>
+        <v>3.319582915447844</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636285</v>
+        <v>3.828661445636281</v>
       </c>
       <c r="C1991" t="n">
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.272472238775763</v>
+        <v>-3.288324015140418</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.538800694976918</v>
+        <v>1.532459984431055</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.010200666398366</v>
+        <v>0.9943488900337114</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.45426641463999</v>
+        <v>3.444755348821197</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957623</v>
+        <v>3.81322282095762</v>
       </c>
       <c r="C1992" t="n">
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.19768997775075</v>
+        <v>-3.213541754115406</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.68882650860474</v>
+        <v>1.682485798058878</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.084982927423378</v>
+        <v>1.069131151058724</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.619248680472815</v>
+        <v>3.609737614654022</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998754</v>
+        <v>3.81423072799875</v>
       </c>
       <c r="C1993" t="n">
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.171605893486942</v>
+        <v>-3.187457669851598</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.690968118324122</v>
+        <v>1.68462740777826</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.084982927423378</v>
+        <v>1.069131151058724</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.610956656486674</v>
+        <v>3.601445590667881</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896925</v>
       </c>
       <c r="C1994" t="n">
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.083727980377822</v>
+        <v>-3.119631382367325</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.72431247915155</v>
+        <v>1.709951118355748</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.200908569846729</v>
+        <v>1.233674174192717</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.678705237524464</v>
+        <v>3.698364600132056</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959856</v>
+        <v>3.796264143959852</v>
       </c>
       <c r="C1995" t="n">
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.074835518984538</v>
+        <v>-3.110738920974042</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.745423869435655</v>
+        <v>1.731062508639853</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.200908569846729</v>
+        <v>1.233674174192717</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.696259643251255</v>
+        <v>3.715919005858847</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945364</v>
+        <v>3.794424941945359</v>
       </c>
       <c r="C1996" t="n">
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.243311635954416</v>
+        <v>-3.27921503794392</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.669888470052287</v>
+        <v>1.655527109256486</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.172960734130149</v>
+        <v>1.205726338476136</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.671345989225891</v>
+        <v>3.691005351833483</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782703</v>
       </c>
       <c r="C1997" t="n">
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.797055443324976</v>
+        <v>-2.83295884531448</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.829660644291925</v>
+        <v>1.815299283496124</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.078242064460516</v>
+        <v>1.111007668806503</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.595784484611973</v>
+        <v>3.615443847219565</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632635</v>
+        <v>3.784671345632631</v>
       </c>
       <c r="C1998" t="n">
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.774334339641824</v>
+        <v>-2.810237741631328</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.829413108262091</v>
+        <v>1.815051747466289</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.078242064460516</v>
+        <v>1.111007668806503</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.586448507108877</v>
+        <v>3.60610786971647</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777672</v>
+        <v>3.783205696777668</v>
       </c>
       <c r="C1999" t="n">
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.903536152935866</v>
+        <v>-2.93943955492537</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.936638508795643</v>
+        <v>1.922277147999841</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.9490402511664737</v>
+        <v>0.9818058555124609</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.667833544983621</v>
+        <v>3.687492907591214</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644411</v>
+        <v>3.779933725644407</v>
       </c>
       <c r="C2000" t="n">
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.929410551409892</v>
+        <v>-2.965313953399396</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.963366571899679</v>
+        <v>1.949005211103877</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.9939518598782149</v>
+        <v>1.026717464224202</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.731858332704312</v>
+        <v>3.751517695311905</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799963</v>
+        <v>3.76944361979996</v>
       </c>
       <c r="C2001" t="n">
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.922355861194718</v>
+        <v>-2.958259263184222</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.962863803975294</v>
+        <v>1.948502443179492</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.001006550093389</v>
+        <v>1.033772154439376</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.732766502822962</v>
+        <v>3.752425865430554</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331114</v>
+        <v>3.766673496331109</v>
       </c>
       <c r="C2002" t="n">
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.89540463686823</v>
+        <v>-2.931308038857734</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.98365044735063</v>
+        <v>1.969289086554829</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.015886896121108</v>
+        <v>1.048652500467095</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.751700864084335</v>
+        <v>3.771360226691927</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784106</v>
+        <v>3.768052067784102</v>
       </c>
       <c r="C2003" t="n">
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.031357644924547</v>
+        <v>-3.067261046914051</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.113372376273063</v>
+        <v>2.099011015477262</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.015886896121108</v>
+        <v>1.048652500467095</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.935803996229295</v>
+        <v>3.955463358836887</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714425</v>
+        <v>3.743925505714421</v>
       </c>
       <c r="C2004" t="n">
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.053765762729419</v>
+        <v>-3.089669164718923</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.096525824054108</v>
+        <v>2.082164463258306</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.015886896121108</v>
+        <v>1.048652500467095</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.927920691132288</v>
+        <v>3.94758005373988</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155031</v>
+        <v>3.719118627155027</v>
       </c>
       <c r="C2005" t="n">
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.081989998307019</v>
+        <v>-3.117893400296523</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.087290129372705</v>
+        <v>2.072928768576904</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.033863648572416</v>
+        <v>1.066629252918404</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.94076074215271</v>
+        <v>3.960420104760303</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161975</v>
+        <v>3.729452285161971</v>
       </c>
       <c r="C2006" t="n">
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.091430924195549</v>
+        <v>-3.127334326185053</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.139767476739141</v>
+        <v>2.125406115943339</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.156290766115808</v>
+        <v>1.189056370461795</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.070470730400592</v>
+        <v>4.090130093008185</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321632</v>
+        <v>3.714941193321628</v>
       </c>
       <c r="C2007" t="n">
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.14370453153119</v>
+        <v>-3.179607933520694</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.121749128350185</v>
+        <v>2.107387767554383</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.104017158780167</v>
+        <v>1.136782763126154</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.041997660544508</v>
+        <v>4.061657023152101</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347701</v>
+        <v>3.727898186347698</v>
       </c>
       <c r="C2008" t="n">
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.220034509132096</v>
+        <v>-3.2559379111216</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.089328950203598</v>
+        <v>2.074967589407796</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.104017158780167</v>
+        <v>1.136782763126154</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.040109473438283</v>
+        <v>4.059768836045876</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887746</v>
+        <v>3.710654104887743</v>
       </c>
       <c r="C2009" t="n">
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.313698453809637</v>
+        <v>-3.349601855799142</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.046683601935444</v>
+        <v>2.032322241139642</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.010353214102625</v>
+        <v>1.043118818448612</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.978731336234621</v>
+        <v>3.998390698842213</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343065</v>
+        <v>3.712897612343061</v>
       </c>
       <c r="C2010" t="n">
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.475266879336893</v>
+        <v>-3.511170281326397</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.980490241934694</v>
+        <v>1.966128881138892</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.8835702903047459</v>
+        <v>0.9163358946507328</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.901095592166046</v>
+        <v>3.920754954773638</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389347</v>
+        <v>3.754596135389344</v>
       </c>
       <c r="C2011" t="n">
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.583567541207012</v>
+        <v>-3.619470943196516</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.950243384052564</v>
+        <v>1.935882023256763</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.8835702903047459</v>
+        <v>0.9163358946507328</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.914168999031965</v>
+        <v>3.933828361639557</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74988269137839</v>
+        <v>3.749882691378388</v>
       </c>
       <c r="C2012" t="n">
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.676715012510379</v>
+        <v>-3.712618414499883</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.904989592314158</v>
+        <v>1.890628231518356</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7607410790222131</v>
+        <v>0.7935066833682001</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.832476669045385</v>
+        <v>3.852136031652977</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006974</v>
+        <v>3.715819895006971</v>
       </c>
       <c r="C2013" t="n">
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.704615799619852</v>
+        <v>-3.740519201609356</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.892353318597371</v>
+        <v>1.877991957801569</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7261441548792783</v>
+        <v>0.7589097592252653</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.810242555686626</v>
+        <v>3.829901918294218</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787386</v>
+        <v>3.684895778787383</v>
       </c>
       <c r="C2014" t="n">
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.827141902322746</v>
+        <v>-3.86304530431225</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.840107321493412</v>
+        <v>1.82574596069761</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6036180521763844</v>
+        <v>0.6363836565223714</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.733491338042088</v>
+        <v>3.75315070064968</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585936</v>
+        <v>3.619348081585932</v>
       </c>
       <c r="C2015" t="n">
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.057656398508334</v>
+        <v>-4.093559800497839</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.81460748260968</v>
+        <v>1.800246121813878</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.3731035559907957</v>
+        <v>0.4058691603367827</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.661888599921239</v>
+        <v>3.681547962528831</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814664</v>
+        <v>3.640750087814659</v>
       </c>
       <c r="C2016" t="n">
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.406401483732778</v>
+        <v>-4.442304885722282</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.81542116752175</v>
+        <v>1.801059806725948</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.2643556020718979</v>
+        <v>0.2971212064178849</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.736951546571747</v>
+        <v>3.756610909179339</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237092</v>
+        <v>3.668289004237088</v>
       </c>
       <c r="C2017" t="n">
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.560387901508919</v>
+        <v>-4.596291303498423</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.822806869556933</v>
+        <v>1.808445508761132</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.2643556020718979</v>
+        <v>0.2971212064178849</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.805931815717387</v>
+        <v>3.825591178324979</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423385</v>
+        <v>3.619923016423381</v>
       </c>
       <c r="C2018" t="n">
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.509865997681253</v>
+        <v>-4.545769399670757</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.82906683320812</v>
+        <v>1.814705472412319</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.2643556020718979</v>
+        <v>0.2971212064178849</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.791983017837508</v>
+        <v>3.8116423804451</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609752</v>
+        <v>3.656332733609747</v>
       </c>
       <c r="C2019" t="n">
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.762341151688977</v>
+        <v>-4.798244553678481</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.739947260660445</v>
+        <v>1.725585899864643</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.2643556020718979</v>
+        <v>0.2971212064178849</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.803853506892922</v>
+        <v>3.823512869500514</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973156</v>
+        <v>3.674028535973151</v>
       </c>
       <c r="C2020" t="n">
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.055236908168389</v>
+        <v>-5.091140310157893</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.623999492587624</v>
+        <v>1.609638131791822</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.2643556020718979</v>
+        <v>0.2971212064178849</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.805064041411865</v>
+        <v>3.824723404019458</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251944</v>
+        <v>3.66350945725194</v>
       </c>
       <c r="C2021" t="n">
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.241901036303197</v>
+        <v>-5.277804438292701</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.553455583561022</v>
+        <v>1.53909422276522</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.237616631247338</v>
+        <v>0.270382235593325</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.793142401144451</v>
+        <v>3.812801763752043</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.6521491529162</v>
+        <v>3.652149152916196</v>
       </c>
       <c r="C2022" t="n">
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.387921723217159</v>
+        <v>-5.423825125206664</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.490125161531626</v>
+        <v>1.475763800735824</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.228533539453481</v>
+        <v>0.261299143799468</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.782770398804326</v>
+        <v>3.802429761411918</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830327</v>
+        <v>3.667962306830322</v>
       </c>
       <c r="C2023" t="n">
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.479635732326745</v>
+        <v>-5.515539134316249</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.615643614586836</v>
+        <v>1.601282253791034</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.228533539453481</v>
+        <v>0.261299143799468</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.94497445550337</v>
+        <v>3.964633818110962</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071549</v>
+        <v>3.696539468071545</v>
       </c>
       <c r="C2024" t="n">
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.511287391386714</v>
+        <v>-5.547190793376219</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.597829588926662</v>
+        <v>1.583468228130861</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.2233650822090408</v>
+        <v>0.2561306865550278</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.93672001912052</v>
+        <v>3.956379381728112</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868144</v>
+        <v>3.75004401586814</v>
       </c>
       <c r="C2025" t="n">
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.593222209655598</v>
+        <v>-5.629125611645102</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.575285079187601</v>
+        <v>1.560923718391799</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.2134303366219606</v>
+        <v>0.2461959409679476</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.940988589336763</v>
+        <v>3.960647951944355</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332689</v>
+        <v>3.783632867332685</v>
       </c>
       <c r="C2026" t="n">
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.695198331904005</v>
+        <v>-5.731101733893509</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.54342026874414</v>
+        <v>1.529058907948338</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.1114542143735531</v>
+        <v>0.14421981871954</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.888728554443621</v>
+        <v>3.908387917051213</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231806</v>
+        <v>3.798296784231802</v>
       </c>
       <c r="C2027" t="n">
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.585192048426784</v>
+        <v>-5.621095450416288</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.579575669379204</v>
+        <v>1.565214308583402</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.1346587862908283</v>
+        <v>0.1674243906368152</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.894804184838162</v>
+        <v>3.914463547445754</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.78556392481852</v>
+        <v>3.785563924818517</v>
       </c>
       <c r="C2028" t="n">
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.442132472685858</v>
+        <v>-5.478035874675362</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.641049510397548</v>
+        <v>1.626688149601747</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.1426722128808076</v>
+        <v>0.1754378172267945</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.903862251514123</v>
+        <v>3.923521614121716</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051786</v>
+        <v>3.777237412051782</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.825519806668175</v>
+        <v>3.704210948679298</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.14068574721402</v>
+        <v>-5.176589149203524</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.76888908346882</v>
+        <v>1.633218864684141</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.4441189383526448</v>
+        <v>0.4768845426986318</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.091991169679762</v>
+        <v>3.990341674298477</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679622</v>
+        <v>3.812635940679618</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.826490984420885</v>
+        <v>3.705182126432009</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.165275991449204</v>
+        <v>-5.201179393438708</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.760024163527456</v>
+        <v>1.624353944742778</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.4441189383526448</v>
+        <v>0.4768845426986318</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.092962347432472</v>
+        <v>3.991312852051188</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474156</v>
+        <v>3.821184182474153</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.827333888800641</v>
+        <v>3.706025030811765</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.114237615442684</v>
+        <v>-5.150141017432188</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.78128241830982</v>
+        <v>1.645612199525142</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.4441189383526448</v>
+        <v>0.4768845426986318</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.093805251812228</v>
+        <v>3.992155756430944</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.83173451696954</v>
+        <v>3.831734516969536</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.846371987674786</v>
+        <v>3.72506312968591</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.073098320576053</v>
+        <v>-5.109001722565557</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.816776235130618</v>
+        <v>1.68110601634594</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.4852582332192756</v>
+        <v>0.5180238375652626</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.137526927606352</v>
+        <v>4.035877432225067</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700476</v>
+        <v>3.825752932700472</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.662555983798721</v>
+        <v>3.541247125809845</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.976463408557413</v>
+        <v>-5.012366810546917</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.671614196062009</v>
+        <v>1.535943977277331</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.5818931452379156</v>
+        <v>0.6146587495839025</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.011691870941471</v>
+        <v>3.910042375560186</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077638</v>
+        <v>3.804688961077634</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.666058027872685</v>
+        <v>3.544749169883809</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.107044143088255</v>
+        <v>-5.142947545077759</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.622883946323636</v>
+        <v>1.487213727538958</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.4513124107070731</v>
+        <v>0.48407801505306</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.936845474296929</v>
+        <v>3.835195978915645</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833455</v>
+        <v>3.775028860833451</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.650484846948768</v>
+        <v>3.529175988959891</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.942547808897293</v>
+        <v>-4.978451210886798</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.673109299076103</v>
+        <v>1.537439080291425</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.6158087448980349</v>
+        <v>0.6485743492440219</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.019970093887589</v>
+        <v>3.918320598506305</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077626</v>
+        <v>3.821030660077623</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.649672557385197</v>
+        <v>3.528363699396321</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.969917741581726</v>
+        <v>-5.00582114357123</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.66134903643876</v>
+        <v>1.525678817654082</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.6158087448980349</v>
+        <v>0.6485743492440219</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.019157804324019</v>
+        <v>3.917508308942734</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147906</v>
+        <v>3.832307024147903</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.65954133651027</v>
+        <v>3.538232478521393</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.980302936471615</v>
+        <v>-5.016206338461119</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.667063737607877</v>
+        <v>1.531393518823199</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.6054235500081456</v>
+        <v>0.6381891543541326</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.022795466515158</v>
+        <v>3.921145971133873</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735278</v>
+        <v>3.834415493735275</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.730378342286695</v>
+        <v>3.609069484297819</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.99889109519384</v>
+        <v>-5.034794497183344</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.730465479895412</v>
+        <v>1.594795261110734</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.5868353912859203</v>
+        <v>0.6196009956319073</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.082479577058248</v>
+        <v>3.980830081676963</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496551</v>
+        <v>3.855120535496547</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.727247353104993</v>
+        <v>3.605938495116117</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.999189641889876</v>
+        <v>-5.03509304387938</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.727215072035296</v>
+        <v>1.591544853250618</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.5865368445898844</v>
+        <v>0.6193024489358714</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.079169459858925</v>
+        <v>3.97751996447764</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108854</v>
+        <v>3.81564321210885</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.731778248044385</v>
+        <v>3.610469390055508</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.898366508199448</v>
+        <v>-4.934269910188952</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.772075220450858</v>
+        <v>1.63640500166618</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.5990010600742383</v>
+        <v>0.6317666644202252</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.091178884088928</v>
+        <v>3.989529388707644</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121463</v>
+        <v>3.807356168121459</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.731907501522928</v>
+        <v>3.610598643534052</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.707585147447041</v>
+        <v>-4.743488549436545</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.848517018230365</v>
+        <v>1.712846799445686</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.7897824208266456</v>
+        <v>0.8225480251726326</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.205776954018916</v>
+        <v>4.104127458637632</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906076</v>
+        <v>3.775233033906073</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.711744347260525</v>
+        <v>3.590435489271648</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.60062178959762</v>
+        <v>-4.636525191587124</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.87113920710773</v>
+        <v>1.735468988323052</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.8482470287864471</v>
+        <v>0.8810126331324341</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.220692564532393</v>
+        <v>4.119043069151109</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912981</v>
+        <v>3.785761685912978</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.746711283872583</v>
+        <v>3.625402425883707</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.545291201695857</v>
+        <v>-4.581194603685361</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.928238378880493</v>
+        <v>1.792568160095815</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.9035776166882092</v>
+        <v>0.9363432210341962</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.288857853885509</v>
+        <v>4.187208358504225</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539891</v>
+        <v>3.743767956539887</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.740397851774021</v>
+        <v>3.619088993785144</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.533237074782894</v>
+        <v>-4.569140476772398</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.926746597547116</v>
+        <v>1.791076378762438</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.9156317436011721</v>
+        <v>0.948397347947159</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.289776897934725</v>
+        <v>4.18812740255344</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811005</v>
+        <v>3.725010844811002</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.742278481958157</v>
+        <v>3.62096962396928</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.574392194351115</v>
+        <v>-4.610295596340619</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.912165179903963</v>
+        <v>1.776494961119285</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.8744766240329511</v>
+        <v>0.9072422283789381</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.266964456377927</v>
+        <v>4.165314960996644</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382916</v>
+        <v>3.612322444382913</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.755129507836039</v>
+        <v>3.633820649847163</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.506343631659585</v>
+        <v>-4.542247033649089</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.952235630858458</v>
+        <v>1.81656541207378</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.9425251867244809</v>
+        <v>0.9752907910704679</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.320644619870728</v>
+        <v>4.218995124489444</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013423</v>
+        <v>3.646857607760309</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.775332178009633</v>
+        <v>3.654023320020757</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.737944024829086</v>
+        <v>-4.77384742681859</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.879798143764252</v>
+        <v>1.744127924979574</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.9425251867244809</v>
+        <v>0.9752907910704679</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.340847290044322</v>
+        <v>4.239197794663038</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498968</v>
+        <v>3.666767386781699</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.758938414076515</v>
+        <v>3.654023320020757</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.807829082898062</v>
+        <v>-4.791919935110202</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.835450356603543</v>
+        <v>1.736898921662929</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.9425251867244809</v>
+        <v>0.9752907910704679</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.324453526111204</v>
+        <v>4.239197794663038</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800097</v>
+        <v>3.670068888082828</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.719190327669982</v>
+        <v>3.614275233614224</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.982935915474506</v>
+        <v>-4.967026767686647</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.725659537166432</v>
+        <v>1.627108102225817</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.9425251867244809</v>
+        <v>0.9752907910704679</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.284705439704671</v>
+        <v>4.199449708256505</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660848</v>
+        <v>3.74559333394358</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.726212946666922</v>
+        <v>3.621297852611164</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.951649894934051</v>
+        <v>-4.935740747146192</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.745196564379554</v>
+        <v>1.646645129438939</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.9738112072649363</v>
+        <v>1.006576811610923</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.310499671025884</v>
+        <v>4.225243939577718</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395086</v>
+        <v>3.730590658677817</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.825383946239826</v>
+        <v>3.720468852184068</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.798624502820767</v>
+        <v>-4.782715355032908</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.905577720797773</v>
+        <v>1.807026285857158</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.12683659937822</v>
+        <v>1.159602203724207</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.501485905866759</v>
+        <v>4.416230174418593</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791145</v>
+        <v>3.741298518073876</v>
       </c>
       <c r="C2052" t="n">
-        <v>4.012850171148119</v>
+        <v>3.907935077092361</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.826931816694037</v>
+        <v>-4.811022668906178</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.081721020156757</v>
+        <v>1.983169585216142</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.12683659937822</v>
+        <v>1.159602203724207</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.688952130775052</v>
+        <v>4.603696399326886</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.69911561562043</v>
+        <v>3.699135800903161</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.982253122502201</v>
+        <v>3.877338028446443</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.993525041807559</v>
+        <v>-4.9776158940197</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.98448668146543</v>
+        <v>1.885935246524816</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.9602433742646979</v>
+        <v>0.9930089786106848</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.55839914706102</v>
+        <v>4.473143415612855</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285645</v>
+        <v>3.708202704568375</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.985929525163919</v>
+        <v>3.881014431108161</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.820460662425259</v>
+        <v>-4.8045515146374</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.057388835880068</v>
+        <v>1.958837400939454</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.9602433742646979</v>
+        <v>0.9930089786106848</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.562075549722738</v>
+        <v>4.476819818274572</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399466</v>
+        <v>3.740601586682197</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.983547580287414</v>
+        <v>3.878632486231656</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.791214681969563</v>
+        <v>-4.775305534181704</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.066705283185842</v>
+        <v>1.968153848245228</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.9602433742646979</v>
+        <v>0.9930089786106848</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.559693604846233</v>
+        <v>4.474437873398068</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256369</v>
+        <v>3.6994248275391</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.980840819445049</v>
+        <v>3.875925725389291</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.898140229847414</v>
+        <v>-4.882231082059555</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.021228303192337</v>
+        <v>1.922676868251722</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.8533178263868465</v>
+        <v>0.8860834307328335</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.492831515277158</v>
+        <v>4.407575783828992</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600700999</v>
+        <v>3.68996278598373</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.982269621588284</v>
+        <v>3.877354527532526</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.043158788354662</v>
+        <v>-5.027249640566803</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.964649681932671</v>
+        <v>1.866098246992057</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.708299267879598</v>
+        <v>0.7410648722255849</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.407249182316042</v>
+        <v>4.321993450867877</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687011</v>
+        <v>3.711872614969741</v>
       </c>
       <c r="C2058" t="n">
-        <v>4.082200860846037</v>
+        <v>3.977285766790279</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.16150055413938</v>
+        <v>-5.145591406351521</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.017244214876537</v>
+        <v>1.918692779935923</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.718985306442488</v>
+        <v>0.751750910788475</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.51359204471153</v>
+        <v>4.428336313263364</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790801</v>
+        <v>3.714899237073531</v>
       </c>
       <c r="C2059" t="n">
-        <v>4.079986557971975</v>
+        <v>3.975071463916217</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.212910976460088</v>
+        <v>-5.197001828672229</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.994465743074193</v>
+        <v>1.895914308133579</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.718985306442488</v>
+        <v>0.751750910788475</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.511377741837468</v>
+        <v>4.426122010389302</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437329</v>
+        <v>3.704778134720059</v>
       </c>
       <c r="C2060" t="n">
-        <v>4.079889686046265</v>
+        <v>3.974974591990507</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.29233042766784</v>
+        <v>-5.276421279879981</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.962601090665382</v>
+        <v>1.864049655724767</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.718985306442488</v>
+        <v>0.751750910788475</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.511280869911758</v>
+        <v>4.426025138463592</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298396</v>
+        <v>3.736825137581127</v>
       </c>
       <c r="C2061" t="n">
-        <v>4.079883579604308</v>
+        <v>3.97496848554855</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.387793425585057</v>
+        <v>-5.371884277797198</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.924409785056538</v>
+        <v>1.825858350115924</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.718985306442488</v>
+        <v>0.751750910788475</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.511274763469801</v>
+        <v>4.426019032021635</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960217998</v>
+        <v>3.715393145500729</v>
       </c>
       <c r="C2062" t="n">
-        <v>4.077979976166919</v>
+        <v>3.973064882111161</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.427813423628841</v>
+        <v>-5.411904275840982</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.906498182401635</v>
+        <v>1.807946747461021</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.6789653083987042</v>
+        <v>0.7117309127446911</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.485359161206142</v>
+        <v>4.400103429757976</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353533</v>
+        <v>3.736109598636264</v>
       </c>
       <c r="C2063" t="n">
-        <v>4.083713793914646</v>
+        <v>3.978798699858888</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.483182585761035</v>
+        <v>-5.467273437973176</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.890084335296484</v>
+        <v>1.79153290035587</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.6789653083987042</v>
+        <v>0.7117309127446911</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.491092978953868</v>
+        <v>4.405837247505702</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113277</v>
+        <v>3.736843055396007</v>
       </c>
       <c r="C2064" t="n">
-        <v>4.083252157257578</v>
+        <v>3.97833706320182</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.528620365591862</v>
+        <v>-5.512711217804003</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.871447586707085</v>
+        <v>1.772896151766472</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.6361203177205446</v>
+        <v>0.6688859220665315</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.464924347889904</v>
+        <v>4.37966861644174</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113685</v>
+        <v>3.790292685396416</v>
       </c>
       <c r="C2065" t="n">
-        <v>4.103126550107897</v>
+        <v>3.99821145605214</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.440413531444284</v>
+        <v>-5.424504383656425</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.926604713216436</v>
+        <v>1.828053278275823</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.6361203177205446</v>
+        <v>0.6688859220665315</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.484798740740223</v>
+        <v>4.399543009292059</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016439</v>
+        <v>3.79450702929917</v>
       </c>
       <c r="C2066" t="n">
-        <v>4.086827250632624</v>
+        <v>3.981912156576867</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.264123306838976</v>
+        <v>-5.248214159051117</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.980821503583287</v>
+        <v>1.882270068642673</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.6361203177205446</v>
+        <v>0.6688859220665315</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.468499441264951</v>
+        <v>4.383243709816787</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.79470509330767</v>
+        <v>3.794725278590401</v>
       </c>
       <c r="C2067" t="n">
-        <v>4.08925820009667</v>
+        <v>3.984343106040913</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.080911643705881</v>
+        <v>-5.150014030829008</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.05653711830057</v>
+        <v>1.923981069395562</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.6361203177205446</v>
+        <v>0.6688859220665315</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.470930390728997</v>
+        <v>4.385674659280832</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863548</v>
+        <v>3.776866743146279</v>
       </c>
       <c r="C2068" t="n">
-        <v>4.055049385944559</v>
+        <v>3.950134291888802</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.00919019669203</v>
+        <v>-5.078292583815157</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.051016882954</v>
+        <v>1.918460834048992</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.7078417647343952</v>
+        <v>0.7406073690803822</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.479754444785197</v>
+        <v>4.394498713337032</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394111</v>
+        <v>3.723809890676842</v>
       </c>
       <c r="C2069" t="n">
-        <v>4.001965131865731</v>
+        <v>3.897050037809974</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.138568979331808</v>
+        <v>-5.207671366454935</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.946181115819261</v>
+        <v>1.813625066914252</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.6657399920271918</v>
+        <v>0.6985055963731788</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.401409127082046</v>
+        <v>4.316153395633881</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456728</v>
+        <v>3.715627631739459</v>
       </c>
       <c r="C2070" t="n">
-        <v>4.187163336751087</v>
+        <v>4.082248242695329</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.171585275242553</v>
+        <v>-5.24068766236568</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.118172802340318</v>
+        <v>1.98561675343531</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.5963026153604403</v>
+        <v>0.6290682197064272</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.544944905967351</v>
+        <v>4.459689174519186</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883674</v>
+        <v>3.713782722166405</v>
       </c>
       <c r="C2071" t="n">
-        <v>4.179084562579336</v>
+        <v>4.074169468523579</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.160057639592944</v>
+        <v>-5.229160026716071</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.114705082428411</v>
+        <v>1.982149033523403</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.6553032735618027</v>
+        <v>0.6880688779077897</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.572266526716417</v>
+        <v>4.487010795268253</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236295</v>
+        <v>3.717170884519025</v>
       </c>
       <c r="C2072" t="n">
-        <v>4.182752675101124</v>
+        <v>4.077837581045367</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.257399140935313</v>
+        <v>-5.32650152805844</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.079436594413252</v>
+        <v>1.946880545508244</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.6108830913963144</v>
+        <v>0.6436486957423013</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.549282529938913</v>
+        <v>4.464026798490748</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427681</v>
+        <v>3.705221264710412</v>
       </c>
       <c r="C2073" t="n">
-        <v>4.184003757293962</v>
+        <v>4.079088663238205</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.343255170275279</v>
+        <v>-5.412357557398407</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.046345264870103</v>
+        <v>1.913789215965096</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.5685070221701793</v>
+        <v>0.6012726265161663</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.52510797059607</v>
+        <v>4.439852239147905</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.68994055732922</v>
+        <v>3.691855684893113</v>
       </c>
       <c r="C2074" t="n">
-        <v>4.166422959114464</v>
+        <v>4.061507865058707</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.326446245876008</v>
+        <v>-5.395548632999136</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.035488036450313</v>
+        <v>1.902931987545306</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.5925731178585595</v>
+        <v>0.6253387222045464</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.5219668298296</v>
+        <v>4.436711098381435</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.586030342184975</v>
+        <v>3.798879341849917</v>
       </c>
       <c r="C2075" t="n">
-        <v>4.155064803320291</v>
+        <v>4.176893365190812</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.326446245876008</v>
+        <v>-5.395548632999136</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.035488036450313</v>
+        <v>1.902931987545306</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.5925731178585595</v>
+        <v>0.6253387222045464</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.148128600306659</v>
+        <v>4.16995716217718</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240902.xlsx
+++ b/tame_output/ON/bt/strategyON_20240902.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>57.0%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>91.9%</t>
+          <t>95.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>41.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>78.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>106.1%</t>
+          <t>116.0%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-80.0%</t>
+          <t>-79.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.3%</t>
+          <t>108.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>91.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-51.6%</t>
+          <t>-42.4%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.9%</t>
+          <t>-49.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.5%</t>
+          <t>-75.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.8%</t>
+          <t>90.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-701.1%</t>
+          <t>-685.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>22.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>51.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-8.4%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.9%</t>
+          <t>-32.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>47.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-12.7%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-185.9%</t>
+          <t>-167.4%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-13.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.5%</t>
+          <t>72.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-25.1%</t>
+          <t>-24.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-6.3%</t>
+          <t>-7.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>170.0%</t>
+          <t>589.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-307.7%</t>
+          <t>-301.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-161.5%</t>
+          <t>-166.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>77.5%</t>
+          <t>80.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>50.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>70.2%</t>
+          <t>73.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-29.0%</t>
+          <t>-19.1%</t>
         </is>
       </c>
     </row>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279813</v>
+        <v>3.385382209279812</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511404</v>
+        <v>3.367379938511403</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.36737053999856</v>
+        <v>3.367370539998561</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082124</v>
+        <v>3.299560092082125</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757922</v>
+        <v>3.293490533757923</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.29376671976074</v>
+        <v>3.293766719760741</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296834</v>
+        <v>3.299918119296835</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201485</v>
+        <v>3.295507330201486</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153004</v>
+        <v>3.258791981153005</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537424</v>
+        <v>3.271168579537425</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382189</v>
+        <v>3.27276013138219</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.25147557607462</v>
+        <v>3.251475576074621</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911636</v>
+        <v>3.233800325911637</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213492</v>
+        <v>3.223539378213493</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382324</v>
+        <v>3.235981977382325</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.29913614634705</v>
+        <v>3.299136146347051</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130012</v>
+        <v>3.287377576130013</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178238</v>
+        <v>3.315884374178239</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207808</v>
+        <v>3.305316798207809</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310977</v>
+        <v>3.284619513310978</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309419</v>
+        <v>3.31108639130942</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.3047157169709</v>
+        <v>3.304715716970901</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330518</v>
+        <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191732</v>
+        <v>3.302618194191733</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097815</v>
+        <v>3.341378723097816</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.37443904309411</v>
+        <v>3.374439043094111</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199279</v>
+        <v>3.40596051119928</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969587</v>
+        <v>3.424633354969588</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923079</v>
+        <v>3.41997943392308</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297742</v>
+        <v>3.458100091297743</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131761</v>
+        <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737164</v>
+        <v>3.503515506737165</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341307</v>
+        <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539458</v>
+        <v>3.501052558539459</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937497</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440633</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608599</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410271</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297396</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322541</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158919</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940716</v>
+        <v>3.691571733940717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770576</v>
+        <v>3.676841549770577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615279</v>
+        <v>3.68516138161528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812099</v>
+        <v>3.6848438238121</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646213</v>
+        <v>3.710935533646214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611564</v>
+        <v>3.768951674611565</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955324</v>
+        <v>3.728577929955325</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436225</v>
+        <v>3.766317079436226</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311945</v>
+        <v>3.784684521311946</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.80082935409724</v>
+        <v>3.800829354097241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017767</v>
+        <v>3.789311112017768</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839721</v>
+        <v>3.833252747839722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.85616175162647</v>
+        <v>3.856161751626471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291811</v>
+        <v>3.787330429291812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45389,16 +45389,16 @@
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.813770518289574</v>
+        <v>-6.797918741924919</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.3340702289141193</v>
+        <v>0.3404109394599812</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.3302248797212535</v>
+        <v>-0.314373103356599</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.861799932710944</v>
+        <v>2.871310998529737</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.728805851560255</v>
+        <v>-6.712954075195599</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.3809624368295057</v>
+        <v>0.3873031473753676</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.2452602129919339</v>
+        <v>-0.2294084366272794</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.925685073972195</v>
+        <v>2.935196139790988</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.834395841333359</v>
+        <v>-6.818544064968703</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.2107505113210451</v>
+        <v>0.2170912218669074</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.3508502027650383</v>
+        <v>-0.3349984264003837</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.734355150509113</v>
+        <v>2.743866216327906</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.766161256707932</v>
+        <v>-6.750309480343276</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.2865886870483023</v>
+        <v>0.2929293975941647</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.3324348798925023</v>
+        <v>-0.3165831035278477</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.793948686109721</v>
+        <v>2.803459751928514</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.618221215300332</v>
+        <v>-6.602369438935677</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.229143894972935</v>
+        <v>0.2354846055187974</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.3121139639839447</v>
+        <v>-0.2962621876192902</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.689520427016449</v>
+        <v>2.699031492835242</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409203</v>
       </c>
       <c r="C1911" t="n">
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.565251693046344</v>
+        <v>-6.549399916681688</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.2416177176210521</v>
+        <v>0.2479584281669145</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.2591444417299558</v>
+        <v>-0.2432926653653013</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.712588154115364</v>
+        <v>2.722099219934157</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.399463497086053</v>
+        <v>-6.383611720721397</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.3009723839100755</v>
+        <v>0.3073130944559379</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.2591444417299558</v>
+        <v>-0.2432926653653013</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.705627542020271</v>
+        <v>2.715138607839064</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493419</v>
+        <v>3.782922533493418</v>
       </c>
       <c r="C1913" t="n">
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.366100290607284</v>
+        <v>-6.350248514242629</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.3287800208827258</v>
+        <v>0.3351207314285882</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.2591444417299558</v>
+        <v>-0.2432926653653013</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.720089896401414</v>
+        <v>2.729600962220207</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.257841153484763</v>
+        <v>-6.241989377120107</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.3666157961909295</v>
+        <v>0.3729565067367919</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.2591444417299558</v>
+        <v>-0.2432926653653013</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.714622016860609</v>
+        <v>2.724133082679402</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.134550018667632</v>
+        <v>-6.118698242302976</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.4134303441283591</v>
+        <v>0.419771054674221</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.1358533069128253</v>
+        <v>-0.1200015305481708</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.786094791761464</v>
+        <v>2.795605857580257</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.081853151536341</v>
+        <v>-6.066001375171685</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.4422100692182007</v>
+        <v>0.4485507797640631</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.08315643978153414</v>
+        <v>-0.06730466341687963</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.825413890277564</v>
+        <v>2.834924956096357</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.838087709552896</v>
+        <v>-5.822235933188241</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.5354969543586292</v>
+        <v>0.5418376649044916</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.08315643978153414</v>
+        <v>-0.06730466341687963</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.821194598624615</v>
+        <v>2.830705664443407</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.748312037176424</v>
+        <v>-5.732460260811768</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.573531537229234</v>
+        <v>0.5798722477750964</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.02155699486722412</v>
+        <v>-0.005705218502569609</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.860278579493217</v>
+        <v>2.86978964531201</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.498461643227349</v>
+        <v>-5.482609866862694</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.6662137697925661</v>
+        <v>0.6725544803384285</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.02155699486722412</v>
+        <v>-0.005705218502569609</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.853020654476919</v>
+        <v>2.862531720295712</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.322569550759917</v>
+        <v>-5.306717774395262</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.7401697303001877</v>
+        <v>0.7465104408460497</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.02155699486722412</v>
+        <v>-0.005705218502569609</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.856619777997567</v>
+        <v>2.86613084381636</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.151123087737454</v>
+        <v>-5.135271311372798</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8220758215637267</v>
+        <v>0.8284165321095891</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.149889468155239</v>
+        <v>0.1657412445198935</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.972815161865599</v>
+        <v>2.982326227684392</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.071100800628333</v>
+        <v>-5.055249024263677</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.8531052140236719</v>
+        <v>0.8594459245695343</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.22991175526436</v>
+        <v>0.2457635316290145</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.019849011747369</v>
+        <v>3.029360077566162</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.007465058394398</v>
+        <v>-4.991613282029743</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.883254311971563</v>
+        <v>0.8895950225174254</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.2935474974982945</v>
+        <v>0.309399273862949</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.062725258142047</v>
+        <v>3.072236323960839</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.913767740178003</v>
+        <v>-4.897915963813348</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9019274980419167</v>
+        <v>0.9082682085877791</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.2935474974982945</v>
+        <v>0.309399273862949</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.043919516925842</v>
+        <v>3.053430582744635</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.924270363243292</v>
+        <v>-4.908418586878637</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8994695254406786</v>
+        <v>0.9058102359865408</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.2830448744330056</v>
+        <v>0.2988966507976601</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.039361019711547</v>
+        <v>3.048872085530339</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.852027795072098</v>
+        <v>-4.836176018707442</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9322958665439767</v>
+        <v>0.9386365770898388</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.2830448744330056</v>
+        <v>0.2988966507976601</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.043290333546366</v>
+        <v>3.052801399365159</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.834314108194232</v>
+        <v>-4.818462331829577</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9400599252124628</v>
+        <v>0.946400635758325</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.2862262033299224</v>
+        <v>0.3020779796945769</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.045877714801857</v>
+        <v>3.055388780620649</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.710839836881214</v>
+        <v>-4.694988060516558</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9864477049576634</v>
+        <v>0.9927884155035258</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.2862262033299224</v>
+        <v>0.3020779796945769</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.04287578602185</v>
+        <v>3.052386851840643</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.490819038844204</v>
+        <v>-4.474967262479548</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.076035061183082</v>
+        <v>1.082375771728944</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.4274460483979027</v>
+        <v>0.4432978247625572</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.129186730073252</v>
+        <v>3.138697795892045</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.357951349780926</v>
+        <v>-4.34209957341627</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.145076319610216</v>
+        <v>1.151417030156078</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.4274460483979027</v>
+        <v>0.4432978247625572</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.145080912875076</v>
+        <v>3.154591978693869</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496259</v>
+        <v>3.845047386496258</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.237778266416427</v>
+        <v>-4.221926490051771</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.194291397396318</v>
+        <v>1.20063210794218</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.5476191317624016</v>
+        <v>0.5634709081270561</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.218330607334077</v>
+        <v>3.22784167315287</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576996</v>
+        <v>3.791273551576995</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.10252490508645</v>
+        <v>-4.086673128721794</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.258480844489748</v>
+        <v>1.264821555035611</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.6828724930923787</v>
+        <v>0.6987242694570333</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.309570726693503</v>
+        <v>3.319081792512296</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.162399732444142</v>
+        <v>-4.146547956079487</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.220568404948097</v>
+        <v>1.22690911549396</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.6229976657346866</v>
+        <v>0.6388494420993411</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.259683321680314</v>
+        <v>3.269194387499106</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.042579501533305</v>
+        <v>-4.02672772516865</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.283785666546641</v>
+        <v>1.290126377092503</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.6229976657346866</v>
+        <v>0.6388494420993411</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.274972490914522</v>
+        <v>3.284483556733315</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.045049207995111</v>
+        <v>-4.029197431630456</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.19044198328436</v>
+        <v>1.196782693830222</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.6205279592728805</v>
+        <v>0.6363797356375349</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.18113486635988</v>
+        <v>3.190645932178673</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.113419394319122</v>
+        <v>-4.097567617954466</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.082355770240057</v>
+        <v>1.088696480785919</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.6298036583090955</v>
+        <v>0.6456554346737499</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.105962147266911</v>
+        <v>3.115473213085703</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.225291673945272</v>
+        <v>-4.209439897580617</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.028043567021488</v>
+        <v>1.03438427756735</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.6298036583090955</v>
+        <v>0.6456554346737499</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.096398855898802</v>
+        <v>3.105909921717594</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.855547497605547</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.280811749837862</v>
+        <v>-4.264959973473206</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.142866373356655</v>
+        <v>1.149207083902517</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.6298036583090955</v>
+        <v>0.6456554346737499</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.233429692591004</v>
+        <v>3.242940758409797</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.860114729597334</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.105337490045393</v>
+        <v>-4.089485713680737</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.21762330926543</v>
+        <v>1.223964019811292</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.6298036583090955</v>
+        <v>0.6456554346737499</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.237996924582792</v>
+        <v>3.247507990401584</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.835856758358541</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.097413115460479</v>
+        <v>-4.081561339095823</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.196535087860603</v>
+        <v>1.202875798406465</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.6298036583090955</v>
+        <v>0.6456554346737499</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.213738953343999</v>
+        <v>3.223250019162792</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.764395071759991</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.09113491289063</v>
+        <v>-4.075283136525974</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.127584682289992</v>
+        <v>1.133925392835854</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.6360818608789445</v>
+        <v>0.6519336372435989</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.146044188287358</v>
+        <v>3.155555254106151</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.774567458192124</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.031282293686907</v>
+        <v>-4.015430517322251</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.161698116403614</v>
+        <v>1.168038826949476</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.6360818608789445</v>
+        <v>0.6519336372435989</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.15621657471949</v>
+        <v>3.165727640538283</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.769513728765984</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.945038830660529</v>
+        <v>-3.929187054295873</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.191141772188025</v>
+        <v>1.197482482733887</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.6360818608789445</v>
+        <v>0.6519336372435989</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.151162845293351</v>
+        <v>3.160673911112144</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.761289504210509</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.990345650059509</v>
+        <v>-3.974493873694853</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.164794819872959</v>
+        <v>1.171135530418821</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.5952716978697137</v>
+        <v>0.6111234742343681</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.118452522932338</v>
+        <v>3.127963588751131</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.761841377243611</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.01937875476181</v>
+        <v>-4.003526978397154</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.15373345102514</v>
+        <v>1.160074161571002</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.5952716978697137</v>
+        <v>0.6111234742343681</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.119004395965439</v>
+        <v>3.128515461784232</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809496</v>
+        <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
         <v>2.691114069134977</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.926568273310951</v>
+        <v>-3.910716496946295</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.120130335496849</v>
+        <v>1.126471046042711</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.688082179320573</v>
+        <v>0.7039339556852274</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.103963376727321</v>
+        <v>3.113474442546113</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560423</v>
+        <v>3.748285816560424</v>
       </c>
       <c r="C1947" t="n">
         <v>2.692987545059577</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.970957742640378</v>
+        <v>-3.955105966275723</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.104248023689679</v>
+        <v>1.110588734235541</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.6436927099911454</v>
+        <v>0.6595444863557998</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.079203171054265</v>
+        <v>3.088714236873058</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472733</v>
+        <v>3.721077195472734</v>
       </c>
       <c r="C1948" t="n">
         <v>2.6880632535713</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.087499347745721</v>
+        <v>-4.071647571381066</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.052707090159265</v>
+        <v>1.059047800705127</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.5271511048858026</v>
+        <v>0.543002881250457</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.004353916502782</v>
+        <v>3.013864982321575</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798532</v>
+        <v>3.743047603798534</v>
       </c>
       <c r="C1949" t="n">
         <v>2.693554549401968</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.127423442328293</v>
+        <v>-4.111571665963638</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.042228748156903</v>
+        <v>1.048569458702765</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.5271511048858026</v>
+        <v>0.543002881250457</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.009845212333449</v>
+        <v>3.019356278152242</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498858</v>
+        <v>3.68959784049886</v>
       </c>
       <c r="C1950" t="n">
         <v>2.705051751170507</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.155203840229646</v>
+        <v>-4.13935206386499</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.042613790764901</v>
+        <v>1.048954501310763</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.4993707069844495</v>
+        <v>0.5152224833491039</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.004674175361177</v>
+        <v>3.014185241179969</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705318</v>
+        <v>3.64306962170532</v>
       </c>
       <c r="C1951" t="n">
         <v>2.54340747117116</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.273584512959784</v>
+        <v>-4.257732736595129</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.833617241673499</v>
+        <v>0.8399579522193612</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.4321528548334733</v>
+        <v>0.4480046311981277</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.802699184071244</v>
+        <v>2.812210249890037</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729262</v>
+        <v>3.682716310729264</v>
       </c>
       <c r="C1952" t="n">
         <v>2.663557131890366</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.382198591403116</v>
+        <v>-4.36634681503846</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9103212710153721</v>
+        <v>0.9166619815612345</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.4321528548334733</v>
+        <v>0.4480046311981277</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.92284884479045</v>
+        <v>2.932359910609243</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190763</v>
+        <v>3.733012441190764</v>
       </c>
       <c r="C1953" t="n">
         <v>2.678070157992689</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.346789553154973</v>
+        <v>-4.330937776790317</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9389979124169523</v>
+        <v>0.9453386229628147</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.4321528548334733</v>
+        <v>0.4480046311981277</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.937361870892773</v>
+        <v>2.946872936711566</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.74117406991342</v>
+        <v>3.741174069913422</v>
       </c>
       <c r="C1954" t="n">
         <v>2.675489599335057</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.308405890596822</v>
+        <v>-4.292554114232166</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9517708187825815</v>
+        <v>0.9581115293284437</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4705365173916245</v>
+        <v>0.4863882937562789</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.957811509770032</v>
+        <v>2.967322575588825</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532481</v>
+        <v>3.751147197532482</v>
       </c>
       <c r="C1955" t="n">
         <v>2.672218628180359</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.131289560561656</v>
+        <v>-4.115437784197</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.01934637964195</v>
+        <v>1.025687090187812</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4705365173916245</v>
+        <v>0.4863882937562789</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.954540538615334</v>
+        <v>2.964051604434127</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793897</v>
+        <v>3.741328448793899</v>
       </c>
       <c r="C1956" t="n">
         <v>2.672902019942272</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.176381805395201</v>
+        <v>-4.160530029030546</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.001992873470445</v>
+        <v>1.008333584016307</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.4086404742222347</v>
+        <v>0.4244922505868891</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.918086304475613</v>
+        <v>2.927597370294406</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011229</v>
+        <v>3.750729377011231</v>
       </c>
       <c r="C1957" t="n">
         <v>2.666688995248687</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.997006384156434</v>
+        <v>-3.981154607791778</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.067530017272366</v>
+        <v>1.073870727818228</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.5654172323929534</v>
+        <v>0.5812690087576078</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.005939334684459</v>
+        <v>3.015450400503252</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982223</v>
+        <v>3.716991718982225</v>
       </c>
       <c r="C1958" t="n">
         <v>2.647496450580276</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.042020597677039</v>
+        <v>-4.026168821312384</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.030331787195713</v>
+        <v>1.036672497741576</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.5350683370783488</v>
+        <v>0.5509201134430032</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.968537452827286</v>
+        <v>2.978048518646079</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509532</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.653188012919222</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.309025107949474</v>
+        <v>-4.293173331584819</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9292215454256851</v>
+        <v>0.9355622559715475</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.3407052990354002</v>
+        <v>0.3565570754000546</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.857611192340463</v>
+        <v>2.867122258159255</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760808</v>
+        <v>3.70230945476081</v>
       </c>
       <c r="C1960" t="n">
         <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.410222889386647</v>
+        <v>-4.394371113021991</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8879463547473176</v>
+        <v>0.8942870652931798</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.272296485490081</v>
+        <v>0.2881482618547354</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.815769826109773</v>
+        <v>2.825280891928565</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815453</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.403711922772334</v>
+        <v>-4.387860146407679</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8881507029473594</v>
+        <v>0.8944914134932216</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.272296485490081</v>
+        <v>0.2881482618547354</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.813369787664089</v>
+        <v>2.822880853482882</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
         <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.384673795065037</v>
+        <v>-4.368822018700381</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8922906732385232</v>
+        <v>0.8986313837843856</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.2141128741588865</v>
+        <v>0.2299646505235409</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.774984340073618</v>
+        <v>2.78449540589241</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131246</v>
+        <v>3.731064473131248</v>
       </c>
       <c r="C1963" t="n">
         <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.437189597339858</v>
+        <v>-4.421337820975202</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9905787539627853</v>
+        <v>0.9969194645086477</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.2141128741588865</v>
+        <v>0.2299646505235409</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.894278741707808</v>
+        <v>2.9037898075266</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067859</v>
+        <v>3.722447362067861</v>
       </c>
       <c r="C1964" t="n">
         <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.451056358673775</v>
+        <v>-4.43520458230912</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9858653784153517</v>
+        <v>0.9922060889612141</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.1762549574250635</v>
+        <v>0.1921067337897179</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.872397320653648</v>
+        <v>2.88190838647244</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789116</v>
+        <v>3.787425580789118</v>
       </c>
       <c r="C1965" t="n">
         <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.406252187133846</v>
+        <v>-4.39040041076919</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.00979557742825</v>
+        <v>1.016136287974112</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.1762549574250635</v>
+        <v>0.1921067337897179</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.878405851050573</v>
+        <v>2.887916916869366</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519903</v>
+        <v>3.781501250519905</v>
       </c>
       <c r="C1966" t="n">
         <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.258509216898843</v>
+        <v>-4.242657440534187</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9668429867994501</v>
+        <v>0.9731836973453125</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.3440623146599467</v>
+        <v>0.3599140910246011</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.877040486668703</v>
+        <v>2.886551552487496</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181165</v>
+        <v>3.802245929181167</v>
       </c>
       <c r="C1967" t="n">
         <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.342330438173541</v>
+        <v>-4.326478661808886</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9361081198210517</v>
+        <v>0.9424488303669141</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.3440623146599467</v>
+        <v>0.3599140910246011</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.879834108200184</v>
+        <v>2.889345174018977</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394724</v>
+        <v>3.805608985394726</v>
       </c>
       <c r="C1968" t="n">
         <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.336177732120757</v>
+        <v>-4.320325955756101</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9392315506338238</v>
+        <v>0.9455722611796862</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.350215020712731</v>
+        <v>0.3660667970773854</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.884188080223513</v>
+        <v>2.893699146042306</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890608</v>
+        <v>3.79823979489061</v>
       </c>
       <c r="C1969" t="n">
         <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.352987030271259</v>
+        <v>-4.337135253906603</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9315883081137333</v>
+        <v>0.9379290186595957</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.3334057225622293</v>
+        <v>0.3492574989268837</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.873182978073322</v>
+        <v>2.882694043892115</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798419</v>
+        <v>3.867362636798421</v>
       </c>
       <c r="C1970" t="n">
         <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.290689031495137</v>
+        <v>-4.274837255130481</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.022843061421003</v>
+        <v>1.029183771966866</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.3786999868366714</v>
+        <v>0.3945517632013258</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.966695090434808</v>
+        <v>2.976206156253601</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992185</v>
+        <v>3.848729139992187</v>
       </c>
       <c r="C1971" t="n">
         <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.088898833829979</v>
+        <v>-4.073047057465323</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9058511422011934</v>
+        <v>0.9121918527470556</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.5767181790058258</v>
+        <v>0.5925699553704802</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.887798007450428</v>
+        <v>2.89730907326922</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.84144481785242</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
         <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.139785546516173</v>
+        <v>-4.123933770151518</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9557866894488907</v>
+        <v>0.9621273999947531</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.5258314663196313</v>
+        <v>0.5416832426842857</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.927556212160886</v>
+        <v>2.937067277979679</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319539</v>
+        <v>3.819063300319541</v>
       </c>
       <c r="C1973" t="n">
         <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.053174803866367</v>
+        <v>-4.037323027501711</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.005058722624857</v>
+        <v>1.011399433170719</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.6044571975247895</v>
+        <v>0.6203089738894439</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.989359387000025</v>
+        <v>2.998870452818818</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489379</v>
+        <v>3.83181903248938</v>
       </c>
       <c r="C1974" t="n">
         <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.113384101871651</v>
+        <v>-4.097532325506996</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9795109842474148</v>
+        <v>0.9858516947932772</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.544247899519505</v>
+        <v>0.5600996758841594</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.951769789021526</v>
+        <v>2.961280854840318</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397788</v>
+        <v>3.83641167239779</v>
       </c>
       <c r="C1975" t="n">
         <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.0641974531873</v>
+        <v>-4.048345676822644</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9976772617610838</v>
+        <v>1.004017972306946</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.544247899519505</v>
+        <v>0.5600996758841594</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.950261407061455</v>
+        <v>2.959772472880247</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316243</v>
+        <v>3.833513460316245</v>
       </c>
       <c r="C1976" t="n">
         <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.019824321548731</v>
+        <v>-4.003972545184076</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.015289381851948</v>
+        <v>1.02163009239781</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.5886210311580736</v>
+        <v>0.604472807522728</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.976748153480032</v>
+        <v>2.986259219298824</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105961</v>
+        <v>3.821562117105963</v>
       </c>
       <c r="C1977" t="n">
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.042304672407616</v>
+        <v>-4.026452896042961</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.000691035646984</v>
+        <v>1.007031746192846</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.5886210311580736</v>
+        <v>0.604472807522728</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.971141947618622</v>
+        <v>2.980653013437415</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.83301114819032</v>
+        <v>3.833011148190321</v>
       </c>
       <c r="C1978" t="n">
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.99464894184656</v>
+        <v>-3.978797165481905</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.026135084899211</v>
+        <v>1.032475795445073</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.6362767617191293</v>
+        <v>0.6521285380837837</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.006117142983061</v>
+        <v>3.015628208801853</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569613</v>
+        <v>3.822678210569614</v>
       </c>
       <c r="C1979" t="n">
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.894130783347806</v>
+        <v>-3.87827900698315</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.071234721673438</v>
+        <v>1.0775754322193</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.7367949202178838</v>
+        <v>0.7526466965825382</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.071320411457038</v>
+        <v>3.080831477275831</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557289</v>
+        <v>3.828808877557291</v>
       </c>
       <c r="C1980" t="n">
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.878225453915453</v>
+        <v>-3.862373677550798</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.064351525922251</v>
+        <v>1.070692236468113</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.6576822595086449</v>
+        <v>0.6735340358732993</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.010607487507367</v>
+        <v>3.02011855332616</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932764</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.833387052307055</v>
+        <v>-3.817535275942399</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.086384589176239</v>
+        <v>1.092725299722101</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.6622256924535144</v>
+        <v>0.6780774688181688</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.017431249884917</v>
+        <v>3.02694231570371</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917046</v>
+        <v>3.817932354917048</v>
       </c>
       <c r="C1982" t="n">
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.852885508549063</v>
+        <v>-3.837033732184408</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.082746146310514</v>
+        <v>1.089086856856376</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.6141410511736101</v>
+        <v>0.6299928275382645</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.992741404748053</v>
+        <v>3.002252470566845</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405954</v>
+        <v>3.826684745405956</v>
       </c>
       <c r="C1983" t="n">
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.808682671463163</v>
+        <v>-3.792830895098507</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.106306883672711</v>
+        <v>1.112647594218573</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.6583438882595105</v>
+        <v>0.6741956646241649</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.02514270952743</v>
+        <v>3.034653775346222</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265638</v>
+        <v>3.83819962926564</v>
       </c>
       <c r="C1984" t="n">
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.81624233730021</v>
+        <v>-3.800390560935554</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.10169301780714</v>
+        <v>1.108033728353002</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.7131472922693298</v>
+        <v>0.7289990686339842</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.056434752402569</v>
+        <v>3.065945818221362</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284873</v>
+        <v>3.863895080284875</v>
       </c>
       <c r="C1985" t="n">
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.657950919760938</v>
+        <v>-3.642099143396282</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.216257350005888</v>
+        <v>1.222598060551751</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.7131472922693298</v>
+        <v>0.7289990686339842</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.107682517585609</v>
+        <v>3.117193583404402</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321017</v>
+        <v>3.865338681321019</v>
       </c>
       <c r="C1986" t="n">
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.450308916126462</v>
+        <v>-3.434457139761806</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.297754856053932</v>
+        <v>1.304095566599794</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.920789295903806</v>
+        <v>0.9366410722684604</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.230708424360548</v>
+        <v>3.24021949017934</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475133</v>
+        <v>3.864489842475135</v>
       </c>
       <c r="C1987" t="n">
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.399276823403933</v>
+        <v>-3.383425047039278</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.313115921381213</v>
+        <v>1.319456631927075</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.9718213886263339</v>
+        <v>0.9876731649909883</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.256275908232334</v>
+        <v>3.265786974051127</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404847</v>
+        <v>3.842547360404849</v>
       </c>
       <c r="C1988" t="n">
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.334052642276728</v>
+        <v>-3.318200865912072</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.3563929979248</v>
+        <v>1.362733708470663</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.037045569753539</v>
+        <v>1.052897346118194</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.312597821001363</v>
+        <v>3.322108886820155</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882552</v>
+        <v>3.840061186882553</v>
       </c>
       <c r="C1989" t="n">
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.296625622205594</v>
+        <v>-3.280773845840938</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.367324778252534</v>
+        <v>1.373665488798397</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.042297107782721</v>
+        <v>1.058148884147375</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.311709716118152</v>
+        <v>3.321220781936944</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992654</v>
+        <v>3.845169808992656</v>
       </c>
       <c r="C1990" t="n">
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.316737278240302</v>
+        <v>-3.300885501875646</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.360536908169891</v>
+        <v>1.366877618715753</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.05332445278014</v>
+        <v>1.069176229144795</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.319582915447844</v>
+        <v>3.329093981266636</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636281</v>
+        <v>3.828661445636283</v>
       </c>
       <c r="C1991" t="n">
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.288324015140418</v>
+        <v>-3.272472238775763</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.532459984431055</v>
+        <v>1.538800694976918</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.9943488900337114</v>
+        <v>1.010200666398366</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.444755348821197</v>
+        <v>3.45426641463999</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.81322282095762</v>
+        <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.213541754115406</v>
+        <v>-3.19768997775075</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.682485798058878</v>
+        <v>1.68882650860474</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.069131151058724</v>
+        <v>1.084982927423378</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.609737614654022</v>
+        <v>3.619248680472815</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.81423072799875</v>
+        <v>3.814230727998752</v>
       </c>
       <c r="C1993" t="n">
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.187457669851598</v>
+        <v>-3.171605893486942</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.68462740777826</v>
+        <v>1.690968118324122</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.069131151058724</v>
+        <v>1.084982927423378</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.601445590667881</v>
+        <v>3.610956656486674</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896925</v>
+        <v>3.803397818896927</v>
       </c>
       <c r="C1994" t="n">
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.119631382367325</v>
+        <v>-3.083727980377822</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.709951118355748</v>
+        <v>1.72431247915155</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.233674174192717</v>
+        <v>1.200908569846729</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.698364600132056</v>
+        <v>3.678705237524464</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959852</v>
+        <v>3.796264143959854</v>
       </c>
       <c r="C1995" t="n">
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.110738920974042</v>
+        <v>-3.074835518984538</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.731062508639853</v>
+        <v>1.745423869435655</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.233674174192717</v>
+        <v>1.200908569846729</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.715919005858847</v>
+        <v>3.696259643251255</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945359</v>
+        <v>3.794424941945361</v>
       </c>
       <c r="C1996" t="n">
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.27921503794392</v>
+        <v>-3.243311635954416</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.655527109256486</v>
+        <v>1.669888470052287</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.205726338476136</v>
+        <v>1.172960734130149</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.691005351833483</v>
+        <v>3.671345989225891</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782703</v>
+        <v>3.795574066782705</v>
       </c>
       <c r="C1997" t="n">
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.83295884531448</v>
+        <v>-2.797055443324976</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.815299283496124</v>
+        <v>1.829660644291925</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.111007668806503</v>
+        <v>1.078242064460516</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.615443847219565</v>
+        <v>3.595784484611973</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632631</v>
+        <v>3.784671345632633</v>
       </c>
       <c r="C1998" t="n">
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.810237741631328</v>
+        <v>-2.774334339641824</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.815051747466289</v>
+        <v>1.829413108262091</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.111007668806503</v>
+        <v>1.078242064460516</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.60610786971647</v>
+        <v>3.586448507108877</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777668</v>
+        <v>3.78320569677767</v>
       </c>
       <c r="C1999" t="n">
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.93943955492537</v>
+        <v>-2.903536152935866</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.922277147999841</v>
+        <v>1.936638508795643</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.9818058555124609</v>
+        <v>0.9490402511664737</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.687492907591214</v>
+        <v>3.667833544983621</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644407</v>
+        <v>3.779933725644409</v>
       </c>
       <c r="C2000" t="n">
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.965313953399396</v>
+        <v>-2.929410551409892</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.949005211103877</v>
+        <v>1.963366571899679</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.026717464224202</v>
+        <v>0.9939518598782149</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.751517695311905</v>
+        <v>3.731858332704312</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.76944361979996</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.958259263184222</v>
+        <v>-2.922355861194718</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.948502443179492</v>
+        <v>1.962863803975294</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.033772154439376</v>
+        <v>1.001006550093389</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.752425865430554</v>
+        <v>3.732766502822962</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331109</v>
+        <v>3.766673496331112</v>
       </c>
       <c r="C2002" t="n">
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.931308038857734</v>
+        <v>-2.89540463686823</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.969289086554829</v>
+        <v>1.98365044735063</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.048652500467095</v>
+        <v>1.015886896121108</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.771360226691927</v>
+        <v>3.751700864084335</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784102</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.067261046914051</v>
+        <v>-3.031357644924547</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.099011015477262</v>
+        <v>2.113372376273063</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.048652500467095</v>
+        <v>1.015886896121108</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.955463358836887</v>
+        <v>3.935803996229295</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714421</v>
+        <v>3.743925505714423</v>
       </c>
       <c r="C2004" t="n">
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.089669164718923</v>
+        <v>-3.053765762729419</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.082164463258306</v>
+        <v>2.096525824054108</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.048652500467095</v>
+        <v>1.015886896121108</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.94758005373988</v>
+        <v>3.927920691132288</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155027</v>
+        <v>3.719118627155029</v>
       </c>
       <c r="C2005" t="n">
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.117893400296523</v>
+        <v>-3.081989998307019</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.072928768576904</v>
+        <v>2.087290129372705</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.066629252918404</v>
+        <v>1.033863648572416</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.960420104760303</v>
+        <v>3.94076074215271</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161971</v>
+        <v>3.729452285161973</v>
       </c>
       <c r="C2006" t="n">
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.127334326185053</v>
+        <v>-3.121131655156784</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.125406115943339</v>
+        <v>2.127887184354646</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.189056370461795</v>
+        <v>1.069946235533638</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.090130093008185</v>
+        <v>4.018664012051291</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321628</v>
+        <v>3.71494119332163</v>
       </c>
       <c r="C2007" t="n">
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.179607933520694</v>
+        <v>-3.173405262492426</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.107387767554383</v>
+        <v>2.109868835965691</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.136782763126154</v>
+        <v>1.017672628197997</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.061657023152101</v>
+        <v>3.990190942195206</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347698</v>
+        <v>3.7278981863477</v>
       </c>
       <c r="C2008" t="n">
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.2559379111216</v>
+        <v>-3.249735240093332</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.074967589407796</v>
+        <v>2.077448657819104</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.136782763126154</v>
+        <v>1.017672628197997</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.059768836045876</v>
+        <v>3.988302755088982</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887743</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.349601855799142</v>
+        <v>-3.343399184770873</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.032322241139642</v>
+        <v>2.034803309550949</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.043118818448612</v>
+        <v>0.9240086835204558</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.998390698842213</v>
+        <v>3.926924617885319</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343061</v>
+        <v>3.712897612343063</v>
       </c>
       <c r="C2010" t="n">
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.511170281326397</v>
+        <v>-3.504967610298128</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.966128881138892</v>
+        <v>1.968609949550199</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.9163358946507328</v>
+        <v>0.7972257597225765</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.920754954773638</v>
+        <v>3.849288873816744</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389344</v>
+        <v>3.754596135389345</v>
       </c>
       <c r="C2011" t="n">
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.619470943196516</v>
+        <v>-3.613268272168248</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.935882023256763</v>
+        <v>1.93836309166807</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.9163358946507328</v>
+        <v>0.7972257597225765</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.933828361639557</v>
+        <v>3.862362280682663</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378388</v>
+        <v>3.749882691378389</v>
       </c>
       <c r="C2012" t="n">
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.712618414499883</v>
+        <v>-3.706415743471614</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.890628231518356</v>
+        <v>1.893109299929663</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7935066833682001</v>
+        <v>0.6743965484400437</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.852136031652977</v>
+        <v>3.780669950696083</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006971</v>
+        <v>3.715819895006972</v>
       </c>
       <c r="C2013" t="n">
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.740519201609356</v>
+        <v>-3.734316530581087</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.877991957801569</v>
+        <v>1.880473026212876</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7589097592252653</v>
+        <v>0.6397996242971089</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.829901918294218</v>
+        <v>3.758435837337324</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787383</v>
+        <v>3.684895778787385</v>
       </c>
       <c r="C2014" t="n">
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.86304530431225</v>
+        <v>-3.856842633283981</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.82574596069761</v>
+        <v>1.828227029108918</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6363836565223714</v>
+        <v>0.517273521594215</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.75315070064968</v>
+        <v>3.681684619692787</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585932</v>
+        <v>3.619348081585934</v>
       </c>
       <c r="C2015" t="n">
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.093559800497839</v>
+        <v>-4.08735712946957</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.800246121813878</v>
+        <v>1.802727190225186</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.4058691603367827</v>
+        <v>0.2867590254086263</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.681547962528831</v>
+        <v>3.610081881571937</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814659</v>
+        <v>3.640750087814662</v>
       </c>
       <c r="C2016" t="n">
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.442304885722282</v>
+        <v>-4.436102214694014</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.801059806725948</v>
+        <v>1.803540875137255</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.2971212064178849</v>
+        <v>0.1780110714897285</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.756610909179339</v>
+        <v>3.685144828222445</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237088</v>
+        <v>3.66828900423709</v>
       </c>
       <c r="C2017" t="n">
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.596291303498423</v>
+        <v>-4.590088632470154</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.808445508761132</v>
+        <v>1.810926577172439</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.2971212064178849</v>
+        <v>0.1780110714897285</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.825591178324979</v>
+        <v>3.754125097368085</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423381</v>
+        <v>3.619923016423384</v>
       </c>
       <c r="C2018" t="n">
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.545769399670757</v>
+        <v>-4.539566728642488</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.814705472412319</v>
+        <v>1.817186540823626</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.2971212064178849</v>
+        <v>0.1780110714897285</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.8116423804451</v>
+        <v>3.740176299488206</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609747</v>
+        <v>3.65633273360975</v>
       </c>
       <c r="C2019" t="n">
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.798244553678481</v>
+        <v>-4.792041882650213</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.725585899864643</v>
+        <v>1.72806696827595</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.2971212064178849</v>
+        <v>0.1780110714897285</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.823512869500514</v>
+        <v>3.75204678854362</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973151</v>
+        <v>3.674028535973154</v>
       </c>
       <c r="C2020" t="n">
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.091140310157893</v>
+        <v>-5.084937639129625</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.609638131791822</v>
+        <v>1.612119200203129</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.2971212064178849</v>
+        <v>0.1780110714897285</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.824723404019458</v>
+        <v>3.753257323062564</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.66350945725194</v>
+        <v>3.663509457251942</v>
       </c>
       <c r="C2021" t="n">
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.277804438292701</v>
+        <v>-5.271601767264433</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.53909422276522</v>
+        <v>1.541575291176527</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.270382235593325</v>
+        <v>0.1512721006651686</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.812801763752043</v>
+        <v>3.741335682795149</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916196</v>
+        <v>3.652149152916198</v>
       </c>
       <c r="C2022" t="n">
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.423825125206664</v>
+        <v>-5.417622454178395</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.475763800735824</v>
+        <v>1.478244869147132</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.261299143799468</v>
+        <v>0.1421890088713116</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.802429761411918</v>
+        <v>3.730963680455024</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830322</v>
+        <v>3.667962306830325</v>
       </c>
       <c r="C2023" t="n">
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.515539134316249</v>
+        <v>-5.50933646328798</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.601282253791034</v>
+        <v>1.603763322202342</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.261299143799468</v>
+        <v>0.1421890088713116</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.964633818110962</v>
+        <v>3.893167737154068</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071545</v>
+        <v>3.696539468071547</v>
       </c>
       <c r="C2024" t="n">
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.547190793376219</v>
+        <v>-5.540988122347949</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.583468228130861</v>
+        <v>1.585949296542168</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.2561306865550278</v>
+        <v>0.1370205516268714</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.956379381728112</v>
+        <v>3.884913300771219</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.75004401586814</v>
+        <v>3.750044015868142</v>
       </c>
       <c r="C2025" t="n">
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.629125611645102</v>
+        <v>-5.622922940616832</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.560923718391799</v>
+        <v>1.563404786803106</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.2461959409679476</v>
+        <v>0.1270858060397912</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.960647951944355</v>
+        <v>3.889181870987461</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332685</v>
+        <v>3.783632867332687</v>
       </c>
       <c r="C2026" t="n">
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.731101733893509</v>
+        <v>-5.72489906286524</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.529058907948338</v>
+        <v>1.531539976359646</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.14421981871954</v>
+        <v>0.02510968379138367</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.908387917051213</v>
+        <v>3.83692183609432</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231802</v>
+        <v>3.798296784231805</v>
       </c>
       <c r="C2027" t="n">
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.621095450416288</v>
+        <v>-5.614892779388018</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.565214308583402</v>
+        <v>1.56769537699471</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.1674243906368152</v>
+        <v>0.04831425570865888</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.914463547445754</v>
+        <v>3.84299746648886</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818517</v>
+        <v>3.785563924818518</v>
       </c>
       <c r="C2028" t="n">
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.478035874675362</v>
+        <v>-5.471833203647092</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.626688149601747</v>
+        <v>1.629169218013055</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.1754378172267945</v>
+        <v>0.05632768229863816</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.923521614121716</v>
+        <v>3.852055533164822</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051782</v>
+        <v>3.777237412051785</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.704210948679298</v>
+        <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.176589149203524</v>
+        <v>-5.170386478175255</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.633218864684141</v>
+        <v>1.757008791084326</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.4768845426986318</v>
+        <v>0.3577744077704754</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.990341674298477</v>
+        <v>4.04018445133046</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679618</v>
+        <v>3.812635940679621</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.705182126432009</v>
+        <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.201179393438708</v>
+        <v>-5.194976722410439</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.624353944742778</v>
+        <v>1.748143871142963</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.4768845426986318</v>
+        <v>0.3577744077704754</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.991312852051188</v>
+        <v>4.041155629083171</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474153</v>
+        <v>3.821184182474155</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.706025030811765</v>
+        <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.150141017432188</v>
+        <v>-5.143938346403918</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.645612199525142</v>
+        <v>1.769402125925327</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.4768845426986318</v>
+        <v>0.3577744077704754</v>
       </c>
       <c r="G2031" t="n">
-        <v>3.992155756430944</v>
+        <v>4.041998533462927</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969536</v>
+        <v>3.831734516969539</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.72506312968591</v>
+        <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.109001722565557</v>
+        <v>-5.102799051537287</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.68110601634594</v>
+        <v>1.804895942746124</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.5180238375652626</v>
+        <v>0.3989137026371062</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.035877432225067</v>
+        <v>4.08572020925705</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700472</v>
+        <v>3.825752932700475</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.541247125809845</v>
+        <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.012366810546917</v>
+        <v>-5.006164139518647</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.535943977277331</v>
+        <v>1.659733903677515</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.6146587495839025</v>
+        <v>0.4955486146557462</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.910042375560186</v>
+        <v>3.959885152592169</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077634</v>
+        <v>3.804688961077637</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.544749169883809</v>
+        <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.142947545077759</v>
+        <v>-5.13674487404949</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.487213727538958</v>
+        <v>1.611003653939142</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.48407801505306</v>
+        <v>0.3649678801249037</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.835195978915645</v>
+        <v>3.885038755947627</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833451</v>
+        <v>3.775028860833455</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.529175988959891</v>
+        <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.978451210886798</v>
+        <v>-4.972248539858528</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.537439080291425</v>
+        <v>1.661229006691609</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.6485743492440219</v>
+        <v>0.5294642143158655</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.918320598506305</v>
+        <v>3.968163375538287</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077623</v>
+        <v>3.821030660077627</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.528363699396321</v>
+        <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-5.00582114357123</v>
+        <v>-4.99961847254296</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.525678817654082</v>
+        <v>1.649468744054266</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.6485743492440219</v>
+        <v>0.5294642143158655</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.917508308942734</v>
+        <v>3.967351085974717</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147903</v>
+        <v>3.832307024147907</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.538232478521393</v>
+        <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.016206338461119</v>
+        <v>-5.01000366743285</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.531393518823199</v>
+        <v>1.655183445223383</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.6381891543541326</v>
+        <v>0.5190790194259762</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.921145971133873</v>
+        <v>3.970988748165856</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735275</v>
+        <v>3.834415493735278</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.609069484297819</v>
+        <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.034794497183344</v>
+        <v>-5.028591826155075</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.594795261110734</v>
+        <v>1.718585187510918</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.6196009956319073</v>
+        <v>0.5004908607037508</v>
       </c>
       <c r="G2038" t="n">
-        <v>3.980830081676963</v>
+        <v>4.030672858708946</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496547</v>
+        <v>3.855120535496551</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.605938495116117</v>
+        <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.03509304387938</v>
+        <v>-5.028890372851111</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.591544853250618</v>
+        <v>1.715334779650802</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.6193024489358714</v>
+        <v>0.5001923140077149</v>
       </c>
       <c r="G2039" t="n">
-        <v>3.97751996447764</v>
+        <v>4.027362741509623</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.81564321210885</v>
+        <v>3.815643212108854</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.610469390055508</v>
+        <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.934269910188952</v>
+        <v>-4.928067239160683</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.63640500166618</v>
+        <v>1.760194928066364</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.6317666644202252</v>
+        <v>0.5126565294920687</v>
       </c>
       <c r="G2040" t="n">
-        <v>3.989529388707644</v>
+        <v>4.039372165739627</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121459</v>
+        <v>3.807356168121463</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.610598643534052</v>
+        <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.743488549436545</v>
+        <v>-4.737285878408276</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.712846799445686</v>
+        <v>1.83663672584587</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.8225480251726326</v>
+        <v>0.7034378902444761</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.104127458637632</v>
+        <v>4.153970235669614</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906073</v>
+        <v>3.775233033906076</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.590435489271648</v>
+        <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.636525191587124</v>
+        <v>-4.630322520558854</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.735468988323052</v>
+        <v>1.859258914723236</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.8810126331324341</v>
+        <v>0.7619024982042776</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.119043069151109</v>
+        <v>4.168885846183091</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912978</v>
+        <v>3.785761685912981</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.625402425883707</v>
+        <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.581194603685361</v>
+        <v>-4.574991932657092</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.792568160095815</v>
+        <v>1.916358086495999</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.9363432210341962</v>
+        <v>0.8172330861060397</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.187208358504225</v>
+        <v>4.237051135536207</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539887</v>
+        <v>3.743767956539891</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.619088993785144</v>
+        <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.569140476772398</v>
+        <v>-4.562937805744129</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.791076378762438</v>
+        <v>1.914866305162622</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.948397347947159</v>
+        <v>0.8292872130190025</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.18812740255344</v>
+        <v>4.237970179585423</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811002</v>
+        <v>3.725010844811005</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.62096962396928</v>
+        <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.610295596340619</v>
+        <v>-4.60409292531235</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.776494961119285</v>
+        <v>1.90028488751947</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.9072422283789381</v>
+        <v>0.7881320934507816</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.165314960996644</v>
+        <v>4.215157738028626</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382913</v>
+        <v>3.612322444382916</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.633820649847163</v>
+        <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.542247033649089</v>
+        <v>-4.53604436262082</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.81656541207378</v>
+        <v>1.940355338473964</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.9752907910704679</v>
+        <v>0.8561806561423114</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.218995124489444</v>
+        <v>4.268837901521426</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760309</v>
+        <v>3.646857607760312</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.654023320020757</v>
+        <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.77384742681859</v>
+        <v>-4.767644755790321</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.744127924979574</v>
+        <v>1.867917851379758</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.9752907910704679</v>
+        <v>0.8561806561423114</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.239197794663038</v>
+        <v>4.28904057169502</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781699</v>
+        <v>3.666767386781702</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.654023320020757</v>
+        <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.791919935110202</v>
+        <v>-4.785717264081932</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.736898921662929</v>
+        <v>1.860688848063113</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.9752907910704679</v>
+        <v>0.8561806561423114</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.239197794663038</v>
+        <v>4.28904057169502</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082828</v>
+        <v>3.670068888082831</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.614275233614224</v>
+        <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.967026767686647</v>
+        <v>-4.960824096658378</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.627108102225817</v>
+        <v>1.750898028626002</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.9752907910704679</v>
+        <v>0.8561806561423114</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.199449708256505</v>
+        <v>4.249292485288487</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.74559333394358</v>
+        <v>3.745593333943583</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.621297852611164</v>
+        <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.935740747146192</v>
+        <v>-4.929538076117923</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.646645129438939</v>
+        <v>1.770435055839124</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.006576811610923</v>
+        <v>0.8874666766827668</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.225243939577718</v>
+        <v>4.2750867166097</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677817</v>
+        <v>3.73059065867782</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.720468852184068</v>
+        <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.782715355032908</v>
+        <v>-4.707967159492662</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.807026285857158</v>
+        <v>1.958234422062132</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.159602203724207</v>
+        <v>1.109037593308027</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.416230174418593</v>
+        <v>4.507200266157761</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073876</v>
+        <v>3.741298518073879</v>
       </c>
       <c r="C2052" t="n">
-        <v>3.907935077092361</v>
+        <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.811022668906178</v>
+        <v>-4.736274473365932</v>
       </c>
       <c r="E2052" t="n">
-        <v>1.983169585216142</v>
+        <v>2.134377721421116</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.159602203724207</v>
+        <v>1.109037593308027</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.603696399326886</v>
+        <v>4.694666491066053</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903161</v>
+        <v>3.699135800903164</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.877338028446443</v>
+        <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.9776158940197</v>
+        <v>-4.902867698479454</v>
       </c>
       <c r="E2053" t="n">
-        <v>1.885935246524816</v>
+        <v>2.03714338272979</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.9930089786106848</v>
+        <v>0.9424443681945049</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.473143415612855</v>
+        <v>4.564113507352022</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568375</v>
+        <v>3.708202704568379</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.881014431108161</v>
+        <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.8045515146374</v>
+        <v>-4.729803319097154</v>
       </c>
       <c r="E2054" t="n">
-        <v>1.958837400939454</v>
+        <v>2.110045537144428</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.9930089786106848</v>
+        <v>0.9424443681945049</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.476819818274572</v>
+        <v>4.56778991001374</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682197</v>
+        <v>3.7406015866822</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.878632486231656</v>
+        <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.775305534181704</v>
+        <v>-4.700557338641458</v>
       </c>
       <c r="E2055" t="n">
-        <v>1.968153848245228</v>
+        <v>2.119361984450201</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.9930089786106848</v>
+        <v>0.9424443681945049</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.474437873398068</v>
+        <v>4.565407965137235</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.6994248275391</v>
+        <v>3.699424827539104</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.875925725389291</v>
+        <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.882231082059555</v>
+        <v>-4.807482886519309</v>
       </c>
       <c r="E2056" t="n">
-        <v>1.922676868251722</v>
+        <v>2.073885004456696</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.8860834307328335</v>
+        <v>0.8355188203166536</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.407575783828992</v>
+        <v>4.498545875568159</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.68996278598373</v>
+        <v>3.689962785983734</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.877354527532526</v>
+        <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-5.027249640566803</v>
+        <v>-4.952501445026558</v>
       </c>
       <c r="E2057" t="n">
-        <v>1.866098246992057</v>
+        <v>2.017306383197031</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.7410648722255849</v>
+        <v>0.690500261809405</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.321993450867877</v>
+        <v>4.412963542607044</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969741</v>
+        <v>3.711872614969745</v>
       </c>
       <c r="C2058" t="n">
-        <v>3.977285766790279</v>
+        <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.145591406351521</v>
+        <v>-5.070843210811275</v>
       </c>
       <c r="E2058" t="n">
-        <v>1.918692779935923</v>
+        <v>2.069900916140897</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.751750910788475</v>
+        <v>0.7011863003722951</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.428336313263364</v>
+        <v>4.519306405002531</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073531</v>
+        <v>3.714899237073535</v>
       </c>
       <c r="C2059" t="n">
-        <v>3.975071463916217</v>
+        <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.197001828672229</v>
+        <v>-5.122253633131983</v>
       </c>
       <c r="E2059" t="n">
-        <v>1.895914308133579</v>
+        <v>2.047122444338552</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.751750910788475</v>
+        <v>0.7011863003722951</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.426122010389302</v>
+        <v>4.51709210212847</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720059</v>
+        <v>3.704778134720063</v>
       </c>
       <c r="C2060" t="n">
-        <v>3.974974591990507</v>
+        <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.276421279879981</v>
+        <v>-5.201673084339735</v>
       </c>
       <c r="E2060" t="n">
-        <v>1.864049655724767</v>
+        <v>2.015257791929741</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.751750910788475</v>
+        <v>0.7011863003722951</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.426025138463592</v>
+        <v>4.51699523020276</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736825137581127</v>
+        <v>3.73682513758113</v>
       </c>
       <c r="C2061" t="n">
-        <v>3.97496848554855</v>
+        <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.371884277797198</v>
+        <v>-5.297136082256952</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.825858350115924</v>
+        <v>1.977066486320898</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.751750910788475</v>
+        <v>0.7011863003722951</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.426019032021635</v>
+        <v>4.516989123760803</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715393145500729</v>
+        <v>3.715393145500732</v>
       </c>
       <c r="C2062" t="n">
-        <v>3.973064882111161</v>
+        <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.411904275840982</v>
+        <v>-5.337156080300736</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.807946747461021</v>
+        <v>1.959154883665995</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.7117309127446911</v>
+        <v>0.6611663023285113</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.400103429757976</v>
+        <v>4.491073521497143</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736109598636264</v>
+        <v>3.736109598636268</v>
       </c>
       <c r="C2063" t="n">
-        <v>3.978798699858888</v>
+        <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.467273437973176</v>
+        <v>-5.39252524243293</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.79153290035587</v>
+        <v>1.942741036560844</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.7117309127446911</v>
+        <v>0.6611663023285113</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.405837247505702</v>
+        <v>4.49680733924487</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736843055396007</v>
+        <v>3.736843055396011</v>
       </c>
       <c r="C2064" t="n">
-        <v>3.97833706320182</v>
+        <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.512711217804003</v>
+        <v>-5.437963022263757</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.772896151766472</v>
+        <v>1.924104287971446</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.6688859220665315</v>
+        <v>0.6183213116503516</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.37966861644174</v>
+        <v>4.470638708180907</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790292685396416</v>
+        <v>3.79029268539642</v>
       </c>
       <c r="C2065" t="n">
-        <v>3.99821145605214</v>
+        <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.424504383656425</v>
+        <v>-5.349756188116179</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.828053278275823</v>
+        <v>1.979261414480796</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.6688859220665315</v>
+        <v>0.6183213116503516</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.399543009292059</v>
+        <v>4.490513101031226</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.79450702929917</v>
+        <v>3.794507029299173</v>
       </c>
       <c r="C2066" t="n">
-        <v>3.981912156576867</v>
+        <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.248214159051117</v>
+        <v>-5.173465963510871</v>
       </c>
       <c r="E2066" t="n">
-        <v>1.882270068642673</v>
+        <v>2.033478204847647</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.6688859220665315</v>
+        <v>0.6183213116503516</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.383243709816787</v>
+        <v>4.474213801555954</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794725278590401</v>
+        <v>3.794725278590405</v>
       </c>
       <c r="C2067" t="n">
-        <v>3.984343106040913</v>
+        <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-5.150014030829008</v>
+        <v>-4.990254300377776</v>
       </c>
       <c r="E2067" t="n">
-        <v>1.923981069395562</v>
+        <v>2.109193819564931</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.6688859220665315</v>
+        <v>0.6183213116503516</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.385674659280832</v>
+        <v>4.476644751019999</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776866743146279</v>
+        <v>3.776866743146282</v>
       </c>
       <c r="C2068" t="n">
-        <v>3.950134291888802</v>
+        <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-5.078292583815157</v>
+        <v>-4.918532853363925</v>
       </c>
       <c r="E2068" t="n">
-        <v>1.918460834048992</v>
+        <v>2.10367358421836</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.7406073690803822</v>
+        <v>0.6900427586642023</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.394498713337032</v>
+        <v>4.485468805076199</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723809890676842</v>
+        <v>3.723809890676845</v>
       </c>
       <c r="C2069" t="n">
-        <v>3.897050037809974</v>
+        <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.207671366454935</v>
+        <v>-5.047911636003703</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.813625066914252</v>
+        <v>1.998837817083621</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.6985055963731788</v>
+        <v>0.6479409859569989</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.316153395633881</v>
+        <v>4.407123487373049</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715627631739459</v>
+        <v>3.715627631739462</v>
       </c>
       <c r="C2070" t="n">
-        <v>4.082248242695329</v>
+        <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.24068766236568</v>
+        <v>-5.080927931914448</v>
       </c>
       <c r="E2070" t="n">
-        <v>1.98561675343531</v>
+        <v>2.170829503604679</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.6290682197064272</v>
+        <v>0.5785036092902474</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.459689174519186</v>
+        <v>4.550659266258354</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713782722166405</v>
+        <v>3.713782722166409</v>
       </c>
       <c r="C2071" t="n">
-        <v>4.074169468523579</v>
+        <v>4.195478326512454</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.229160026716071</v>
+        <v>-5.069400296264839</v>
       </c>
       <c r="E2071" t="n">
-        <v>1.982149033523403</v>
+        <v>2.167361783692771</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.6880688779077897</v>
+        <v>0.6375042674916098</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.487010795268253</v>
+        <v>4.577980887007421</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717170884519025</v>
+        <v>3.717170884519029</v>
       </c>
       <c r="C2072" t="n">
-        <v>4.077837581045367</v>
+        <v>4.199146439034243</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.32650152805844</v>
+        <v>-5.166741797607208</v>
       </c>
       <c r="E2072" t="n">
-        <v>1.946880545508244</v>
+        <v>2.132093295677612</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.6436486957423013</v>
+        <v>0.5930840853261214</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.464026798490748</v>
+        <v>4.554996890229916</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705221264710412</v>
+        <v>3.705221264710415</v>
       </c>
       <c r="C2073" t="n">
-        <v>4.079088663238205</v>
+        <v>4.200397521227081</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.412357557398407</v>
+        <v>-5.252597826947174</v>
       </c>
       <c r="E2073" t="n">
-        <v>1.913789215965096</v>
+        <v>2.099001966134464</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.6012726265161663</v>
+        <v>0.5507080160999864</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.439852239147905</v>
+        <v>4.530822330887073</v>
       </c>
     </row>
     <row r="2074">
@@ -49250,19 +49250,19 @@
         <v>3.691855684893113</v>
       </c>
       <c r="C2074" t="n">
-        <v>4.061507865058707</v>
+        <v>4.182816723047583</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.395548632999136</v>
+        <v>-5.235788902547903</v>
       </c>
       <c r="E2074" t="n">
-        <v>1.902931987545306</v>
+        <v>2.088144737714674</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.6253387222045464</v>
+        <v>0.5747741117883666</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.436711098381435</v>
+        <v>4.527681190120603</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.798879341849917</v>
+        <v>3.850670066106093</v>
       </c>
       <c r="C2075" t="n">
-        <v>4.176893365190812</v>
+        <v>4.276067444493082</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.395548632999136</v>
+        <v>-5.235788902547903</v>
       </c>
       <c r="E2075" t="n">
-        <v>1.902931987545306</v>
+        <v>2.088144737714674</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.6253387222045464</v>
+        <v>0.5747741117883666</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.16995716217718</v>
+        <v>4.26913124147945</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240902.xlsx
+++ b/tame_output/ON/bt/strategyON_20240902.xlsx
@@ -600,12 +600,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>58.5%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>95.6%</t>
+          <t>94.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>41.0%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>78.1%</t>
+          <t>77.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>116.0%</t>
+          <t>113.3%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.5%</t>
+          <t>-79.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.8%</t>
+          <t>108.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.6%</t>
+          <t>123.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.9%</t>
+          <t>91.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,12 +977,12 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-616.8%</t>
+          <t>-604.1%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-42.4%</t>
+          <t>-44.6%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.3%</t>
+          <t>-47.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.9%</t>
+          <t>-75.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.2%</t>
+          <t>89.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.0%</t>
+          <t>426.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-685.2%</t>
+          <t>-676.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>51.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-247.1%</t>
+          <t>-242.0%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.1%</t>
+          <t>-34.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-167.4%</t>
+          <t>-157.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-13.6%</t>
+          <t>-13.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.20</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.7%</t>
+          <t>-25.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-7.0%</t>
+          <t>-6.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>589.4%</t>
+          <t>589.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-301.3%</t>
+          <t>-307.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-166.5%</t>
+          <t>-165.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>80.3%</t>
+          <t>92.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.9%</t>
+          <t>-22.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>73.4%</t>
+          <t>82.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-19.1%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386093</v>
+        <v>3.376932391386092</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998561</v>
+        <v>3.367370539998559</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082125</v>
+        <v>3.299560092082123</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757923</v>
+        <v>3.293490533757921</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760741</v>
+        <v>3.293766719760739</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706668</v>
+        <v>3.298730590706667</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,16 +43980,16 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296835</v>
+        <v>3.299918119296834</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.6545912063460799</v>
+        <v>-0.5282982604764979</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.859135855474547</v>
+        <v>2.90965303382238</v>
       </c>
       <c r="F1845" t="n">
         <v>1.533058604805237</v>
@@ -44003,16 +44003,16 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201486</v>
+        <v>3.295507330201485</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.6432019696912785</v>
+        <v>-0.5169090238216965</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.861516346255708</v>
+        <v>2.91203352460354</v>
       </c>
       <c r="F1846" t="n">
         <v>1.544447841460039</v>
@@ -44026,16 +44026,16 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153005</v>
+        <v>3.258791981153004</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.8956798641106845</v>
+        <v>-0.7693869182411024</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.758452079993008</v>
+        <v>2.808969258340841</v>
       </c>
       <c r="F1847" t="n">
         <v>1.291969947040633</v>
@@ -44055,10 +44055,10 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.185811530716116</v>
+        <v>-1.059518584846534</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.642265629949757</v>
+        <v>2.69278280829759</v>
       </c>
       <c r="F1848" t="n">
         <v>1.316051741780813</v>
@@ -44072,16 +44072,16 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.27276013138219</v>
+        <v>3.272760131382189</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.393815589069193</v>
+        <v>-1.267522643199611</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.563956151162452</v>
+        <v>2.614473329510285</v>
       </c>
       <c r="F1849" t="n">
         <v>1.316051741780813</v>
@@ -44095,16 +44095,16 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074621</v>
+        <v>3.25147557607462</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.455994000230163</v>
+        <v>-1.329701054360581</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.534166243036052</v>
+        <v>2.584683421383885</v>
       </c>
       <c r="F1850" t="n">
         <v>1.253873330619843</v>
@@ -44124,10 +44124,10 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.822062727374816</v>
+        <v>-1.695769781505234</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.38082305148464</v>
+        <v>2.431340229832473</v>
       </c>
       <c r="F1851" t="n">
         <v>0.88780460347519</v>
@@ -44141,16 +44141,16 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213493</v>
+        <v>3.223539378213494</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.0305535088265</v>
+        <v>-1.904260562956918</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.317765028642734</v>
+        <v>2.368282206990567</v>
       </c>
       <c r="F1852" t="n">
         <v>0.6793138220235055</v>
@@ -44164,16 +44164,16 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416042</v>
+        <v>3.231167537416043</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.277754693591722</v>
+        <v>-2.15146174772214</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.226983305145214</v>
+        <v>2.277500483493047</v>
       </c>
       <c r="F1853" t="n">
         <v>0.699467175522318</v>
@@ -44187,16 +44187,16 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382325</v>
+        <v>3.235981977382326</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.770139721615819</v>
+        <v>-2.643846775746237</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.031135685979308</v>
+        <v>2.081652864327141</v>
       </c>
       <c r="F1854" t="n">
         <v>0.2070821474982212</v>
@@ -44210,16 +44210,16 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495495</v>
+        <v>3.278199702495496</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.155320112545891</v>
+        <v>-3.02902716667631</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.875606068420142</v>
+        <v>1.926123246767975</v>
       </c>
       <c r="F1855" t="n">
         <v>0.2070821474982212</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.405190792560473</v>
+        <v>-3.278897846690891</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.777426919868925</v>
+        <v>1.827944098216758</v>
       </c>
       <c r="F1856" t="n">
         <v>0.2433448673286845</v>
@@ -44256,16 +44256,16 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130013</v>
+        <v>3.287377576130014</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.611702569447494</v>
+        <v>-3.485409623577913</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.690928267770375</v>
+        <v>1.741445446118208</v>
       </c>
       <c r="F1857" t="n">
         <v>0.036833090441663</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.931046644527996</v>
+        <v>-3.804753698658414</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.564963564438434</v>
+        <v>1.615480742786267</v>
       </c>
       <c r="F1858" t="n">
         <v>0.036833090441663</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.31725647580377</v>
+        <v>-4.190963529934189</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.396812519395528</v>
+        <v>1.447329697743361</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.05393984927578033</v>
@@ -44325,16 +44325,16 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310978</v>
+        <v>3.284619513310977</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.551950469936322</v>
+        <v>-4.425657524066741</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.291219696744598</v>
+        <v>1.341736875092431</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.04760358204652515</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.887613117166775</v>
+        <v>-4.761320171297194</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.155535229508382</v>
+        <v>1.206052407856215</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.11553456753543</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.964057447369647</v>
+        <v>-4.837764501500065</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.131445057661475</v>
+        <v>1.181962236009308</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.03508905844176807</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.329184830008393</v>
+        <v>-5.202891884138812</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.9846486196118076</v>
+        <v>1.035165797959641</v>
       </c>
       <c r="F1863" t="n">
         <v>-0.3313998427407806</v>
@@ -44417,16 +44417,16 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330519</v>
+        <v>3.300815818330518</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.737773607189072</v>
+        <v>-5.61148066131949</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.8199746527542953</v>
+        <v>0.8704918311021284</v>
       </c>
       <c r="F1864" t="n">
         <v>-0.739988619921459</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.851534019211937</v>
+        <v>-5.725241073342355</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.7696559204166098</v>
+        <v>0.8201730987644429</v>
       </c>
       <c r="F1865" t="n">
         <v>-0.739988619921459</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.267925893498934</v>
+        <v>-6.141632947629352</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.6010932213106881</v>
+        <v>0.6516103996585212</v>
       </c>
       <c r="F1866" t="n">
         <v>-0.739988619921459</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.629099523315922</v>
+        <v>-6.50280657744634</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.4668824600525721</v>
+        <v>0.5173996384004051</v>
       </c>
       <c r="F1867" t="n">
         <v>-0.739988619921459</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.972358042958941</v>
+        <v>-6.846065097089359</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.3256786173410595</v>
+        <v>0.3761957956888931</v>
       </c>
       <c r="F1868" t="n">
         <v>-0.739988619921459</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.020560860201285</v>
+        <v>-6.894267914331703</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.3048024104991232</v>
+        <v>0.3553195888469562</v>
       </c>
       <c r="F1869" t="n">
         <v>-0.739988619921459</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.187369520175647</v>
+        <v>-7.061076574306065</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.2418579224385864</v>
+        <v>0.2923751007864195</v>
       </c>
       <c r="F1870" t="n">
         <v>-0.7822719436345955</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.37408922848495</v>
+        <v>-7.247796282615368</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.1631437345804621</v>
+        <v>0.2136609129282956</v>
       </c>
       <c r="F1871" t="n">
         <v>-0.7822719436345955</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.757090617227581</v>
+        <v>-7.630797671357999</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.009841077761825634</v>
+        <v>0.06035825610965873</v>
       </c>
       <c r="F1872" t="n">
         <v>-0.7822719436345955</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.761577062428969</v>
+        <v>-7.635284116559387</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.01061801565270049</v>
+        <v>0.06113519400053358</v>
       </c>
       <c r="F1873" t="n">
         <v>-0.7867583888359841</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.121107384932973</v>
+        <v>-7.994814439063389</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.1278438100508503</v>
+        <v>-0.07732663170301679</v>
       </c>
       <c r="F1874" t="n">
         <v>-0.7867583888359841</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.171456448387195</v>
+        <v>-8.04516350251761</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.1400674154753618</v>
+        <v>-0.08955023712752785</v>
       </c>
       <c r="F1875" t="n">
         <v>-0.8371074522902062</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.269075725808591</v>
+        <v>-8.142782779939006</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1760733758221513</v>
+        <v>-0.1255561974743173</v>
       </c>
       <c r="F1876" t="n">
         <v>-0.9347267297116029</v>
@@ -44722,10 +44722,10 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.32314722531695</v>
+        <v>-8.196854279447365</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1948084193039228</v>
+        <v>-0.1442912409560888</v>
       </c>
       <c r="F1877" t="n">
         <v>-0.9887982292199623</v>
@@ -44745,10 +44745,10 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.527405400646813</v>
+        <v>-8.401112454777229</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.2709984923172257</v>
+        <v>-0.2204813139693917</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.116437173833951</v>
@@ -44768,10 +44768,10 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.561058239155287</v>
+        <v>-8.434765293285702</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.279977073236179</v>
+        <v>-0.2294598948883451</v>
       </c>
       <c r="F1879" t="n">
         <v>-1.216850541750989</v>
@@ -44791,10 +44791,10 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.700144353774144</v>
+        <v>-8.573851407904559</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.3202398175903007</v>
+        <v>-0.2697226392424668</v>
       </c>
       <c r="F1880" t="n">
         <v>-1.355936656369845</v>
@@ -44814,10 +44814,10 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.875268771160687</v>
+        <v>-8.748975825291103</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.3757343637974015</v>
+        <v>-0.3252171854495676</v>
       </c>
       <c r="F1881" t="n">
         <v>-1.531061073756389</v>
@@ -44837,10 +44837,10 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.109720865175177</v>
+        <v>-8.983427919305592</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.4767343663047932</v>
+        <v>-0.4262171879569592</v>
       </c>
       <c r="F1882" t="n">
         <v>-1.531061073756389</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.214095596201624</v>
+        <v>-9.087802650332039</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.5251564494893479</v>
+        <v>-0.4746392711415139</v>
       </c>
       <c r="F1883" t="n">
         <v>-1.635435804782835</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.376609061900208</v>
+        <v>-9.250316116030623</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5890460459302256</v>
+        <v>-0.5385288675823916</v>
       </c>
       <c r="F1884" t="n">
         <v>-1.733069235201522</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.502645855268497</v>
+        <v>-9.376352909398912</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.6367670346484267</v>
+        <v>-0.5862498563005927</v>
       </c>
       <c r="F1885" t="n">
         <v>-1.707817612391779</v>
@@ -44929,10 +44929,10 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.445574083372566</v>
+        <v>-9.319281137502982</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.6099479902036533</v>
+        <v>-0.5594308118558193</v>
       </c>
       <c r="F1886" t="n">
         <v>-1.707817612391779</v>
@@ -44952,10 +44952,10 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.587245925096687</v>
+        <v>-9.460952979227102</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6680919537920431</v>
+        <v>-0.6175747754442091</v>
       </c>
       <c r="F1887" t="n">
         <v>-1.707817612391779</v>
@@ -44975,10 +44975,10 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.537655080671852</v>
+        <v>-9.411362134802268</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.6332022058572373</v>
+        <v>-0.5826850275094033</v>
       </c>
       <c r="F1888" t="n">
         <v>-1.658226767966946</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770577</v>
+        <v>3.676841549770578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.388736746199996</v>
+        <v>-9.262443800330411</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5866860057151775</v>
+        <v>-0.5361688273673435</v>
       </c>
       <c r="F1889" t="n">
         <v>-1.626977177231772</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68516138161528</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.162891593480584</v>
+        <v>-9.036598647611001</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4867688715912042</v>
+        <v>-0.4362516932433711</v>
       </c>
       <c r="F1890" t="n">
         <v>-1.585050501644609</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848438238121</v>
+        <v>3.684843823812101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.038312937142992</v>
+        <v>-8.912019991273409</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.4357982645001086</v>
+        <v>-0.3852810861522751</v>
       </c>
       <c r="F1891" t="n">
         <v>-1.585050501644609</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646214</v>
+        <v>3.710935533646215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.013276255574482</v>
+        <v>-8.886983309704899</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.4231498177105966</v>
+        <v>-0.3726326393627635</v>
       </c>
       <c r="F1892" t="n">
         <v>-1.559721414093873</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611565</v>
+        <v>3.768951674611567</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.941143080286601</v>
+        <v>-8.814850134417018</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3885628433568078</v>
+        <v>-0.3380456650089747</v>
       </c>
       <c r="F1893" t="n">
         <v>-1.559721414093873</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955325</v>
+        <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.869776687676953</v>
+        <v>-8.743483741807371</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.369753548706814</v>
+        <v>-0.3192363703589809</v>
       </c>
       <c r="F1894" t="n">
         <v>-1.488355021484225</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232409</v>
+        <v>3.747702660232412</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.776317653691729</v>
+        <v>-8.650024707822146</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.3422534164256317</v>
+        <v>-0.2917362380777986</v>
       </c>
       <c r="F1895" t="n">
         <v>-1.488355021484225</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436226</v>
+        <v>3.766317079436228</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.765664472138297</v>
+        <v>-8.639371526268715</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.3398267043036332</v>
+        <v>-0.2893095259557996</v>
       </c>
       <c r="F1896" t="n">
         <v>-1.488355021484225</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311946</v>
+        <v>3.784684521311948</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.667757433461807</v>
+        <v>-8.541464487592224</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.3009642038064975</v>
+        <v>-0.2504470254586644</v>
       </c>
       <c r="F1897" t="n">
         <v>-1.420369271623669</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097241</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.643803892485849</v>
+        <v>-8.517510946616266</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2907142812706209</v>
+        <v>-0.2401971029227874</v>
       </c>
       <c r="F1898" t="n">
         <v>-1.396415730647711</v>
@@ -45222,16 +45222,16 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017768</v>
+        <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.379743954163052</v>
+        <v>-8.253451008293469</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1983506221032543</v>
+        <v>-0.1478334437554212</v>
       </c>
       <c r="F1899" t="n">
         <v>-1.132355792324915</v>
@@ -45251,10 +45251,10 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.672664330658214</v>
+        <v>-7.546371384788631</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.08169419363838015</v>
+        <v>0.1322113719862132</v>
       </c>
       <c r="F1900" t="n">
         <v>-1.132355792324915</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388726</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.632480032292023</v>
+        <v>-7.50618708642244</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.09811153687269769</v>
+        <v>0.1486287152205308</v>
       </c>
       <c r="F1901" t="n">
         <v>-1.092171493958724</v>
@@ -45297,10 +45297,10 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.469080161352661</v>
+        <v>-7.342787215483078</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.1628383064691996</v>
+        <v>0.2133554848170327</v>
       </c>
       <c r="F1902" t="n">
         <v>-0.9287716230193617</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.787330429291813</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.235598939123062</v>
+        <v>-7.109305993253479</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.2641552241988916</v>
+        <v>0.3146724025467247</v>
       </c>
       <c r="F1903" t="n">
         <v>-0.6952904007897631</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785786</v>
+        <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.085932548115547</v>
+        <v>-6.959639602245964</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.3211295702889383</v>
+        <v>0.3716467486367714</v>
       </c>
       <c r="F1904" t="n">
         <v>-0.6023869095472272</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390427</v>
+        <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.953657074484661</v>
+        <v>-6.827364128615078</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.2753005457484474</v>
+        <v>0.325817724096281</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.4701114359163405</v>
@@ -45383,16 +45383,16 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105952</v>
+        <v>3.784718794105954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.797918741924919</v>
+        <v>-6.671625796055336</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.3404109394599812</v>
+        <v>0.3909281178078143</v>
       </c>
       <c r="F1906" t="n">
         <v>-0.314373103356599</v>
@@ -45406,16 +45406,16 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960985</v>
+        <v>3.753882571960987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.712954075195599</v>
+        <v>-6.586661129326016</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.3873031473753676</v>
+        <v>0.4378203257232012</v>
       </c>
       <c r="F1907" t="n">
         <v>-0.2294084366272794</v>
@@ -45429,16 +45429,16 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607643</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.818544064968703</v>
+        <v>-6.692251119099121</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.2170912218669074</v>
+        <v>0.2676084002147405</v>
       </c>
       <c r="F1908" t="n">
         <v>-0.3349984264003837</v>
@@ -45452,16 +45452,16 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987899</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.750309480343276</v>
+        <v>-6.624016534473693</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.2929293975941647</v>
+        <v>0.3434465759419978</v>
       </c>
       <c r="F1909" t="n">
         <v>-0.3165831035278477</v>
@@ -45475,16 +45475,16 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710811</v>
+        <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.602369438935677</v>
+        <v>-6.476076493066094</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.2354846055187974</v>
+        <v>0.2860017838666304</v>
       </c>
       <c r="F1910" t="n">
         <v>-0.2962621876192902</v>
@@ -45498,16 +45498,16 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409203</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.549399916681688</v>
+        <v>-6.423106970812105</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.2479584281669145</v>
+        <v>0.2984756065147476</v>
       </c>
       <c r="F1911" t="n">
         <v>-0.2432926653653013</v>
@@ -45521,16 +45521,16 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.729969716098109</v>
       </c>
       <c r="C1912" t="n">
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.383611720721397</v>
+        <v>-6.257318774851814</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.3073130944559379</v>
+        <v>0.357830272803771</v>
       </c>
       <c r="F1912" t="n">
         <v>-0.2432926653653013</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493418</v>
+        <v>3.78292253349342</v>
       </c>
       <c r="C1913" t="n">
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.350248514242629</v>
+        <v>-6.223955568373046</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.3351207314285882</v>
+        <v>0.3856379097764213</v>
       </c>
       <c r="F1913" t="n">
         <v>-0.2432926653653013</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722816</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.241989377120107</v>
+        <v>-6.115696431250524</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.3729565067367919</v>
+        <v>0.423473685084625</v>
       </c>
       <c r="F1914" t="n">
         <v>-0.2432926653653013</v>
@@ -45590,16 +45590,16 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792045</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.118698242302976</v>
+        <v>-5.992405296433393</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.419771054674221</v>
+        <v>0.4702882330220546</v>
       </c>
       <c r="F1915" t="n">
         <v>-0.1200015305481708</v>
@@ -45613,16 +45613,16 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919905</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.066001375171685</v>
+        <v>-5.939708429302102</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.4485507797640631</v>
+        <v>0.4990679581118962</v>
       </c>
       <c r="F1916" t="n">
         <v>-0.06730466341687963</v>
@@ -45636,16 +45636,16 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318089</v>
+        <v>3.748328408318092</v>
       </c>
       <c r="C1917" t="n">
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.822235933188241</v>
+        <v>-5.695942987318658</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.5418376649044916</v>
+        <v>0.5923548432523247</v>
       </c>
       <c r="F1917" t="n">
         <v>-0.06730466341687963</v>
@@ -45659,16 +45659,16 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057522</v>
+        <v>3.824311233057524</v>
       </c>
       <c r="C1918" t="n">
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.732460260811768</v>
+        <v>-5.606167314942185</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.5798722477750964</v>
+        <v>0.6303894261229295</v>
       </c>
       <c r="F1918" t="n">
         <v>-0.005705218502569609</v>
@@ -45682,16 +45682,16 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.82635497427918</v>
+        <v>3.826354974279183</v>
       </c>
       <c r="C1919" t="n">
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.482609866862694</v>
+        <v>-5.356316920993111</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.6725544803384285</v>
+        <v>0.7230716586862616</v>
       </c>
       <c r="F1919" t="n">
         <v>-0.005705218502569609</v>
@@ -45705,16 +45705,16 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011493</v>
+        <v>3.835957987011495</v>
       </c>
       <c r="C1920" t="n">
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.306717774395262</v>
+        <v>-5.180424828525679</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.7465104408460497</v>
+        <v>0.7970276191938832</v>
       </c>
       <c r="F1920" t="n">
         <v>-0.005705218502569609</v>
@@ -45728,16 +45728,16 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392981</v>
+        <v>3.780933911392983</v>
       </c>
       <c r="C1921" t="n">
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.135271311372798</v>
+        <v>-5.008978365503215</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8284165321095891</v>
+        <v>0.8789337104574222</v>
       </c>
       <c r="F1921" t="n">
         <v>0.1657412445198935</v>
@@ -45751,16 +45751,16 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632775</v>
+        <v>3.773765222632777</v>
       </c>
       <c r="C1922" t="n">
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.055249024263677</v>
+        <v>-4.928956078394094</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.8594459245695343</v>
+        <v>0.9099631029173674</v>
       </c>
       <c r="F1922" t="n">
         <v>0.2457635316290145</v>
@@ -45774,16 +45774,16 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883069</v>
+        <v>3.76461787988307</v>
       </c>
       <c r="C1923" t="n">
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.991613282029743</v>
+        <v>-4.86532033616016</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.8895950225174254</v>
+        <v>0.9401122008652585</v>
       </c>
       <c r="F1923" t="n">
         <v>0.309399273862949</v>
@@ -45797,16 +45797,16 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074777</v>
+        <v>3.798814771074779</v>
       </c>
       <c r="C1924" t="n">
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.897915963813348</v>
+        <v>-4.771623017943765</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9082682085877791</v>
+        <v>0.9587853869356122</v>
       </c>
       <c r="F1924" t="n">
         <v>0.309399273862949</v>
@@ -45820,16 +45820,16 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242289</v>
+        <v>3.79769488424229</v>
       </c>
       <c r="C1925" t="n">
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.908418586878637</v>
+        <v>-4.782125641009054</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9058102359865408</v>
+        <v>0.9563274143343741</v>
       </c>
       <c r="F1925" t="n">
         <v>0.2988966507976601</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367679</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.836176018707442</v>
+        <v>-4.709883072837859</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9386365770898388</v>
+        <v>0.9891537554376721</v>
       </c>
       <c r="F1926" t="n">
         <v>0.2988966507976601</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879959</v>
+        <v>3.822326997879961</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.818462331829577</v>
+        <v>-4.692169385959994</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.946400635758325</v>
+        <v>0.9969178141061583</v>
       </c>
       <c r="F1927" t="n">
         <v>0.3020779796945769</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502332</v>
+        <v>3.848616626502333</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.694988060516558</v>
+        <v>-4.568695114646975</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9927884155035258</v>
+        <v>1.043305593851359</v>
       </c>
       <c r="F1928" t="n">
         <v>0.3020779796945769</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675933</v>
+        <v>3.818668951675935</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.474967262479548</v>
+        <v>-4.348674316609965</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.082375771728944</v>
+        <v>1.132892950076777</v>
       </c>
       <c r="F1929" t="n">
         <v>0.4432978247625572</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539945</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.34209957341627</v>
+        <v>-4.215806627546687</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.151417030156078</v>
+        <v>1.201934208503912</v>
       </c>
       <c r="F1930" t="n">
         <v>0.4432978247625572</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496258</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.221926490051771</v>
+        <v>-4.095633544182189</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.20063210794218</v>
+        <v>1.251149286290013</v>
       </c>
       <c r="F1931" t="n">
         <v>0.5634709081270561</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576995</v>
+        <v>3.791273551576997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.086673128721794</v>
+        <v>-3.960380182852211</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.264821555035611</v>
+        <v>1.315338733383444</v>
       </c>
       <c r="F1932" t="n">
         <v>0.6987242694570333</v>
@@ -46010,10 +46010,10 @@
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.146547956079487</v>
+        <v>-4.020255010209904</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.22690911549396</v>
+        <v>1.277426293841793</v>
       </c>
       <c r="F1933" t="n">
         <v>0.6388494420993411</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674511</v>
+        <v>3.762647477674513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.02672772516865</v>
+        <v>-3.900434779299066</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.290126377092503</v>
+        <v>1.340643555440336</v>
       </c>
       <c r="F1934" t="n">
         <v>0.6388494420993411</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430689</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.029197431630456</v>
+        <v>-3.902904485760872</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.196782693830222</v>
+        <v>1.247299872178055</v>
       </c>
       <c r="F1935" t="n">
         <v>0.6363797356375349</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003596</v>
+        <v>3.743220196003599</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.097567617954466</v>
+        <v>-3.971274672084882</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.088696480785919</v>
+        <v>1.139213659133753</v>
       </c>
       <c r="F1936" t="n">
         <v>0.6456554346737499</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508365</v>
+        <v>3.714179139508367</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.209439897580617</v>
+        <v>-4.083146951711033</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.03438427756735</v>
+        <v>1.084901455915184</v>
       </c>
       <c r="F1937" t="n">
         <v>0.6456554346737499</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417699</v>
+        <v>3.710906731417702</v>
       </c>
       <c r="C1938" t="n">
         <v>2.855547497605547</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.264959973473206</v>
+        <v>-4.138667027603622</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.149207083902517</v>
+        <v>1.19972426225035</v>
       </c>
       <c r="F1938" t="n">
         <v>0.6456554346737499</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205894</v>
+        <v>3.746042526205896</v>
       </c>
       <c r="C1939" t="n">
         <v>2.860114729597334</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.089485713680737</v>
+        <v>-3.963192767811153</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.223964019811292</v>
+        <v>1.274481198159126</v>
       </c>
       <c r="F1939" t="n">
         <v>0.6456554346737499</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225438</v>
+        <v>3.76502432322544</v>
       </c>
       <c r="C1940" t="n">
         <v>2.835856758358541</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.081561339095823</v>
+        <v>-3.955268393226239</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.202875798406465</v>
+        <v>1.253392976754299</v>
       </c>
       <c r="F1940" t="n">
         <v>0.6456554346737499</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111292</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.764395071759991</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.075283136525974</v>
+        <v>-3.94899019065639</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.133925392835854</v>
+        <v>1.184442571183688</v>
       </c>
       <c r="F1941" t="n">
         <v>0.6519336372435989</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264161</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.774567458192124</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.015430517322251</v>
+        <v>-3.889137571452667</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.168038826949476</v>
+        <v>1.21855600529731</v>
       </c>
       <c r="F1942" t="n">
         <v>0.6519336372435989</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742297</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.769513728765984</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.929187054295873</v>
+        <v>-3.802894108426289</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.197482482733887</v>
+        <v>1.247999661081721</v>
       </c>
       <c r="F1943" t="n">
         <v>0.6519336372435989</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316044</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.761289504210509</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.974493873694853</v>
+        <v>-3.848200927825269</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.171135530418821</v>
+        <v>1.221652708766654</v>
       </c>
       <c r="F1944" t="n">
         <v>0.6111234742343681</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803189</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.761841377243611</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.003526978397154</v>
+        <v>-3.877234032527571</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.160074161571002</v>
+        <v>1.210591339918835</v>
       </c>
       <c r="F1945" t="n">
         <v>0.6111234742343681</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809497</v>
+        <v>3.733390600809498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.691114069134977</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.910716496946295</v>
+        <v>-3.784423551076712</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.126471046042711</v>
+        <v>1.176988224390545</v>
       </c>
       <c r="F1946" t="n">
         <v>0.7039339556852274</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560424</v>
+        <v>3.748285816560425</v>
       </c>
       <c r="C1947" t="n">
         <v>2.692987545059577</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.955105966275723</v>
+        <v>-3.828813020406139</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.110588734235541</v>
+        <v>1.161105912583374</v>
       </c>
       <c r="F1947" t="n">
         <v>0.6595444863557998</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472734</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.6880632535713</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.071647571381066</v>
+        <v>-3.945354625511482</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.059047800705127</v>
+        <v>1.10956497905296</v>
       </c>
       <c r="F1948" t="n">
         <v>0.543002881250457</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798534</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.693554549401968</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.111571665963638</v>
+        <v>-3.985278720094054</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.048569458702765</v>
+        <v>1.099086637050599</v>
       </c>
       <c r="F1949" t="n">
         <v>0.543002881250457</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.68959784049886</v>
+        <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
         <v>2.705051751170507</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.13935206386499</v>
+        <v>-4.013059117995406</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.048954501310763</v>
+        <v>1.099471679658597</v>
       </c>
       <c r="F1950" t="n">
         <v>0.5152224833491039</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.64306962170532</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.54340747117116</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.257732736595129</v>
+        <v>-4.131439790725545</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8399579522193612</v>
+        <v>0.8904751305671947</v>
       </c>
       <c r="F1951" t="n">
         <v>0.4480046311981277</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729264</v>
+        <v>3.682716310729266</v>
       </c>
       <c r="C1952" t="n">
         <v>2.663557131890366</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.36634681503846</v>
+        <v>-4.240053869168876</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9166619815612345</v>
+        <v>0.967179159909068</v>
       </c>
       <c r="F1952" t="n">
         <v>0.4480046311981277</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190764</v>
+        <v>3.733012441190765</v>
       </c>
       <c r="C1953" t="n">
         <v>2.678070157992689</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.330937776790317</v>
+        <v>-4.204644830920733</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9453386229628147</v>
+        <v>0.9958558013106482</v>
       </c>
       <c r="F1953" t="n">
         <v>0.4480046311981277</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913422</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.675489599335057</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.292554114232166</v>
+        <v>-4.166261168362582</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9581115293284437</v>
+        <v>1.008628707676277</v>
       </c>
       <c r="F1954" t="n">
         <v>0.4863882937562789</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532482</v>
+        <v>3.751147197532484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.672218628180359</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.115437784197</v>
+        <v>-3.989144838327416</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.025687090187812</v>
+        <v>1.076204268535646</v>
       </c>
       <c r="F1955" t="n">
         <v>0.4863882937562789</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793899</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.672902019942272</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.160530029030546</v>
+        <v>-4.034237083160962</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.008333584016307</v>
+        <v>1.05885076236414</v>
       </c>
       <c r="F1956" t="n">
         <v>0.4244922505868891</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011231</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.666688995248687</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.981154607791778</v>
+        <v>-3.854861661922194</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.073870727818228</v>
+        <v>1.124387906166062</v>
       </c>
       <c r="F1957" t="n">
         <v>0.5812690087576078</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982225</v>
+        <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
         <v>2.647496450580276</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.026168821312384</v>
+        <v>-3.8998758754428</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.036672497741576</v>
+        <v>1.087189676089409</v>
       </c>
       <c r="F1958" t="n">
         <v>0.5509201134430032</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509534</v>
+        <v>3.737026608509535</v>
       </c>
       <c r="C1959" t="n">
         <v>2.653188012919222</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.293173331584819</v>
+        <v>-4.166880385715236</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9355622559715475</v>
+        <v>0.9860794343193806</v>
       </c>
       <c r="F1959" t="n">
         <v>0.3565570754000546</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
         <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.394371113021991</v>
+        <v>-4.268078167152408</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8942870652931798</v>
+        <v>0.9448042436410131</v>
       </c>
       <c r="F1960" t="n">
         <v>0.2881482618547354</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.387860146407679</v>
+        <v>-4.261567200538096</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8944914134932216</v>
+        <v>0.9450085918410549</v>
       </c>
       <c r="F1961" t="n">
         <v>0.2881482618547354</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.368822018700381</v>
+        <v>-4.242529072830798</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8986313837843856</v>
+        <v>0.9491485621322187</v>
       </c>
       <c r="F1962" t="n">
         <v>0.2299646505235409</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131248</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
         <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.421337820975202</v>
+        <v>-4.295044875105619</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9969194645086477</v>
+        <v>1.047436642856481</v>
       </c>
       <c r="F1963" t="n">
         <v>0.2299646505235409</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067861</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.43520458230912</v>
+        <v>-4.308911636439537</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9922060889612141</v>
+        <v>1.042723267309047</v>
       </c>
       <c r="F1964" t="n">
         <v>0.1921067337897179</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789118</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.39040041076919</v>
+        <v>-4.264107464899607</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.016136287974112</v>
+        <v>1.066653466321945</v>
       </c>
       <c r="F1965" t="n">
         <v>0.1921067337897179</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519905</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.242657440534187</v>
+        <v>-4.116364494664604</v>
       </c>
       <c r="E1966" t="n">
-        <v>0.9731836973453125</v>
+        <v>1.023700875693146</v>
       </c>
       <c r="F1966" t="n">
         <v>0.3599140910246011</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181167</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.326478661808886</v>
+        <v>-4.200185715939303</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9424488303669141</v>
+        <v>0.9929660087147472</v>
       </c>
       <c r="F1967" t="n">
         <v>0.3599140910246011</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394726</v>
+        <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
         <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.320325955756101</v>
+        <v>-4.194033009886518</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9455722611796862</v>
+        <v>0.9960894395275193</v>
       </c>
       <c r="F1968" t="n">
         <v>0.3660667970773854</v>
@@ -46832,16 +46832,16 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.79823979489061</v>
+        <v>3.798239794890612</v>
       </c>
       <c r="C1969" t="n">
         <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.337135253906603</v>
+        <v>-4.21084230803702</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9379290186595957</v>
+        <v>0.9884461970074288</v>
       </c>
       <c r="F1969" t="n">
         <v>0.3492574989268837</v>
@@ -46855,16 +46855,16 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798421</v>
+        <v>3.867362636798425</v>
       </c>
       <c r="C1970" t="n">
         <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.274837255130481</v>
+        <v>-4.148544309260898</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.029183771966866</v>
+        <v>1.079700950314699</v>
       </c>
       <c r="F1970" t="n">
         <v>0.3945517632013258</v>
@@ -46878,16 +46878,16 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992187</v>
+        <v>3.84872913999219</v>
       </c>
       <c r="C1971" t="n">
         <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.073047057465323</v>
+        <v>-3.94675411159574</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9121918527470556</v>
+        <v>0.9627090310948889</v>
       </c>
       <c r="F1971" t="n">
         <v>0.5925699553704802</v>
@@ -46901,16 +46901,16 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
         <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.123933770151518</v>
+        <v>-3.997640824281935</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9621273999947531</v>
+        <v>1.012644578342586</v>
       </c>
       <c r="F1972" t="n">
         <v>0.5416832426842857</v>
@@ -46924,16 +46924,16 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319541</v>
+        <v>3.819063300319542</v>
       </c>
       <c r="C1973" t="n">
         <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.037323027501711</v>
+        <v>-3.911030081632128</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.011399433170719</v>
+        <v>1.061916611518553</v>
       </c>
       <c r="F1973" t="n">
         <v>0.6203089738894439</v>
@@ -46947,16 +46947,16 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.83181903248938</v>
+        <v>3.831819032489382</v>
       </c>
       <c r="C1974" t="n">
         <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.097532325506996</v>
+        <v>-3.971239379637412</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9858516947932772</v>
+        <v>1.036368873141111</v>
       </c>
       <c r="F1974" t="n">
         <v>0.5600996758841594</v>
@@ -46970,16 +46970,16 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.83641167239779</v>
+        <v>3.836411672397792</v>
       </c>
       <c r="C1975" t="n">
         <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.048345676822644</v>
+        <v>-3.922052730953061</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.004017972306946</v>
+        <v>1.05453515065478</v>
       </c>
       <c r="F1975" t="n">
         <v>0.5600996758841594</v>
@@ -46993,16 +46993,16 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316245</v>
+        <v>3.833513460316246</v>
       </c>
       <c r="C1976" t="n">
         <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.003972545184076</v>
+        <v>-3.877679599314492</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.02163009239781</v>
+        <v>1.072147270745643</v>
       </c>
       <c r="F1976" t="n">
         <v>0.604472807522728</v>
@@ -47016,16 +47016,16 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105963</v>
+        <v>3.821562117105965</v>
       </c>
       <c r="C1977" t="n">
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.026452896042961</v>
+        <v>-3.900159950173377</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.007031746192846</v>
+        <v>1.05754892454068</v>
       </c>
       <c r="F1977" t="n">
         <v>0.604472807522728</v>
@@ -47039,16 +47039,16 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190321</v>
+        <v>3.833011148190323</v>
       </c>
       <c r="C1978" t="n">
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.978797165481905</v>
+        <v>-3.852504219612321</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.032475795445073</v>
+        <v>1.082992973792907</v>
       </c>
       <c r="F1978" t="n">
         <v>0.6521285380837837</v>
@@ -47062,16 +47062,16 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569614</v>
+        <v>3.822678210569616</v>
       </c>
       <c r="C1979" t="n">
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.87827900698315</v>
+        <v>-3.751986061113566</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.0775754322193</v>
+        <v>1.128092610567134</v>
       </c>
       <c r="F1979" t="n">
         <v>0.7526466965825382</v>
@@ -47085,16 +47085,16 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557291</v>
+        <v>3.828808877557292</v>
       </c>
       <c r="C1980" t="n">
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.862373677550798</v>
+        <v>-3.736080731681214</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.070692236468113</v>
+        <v>1.121209414815947</v>
       </c>
       <c r="F1980" t="n">
         <v>0.6735340358732993</v>
@@ -47108,16 +47108,16 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932767</v>
       </c>
       <c r="C1981" t="n">
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.817535275942399</v>
+        <v>-3.691242330072816</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.092725299722101</v>
+        <v>1.143242478069935</v>
       </c>
       <c r="F1981" t="n">
         <v>0.6780774688181688</v>
@@ -47131,16 +47131,16 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917048</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.837033732184408</v>
+        <v>-3.710740786314824</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.089086856856376</v>
+        <v>1.139604035204209</v>
       </c>
       <c r="F1982" t="n">
         <v>0.6299928275382645</v>
@@ -47154,16 +47154,16 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405956</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.792830895098507</v>
+        <v>-3.666537949228923</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.112647594218573</v>
+        <v>1.163164772566407</v>
       </c>
       <c r="F1983" t="n">
         <v>0.6741956646241649</v>
@@ -47177,16 +47177,16 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.83819962926564</v>
+        <v>3.838199629265643</v>
       </c>
       <c r="C1984" t="n">
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.800390560935554</v>
+        <v>-3.67409761506597</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.108033728353002</v>
+        <v>1.158550906700835</v>
       </c>
       <c r="F1984" t="n">
         <v>0.7289990686339842</v>
@@ -47200,16 +47200,16 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284875</v>
+        <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.642099143396282</v>
+        <v>-3.515806197526698</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.222598060551751</v>
+        <v>1.273115238899584</v>
       </c>
       <c r="F1985" t="n">
         <v>0.7289990686339842</v>
@@ -47223,16 +47223,16 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321019</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.434457139761806</v>
+        <v>-3.308164193892222</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.304095566599794</v>
+        <v>1.354612744947628</v>
       </c>
       <c r="F1986" t="n">
         <v>0.9366410722684604</v>
@@ -47246,16 +47246,16 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475135</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.383425047039278</v>
+        <v>-3.257132101169694</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.319456631927075</v>
+        <v>1.369973810274909</v>
       </c>
       <c r="F1987" t="n">
         <v>0.9876731649909883</v>
@@ -47269,16 +47269,16 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404849</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.318200865912072</v>
+        <v>-3.191907920042488</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.362733708470663</v>
+        <v>1.413250886818496</v>
       </c>
       <c r="F1988" t="n">
         <v>1.052897346118194</v>
@@ -47292,16 +47292,16 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882553</v>
+        <v>3.840061186882555</v>
       </c>
       <c r="C1989" t="n">
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.280773845840938</v>
+        <v>-3.154480899971354</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.373665488798397</v>
+        <v>1.42418266714623</v>
       </c>
       <c r="F1989" t="n">
         <v>1.058148884147375</v>
@@ -47315,16 +47315,16 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992656</v>
+        <v>3.845169808992658</v>
       </c>
       <c r="C1990" t="n">
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.300885501875646</v>
+        <v>-3.174592556006063</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.366877618715753</v>
+        <v>1.417394797063587</v>
       </c>
       <c r="F1990" t="n">
         <v>1.069176229144795</v>
@@ -47338,16 +47338,16 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636283</v>
+        <v>3.828661445636285</v>
       </c>
       <c r="C1991" t="n">
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.272472238775763</v>
+        <v>-3.146179292906179</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.538800694976918</v>
+        <v>1.589317873324751</v>
       </c>
       <c r="F1991" t="n">
         <v>1.010200666398366</v>
@@ -47361,16 +47361,16 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.813222820957623</v>
       </c>
       <c r="C1992" t="n">
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.19768997775075</v>
+        <v>-3.071397031881166</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.68882650860474</v>
+        <v>1.739343686952574</v>
       </c>
       <c r="F1992" t="n">
         <v>1.084982927423378</v>
@@ -47384,16 +47384,16 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998752</v>
+        <v>3.814230727998754</v>
       </c>
       <c r="C1993" t="n">
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.171605893486942</v>
+        <v>-3.045312947617358</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.690968118324122</v>
+        <v>1.741485296671956</v>
       </c>
       <c r="F1993" t="n">
         <v>1.084982927423378</v>
@@ -47407,16 +47407,16 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896927</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-3.083727980377822</v>
+        <v>-2.957435034508238</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.72431247915155</v>
+        <v>1.774829657499383</v>
       </c>
       <c r="F1994" t="n">
         <v>1.200908569846729</v>
@@ -47430,16 +47430,16 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959854</v>
+        <v>3.796264143959856</v>
       </c>
       <c r="C1995" t="n">
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-3.074835518984538</v>
+        <v>-2.948542573114954</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.745423869435655</v>
+        <v>1.795941047783488</v>
       </c>
       <c r="F1995" t="n">
         <v>1.200908569846729</v>
@@ -47453,16 +47453,16 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945361</v>
+        <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.243311635954416</v>
+        <v>-3.117018690084832</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.669888470052287</v>
+        <v>1.720405648400121</v>
       </c>
       <c r="F1996" t="n">
         <v>1.172960734130149</v>
@@ -47476,16 +47476,16 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782705</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.797055443324976</v>
+        <v>-2.670762497455392</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.829660644291925</v>
+        <v>1.880177822639759</v>
       </c>
       <c r="F1997" t="n">
         <v>1.078242064460516</v>
@@ -47499,16 +47499,16 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632633</v>
+        <v>3.784671345632635</v>
       </c>
       <c r="C1998" t="n">
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.774334339641824</v>
+        <v>-2.64804139377224</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.829413108262091</v>
+        <v>1.879930286609924</v>
       </c>
       <c r="F1998" t="n">
         <v>1.078242064460516</v>
@@ -47522,16 +47522,16 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.78320569677767</v>
+        <v>3.783205696777672</v>
       </c>
       <c r="C1999" t="n">
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.903536152935866</v>
+        <v>-2.777243207066282</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.936638508795643</v>
+        <v>1.987155687143476</v>
       </c>
       <c r="F1999" t="n">
         <v>0.9490402511664737</v>
@@ -47545,16 +47545,16 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644409</v>
+        <v>3.779933725644411</v>
       </c>
       <c r="C2000" t="n">
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.929410551409892</v>
+        <v>-2.803117605540308</v>
       </c>
       <c r="E2000" t="n">
-        <v>1.963366571899679</v>
+        <v>2.013883750247513</v>
       </c>
       <c r="F2000" t="n">
         <v>0.9939518598782149</v>
@@ -47568,16 +47568,16 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.769443619799963</v>
       </c>
       <c r="C2001" t="n">
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.922355861194718</v>
+        <v>-2.796062915325134</v>
       </c>
       <c r="E2001" t="n">
-        <v>1.962863803975294</v>
+        <v>2.013380982323127</v>
       </c>
       <c r="F2001" t="n">
         <v>1.001006550093389</v>
@@ -47591,16 +47591,16 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331112</v>
+        <v>3.766673496331115</v>
       </c>
       <c r="C2002" t="n">
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.89540463686823</v>
+        <v>-2.769111690998646</v>
       </c>
       <c r="E2002" t="n">
-        <v>1.98365044735063</v>
+        <v>2.034167625698464</v>
       </c>
       <c r="F2002" t="n">
         <v>1.015886896121108</v>
@@ -47614,16 +47614,16 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-3.031357644924547</v>
+        <v>-2.905064699054963</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.113372376273063</v>
+        <v>2.163889554620897</v>
       </c>
       <c r="F2003" t="n">
         <v>1.015886896121108</v>
@@ -47637,16 +47637,16 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714423</v>
+        <v>3.743925505714424</v>
       </c>
       <c r="C2004" t="n">
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-3.053765762729419</v>
+        <v>-2.927472816859835</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.096525824054108</v>
+        <v>2.147043002401942</v>
       </c>
       <c r="F2004" t="n">
         <v>1.015886896121108</v>
@@ -47660,16 +47660,16 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155029</v>
+        <v>3.71911862715503</v>
       </c>
       <c r="C2005" t="n">
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-3.081989998307019</v>
+        <v>-2.955697052437435</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.087290129372705</v>
+        <v>2.137807307720539</v>
       </c>
       <c r="F2005" t="n">
         <v>1.033863648572416</v>
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161973</v>
+        <v>3.729452285161974</v>
       </c>
       <c r="C2006" t="n">
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-3.121131655156784</v>
+        <v>-2.965137978325965</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.127887184354646</v>
+        <v>2.190284655086974</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.069946235533638</v>
+        <v>1.156290766115808</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.018664012051291</v>
+        <v>4.070470730400592</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.71494119332163</v>
+        <v>3.714941193321631</v>
       </c>
       <c r="C2007" t="n">
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.173405262492426</v>
+        <v>-3.017411585661606</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.109868835965691</v>
+        <v>2.172266306698019</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.017672628197997</v>
+        <v>1.104017158780167</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.990190942195206</v>
+        <v>4.041997660544508</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.7278981863477</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.249735240093332</v>
+        <v>-3.093741563262512</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.077448657819104</v>
+        <v>2.139846128551431</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.017672628197997</v>
+        <v>1.104017158780167</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.988302755088982</v>
+        <v>4.040109473438283</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887746</v>
       </c>
       <c r="C2009" t="n">
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.343399184770873</v>
+        <v>-3.187405507940054</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.034803309550949</v>
+        <v>2.097200780283277</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.9240086835204558</v>
+        <v>1.010353214102625</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.926924617885319</v>
+        <v>3.978731336234621</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343063</v>
+        <v>3.712897612343065</v>
       </c>
       <c r="C2010" t="n">
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.504967610298128</v>
+        <v>-3.348973933467309</v>
       </c>
       <c r="E2010" t="n">
-        <v>1.968609949550199</v>
+        <v>2.031007420282527</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.7972257597225765</v>
+        <v>0.8835702903047459</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.849288873816744</v>
+        <v>3.901095592166046</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389345</v>
+        <v>3.754596135389347</v>
       </c>
       <c r="C2011" t="n">
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.613268272168248</v>
+        <v>-3.457274595337428</v>
       </c>
       <c r="E2011" t="n">
-        <v>1.93836309166807</v>
+        <v>2.000760562400398</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.7972257597225765</v>
+        <v>0.8835702903047459</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.862362280682663</v>
+        <v>3.914168999031965</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378389</v>
+        <v>3.74988269137839</v>
       </c>
       <c r="C2012" t="n">
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.706415743471614</v>
+        <v>-3.550422066640795</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.893109299929663</v>
+        <v>1.955506770661991</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.6743965484400437</v>
+        <v>0.7607410790222131</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.780669950696083</v>
+        <v>3.832476669045385</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006972</v>
+        <v>3.715819895006974</v>
       </c>
       <c r="C2013" t="n">
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.734316530581087</v>
+        <v>-3.578322853750268</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.880473026212876</v>
+        <v>1.942870496945204</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.6397996242971089</v>
+        <v>0.7261441548792783</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.758435837337324</v>
+        <v>3.810242555686626</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787385</v>
+        <v>3.684895778787386</v>
       </c>
       <c r="C2014" t="n">
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.856842633283981</v>
+        <v>-3.700848956453162</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.828227029108918</v>
+        <v>1.890624499841245</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.517273521594215</v>
+        <v>0.6036180521763844</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.681684619692787</v>
+        <v>3.733491338042088</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585934</v>
+        <v>3.619348081585937</v>
       </c>
       <c r="C2015" t="n">
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-4.08735712946957</v>
+        <v>-3.931363452638751</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.802727190225186</v>
+        <v>1.865124660957513</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.2867590254086263</v>
+        <v>0.3731035559907957</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.610081881571937</v>
+        <v>3.661888599921239</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814662</v>
+        <v>3.640750087814664</v>
       </c>
       <c r="C2016" t="n">
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.436102214694014</v>
+        <v>-4.280108537863194</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.803540875137255</v>
+        <v>1.865938345869583</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.1780110714897285</v>
+        <v>0.2643556020718979</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.685144828222445</v>
+        <v>3.736951546571747</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.66828900423709</v>
+        <v>3.668289004237093</v>
       </c>
       <c r="C2017" t="n">
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.590088632470154</v>
+        <v>-4.434094955639335</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.810926577172439</v>
+        <v>1.873324047904767</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.1780110714897285</v>
+        <v>0.2643556020718979</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.754125097368085</v>
+        <v>3.805931815717387</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423384</v>
+        <v>3.619923016423386</v>
       </c>
       <c r="C2018" t="n">
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.539566728642488</v>
+        <v>-4.383573051811669</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.817186540823626</v>
+        <v>1.879584011555954</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.1780110714897285</v>
+        <v>0.2643556020718979</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.740176299488206</v>
+        <v>3.791983017837508</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.65633273360975</v>
+        <v>3.656332733609752</v>
       </c>
       <c r="C2019" t="n">
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.792041882650213</v>
+        <v>-4.636048205819393</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.72806696827595</v>
+        <v>1.790464439008278</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.1780110714897285</v>
+        <v>0.2643556020718979</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.75204678854362</v>
+        <v>3.803853506892922</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973154</v>
+        <v>3.674028535973156</v>
       </c>
       <c r="C2020" t="n">
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-5.084937639129625</v>
+        <v>-4.928943962298805</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.612119200203129</v>
+        <v>1.674516670935457</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.1780110714897285</v>
+        <v>0.2643556020718979</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.753257323062564</v>
+        <v>3.805064041411865</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251942</v>
+        <v>3.663509457251945</v>
       </c>
       <c r="C2021" t="n">
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.271601767264433</v>
+        <v>-5.115608090433613</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.541575291176527</v>
+        <v>1.603972761908855</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.1512721006651686</v>
+        <v>0.237616631247338</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.741335682795149</v>
+        <v>3.793142401144451</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916198</v>
+        <v>3.6521491529162</v>
       </c>
       <c r="C2022" t="n">
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.417622454178395</v>
+        <v>-5.261628777347576</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.478244869147132</v>
+        <v>1.54064233987946</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.1421890088713116</v>
+        <v>0.228533539453481</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.730963680455024</v>
+        <v>3.782770398804326</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830325</v>
+        <v>3.667962306830327</v>
       </c>
       <c r="C2023" t="n">
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.50933646328798</v>
+        <v>-5.35334278645716</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.603763322202342</v>
+        <v>1.66616079293467</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.1421890088713116</v>
+        <v>0.228533539453481</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.893167737154068</v>
+        <v>3.94497445550337</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071547</v>
+        <v>3.696539468071549</v>
       </c>
       <c r="C2024" t="n">
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.540988122347949</v>
+        <v>-5.38499444551713</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.585949296542168</v>
+        <v>1.648346767274496</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.1370205516268714</v>
+        <v>0.2233650822090408</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.884913300771219</v>
+        <v>3.93672001912052</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868142</v>
+        <v>3.750044015868144</v>
       </c>
       <c r="C2025" t="n">
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.622922940616832</v>
+        <v>-5.466929263786013</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.563404786803106</v>
+        <v>1.625802257535434</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.1270858060397912</v>
+        <v>0.2134303366219606</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.889181870987461</v>
+        <v>3.940988589336763</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332687</v>
+        <v>3.783632867332689</v>
       </c>
       <c r="C2026" t="n">
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.72489906286524</v>
+        <v>-5.56890538603442</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.531539976359646</v>
+        <v>1.593937447091974</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.02510968379138367</v>
+        <v>0.1114542143735531</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.83692183609432</v>
+        <v>3.888728554443621</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231805</v>
+        <v>3.798296784231806</v>
       </c>
       <c r="C2027" t="n">
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.614892779388018</v>
+        <v>-5.458899102557199</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.56769537699471</v>
+        <v>1.630092847727038</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.04831425570865888</v>
+        <v>0.1346587862908283</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.84299746648886</v>
+        <v>3.894804184838162</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818518</v>
+        <v>3.78556392481852</v>
       </c>
       <c r="C2028" t="n">
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.471833203647092</v>
+        <v>-5.315839526816273</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.629169218013055</v>
+        <v>1.691566688745382</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.05632768229863816</v>
+        <v>0.1426722128808076</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.852055533164822</v>
+        <v>3.903862251514123</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051785</v>
+        <v>3.777237412051786</v>
       </c>
       <c r="C2029" t="n">
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.170386478175255</v>
+        <v>-5.014392801344435</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.757008791084326</v>
+        <v>1.819406261816654</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.3577744077704754</v>
+        <v>0.4441189383526448</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.04018445133046</v>
+        <v>4.091991169679762</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679621</v>
+        <v>3.812635940679623</v>
       </c>
       <c r="C2030" t="n">
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.194976722410439</v>
+        <v>-5.038983045579619</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.748143871142963</v>
+        <v>1.81054134187529</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.3577744077704754</v>
+        <v>0.4441189383526448</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.041155629083171</v>
+        <v>4.092962347432472</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474155</v>
+        <v>3.821184182474157</v>
       </c>
       <c r="C2031" t="n">
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-5.143938346403918</v>
+        <v>-4.987944669573099</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.769402125925327</v>
+        <v>1.831799596657654</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.3577744077704754</v>
+        <v>0.4441189383526448</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.041998533462927</v>
+        <v>4.093805251812228</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969539</v>
+        <v>3.831734516969541</v>
       </c>
       <c r="C2032" t="n">
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-5.102799051537287</v>
+        <v>-4.946805374706468</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.804895942746124</v>
+        <v>1.867293413478452</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.3989137026371062</v>
+        <v>0.4852582332192756</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.08572020925705</v>
+        <v>4.137526927606352</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700475</v>
+        <v>3.825752932700476</v>
       </c>
       <c r="C2033" t="n">
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-5.006164139518647</v>
+        <v>-4.850170462687828</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.659733903677515</v>
+        <v>1.722131374409843</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.4955486146557462</v>
+        <v>0.5818931452379156</v>
       </c>
       <c r="G2033" t="n">
-        <v>3.959885152592169</v>
+        <v>4.011691870941471</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077637</v>
+        <v>3.804688961077638</v>
       </c>
       <c r="C2034" t="n">
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-5.13674487404949</v>
+        <v>-4.98075119721867</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.611003653939142</v>
+        <v>1.67340112467147</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.3649678801249037</v>
+        <v>0.4513124107070731</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.885038755947627</v>
+        <v>3.936845474296929</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833455</v>
+        <v>3.775028860833457</v>
       </c>
       <c r="C2035" t="n">
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.972248539858528</v>
+        <v>-4.816254863027709</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.661229006691609</v>
+        <v>1.723626477423937</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.5294642143158655</v>
+        <v>0.6158087448980349</v>
       </c>
       <c r="G2035" t="n">
-        <v>3.968163375538287</v>
+        <v>4.019970093887589</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077627</v>
+        <v>3.821030660077628</v>
       </c>
       <c r="C2036" t="n">
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.99961847254296</v>
+        <v>-4.843624795712141</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.649468744054266</v>
+        <v>1.711866214786594</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.5294642143158655</v>
+        <v>0.6158087448980349</v>
       </c>
       <c r="G2036" t="n">
-        <v>3.967351085974717</v>
+        <v>4.019157804324019</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147907</v>
+        <v>3.832307024147909</v>
       </c>
       <c r="C2037" t="n">
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-5.01000366743285</v>
+        <v>-4.85400999060203</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.655183445223383</v>
+        <v>1.71758091595571</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.5190790194259762</v>
+        <v>0.6054235500081456</v>
       </c>
       <c r="G2037" t="n">
-        <v>3.970988748165856</v>
+        <v>4.022795466515158</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735278</v>
+        <v>3.83441549373528</v>
       </c>
       <c r="C2038" t="n">
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-5.028591826155075</v>
+        <v>-4.872598149324255</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.718585187510918</v>
+        <v>1.780982658243246</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.5004908607037508</v>
+        <v>0.5868353912859203</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.030672858708946</v>
+        <v>4.082479577058248</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496551</v>
+        <v>3.855120535496553</v>
       </c>
       <c r="C2039" t="n">
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-5.028890372851111</v>
+        <v>-4.872896696020291</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.715334779650802</v>
+        <v>1.77773225038313</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.5001923140077149</v>
+        <v>0.5865368445898844</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.027362741509623</v>
+        <v>4.079169459858925</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108854</v>
+        <v>3.815643212108856</v>
       </c>
       <c r="C2040" t="n">
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.928067239160683</v>
+        <v>-4.772073562329863</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.760194928066364</v>
+        <v>1.822592398798692</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.5126565294920687</v>
+        <v>0.5990010600742383</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.039372165739627</v>
+        <v>4.091178884088928</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121463</v>
+        <v>3.807356168121466</v>
       </c>
       <c r="C2041" t="n">
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.737285878408276</v>
+        <v>-4.581292201577456</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.83663672584587</v>
+        <v>1.899034196578198</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.7034378902444761</v>
+        <v>0.7897824208266456</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.153970235669614</v>
+        <v>4.205776954018916</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906076</v>
+        <v>3.775233033906079</v>
       </c>
       <c r="C2042" t="n">
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.630322520558854</v>
+        <v>-4.474328843728035</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.859258914723236</v>
+        <v>1.921656385455563</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.7619024982042776</v>
+        <v>0.8482470287864471</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.168885846183091</v>
+        <v>4.220692564532393</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912981</v>
+        <v>3.785761685912984</v>
       </c>
       <c r="C2043" t="n">
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.574991932657092</v>
+        <v>-4.418998255826272</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.916358086495999</v>
+        <v>1.978755557228327</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.8172330861060397</v>
+        <v>0.9035776166882092</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.237051135536207</v>
+        <v>4.288857853885509</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539891</v>
+        <v>3.743767956539894</v>
       </c>
       <c r="C2044" t="n">
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.562937805744129</v>
+        <v>-4.40694412891331</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.914866305162622</v>
+        <v>1.97726377589495</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.8292872130190025</v>
+        <v>0.9156317436011721</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.237970179585423</v>
+        <v>4.289776897934725</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811005</v>
+        <v>3.725010844811008</v>
       </c>
       <c r="C2045" t="n">
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.60409292531235</v>
+        <v>-4.44809924848153</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.90028488751947</v>
+        <v>1.962682358251797</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.7881320934507816</v>
+        <v>0.8744766240329511</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.215157738028626</v>
+        <v>4.266964456377927</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382916</v>
+        <v>3.612322444382919</v>
       </c>
       <c r="C2046" t="n">
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.53604436262082</v>
+        <v>-4.380050685790001</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.940355338473964</v>
+        <v>2.002752809206291</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.8561806561423114</v>
+        <v>0.9425251867244809</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.268837901521426</v>
+        <v>4.320644619870728</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760312</v>
+        <v>3.646857607760315</v>
       </c>
       <c r="C2047" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.767644755790321</v>
+        <v>-4.611651078959501</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.867917851379758</v>
+        <v>1.930315322112086</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.8561806561423114</v>
+        <v>0.9425251867244809</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.28904057169502</v>
+        <v>4.340847290044322</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781702</v>
+        <v>3.666767386781705</v>
       </c>
       <c r="C2048" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.785717264081932</v>
+        <v>-4.629723587251113</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.860688848063113</v>
+        <v>1.923086318795441</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.8561806561423114</v>
+        <v>0.9425251867244809</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.28904057169502</v>
+        <v>4.340847290044322</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082831</v>
+        <v>3.670068888082834</v>
       </c>
       <c r="C2049" t="n">
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.960824096658378</v>
+        <v>-4.804830419827558</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.750898028626002</v>
+        <v>1.813295499358329</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.8561806561423114</v>
+        <v>0.9425251867244809</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.249292485288487</v>
+        <v>4.301099203637789</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943583</v>
+        <v>3.745593333943585</v>
       </c>
       <c r="C2050" t="n">
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.929538076117923</v>
+        <v>-4.773544399287103</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.770435055839124</v>
+        <v>1.832832526571452</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.8874666766827668</v>
+        <v>0.9738112072649363</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.2750867166097</v>
+        <v>4.326893434959002</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.73059065867782</v>
+        <v>3.730590658677823</v>
       </c>
       <c r="C2051" t="n">
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.707967159492662</v>
+        <v>-4.620519007173819</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.958234422062132</v>
+        <v>1.99321368298967</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.109037593308027</v>
+        <v>1.12683659937822</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.507200266157761</v>
+        <v>4.517879669799877</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073879</v>
+        <v>3.741298518073883</v>
       </c>
       <c r="C2052" t="n">
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.736274473365932</v>
+        <v>-4.614591320471618</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.134377721421116</v>
+        <v>2.183050982578842</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.109037593308027</v>
+        <v>1.12683659937822</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.694666491066053</v>
+        <v>4.705345894708169</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903164</v>
+        <v>3.699135800903168</v>
       </c>
       <c r="C2053" t="n">
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.902867698479454</v>
+        <v>-4.78118454558514</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.03714338272979</v>
+        <v>2.085816643887515</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.9424443681945049</v>
+        <v>0.9602433742646979</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.564113507352022</v>
+        <v>4.574792910994137</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568379</v>
+        <v>3.708202704568382</v>
       </c>
       <c r="C2054" t="n">
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.729803319097154</v>
+        <v>-4.60812016620284</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.110045537144428</v>
+        <v>2.158718798302153</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.9424443681945049</v>
+        <v>0.9602433742646979</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.56778991001374</v>
+        <v>4.578469313655855</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.7406015866822</v>
+        <v>3.740601586682204</v>
       </c>
       <c r="C2055" t="n">
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.700557338641458</v>
+        <v>-4.578874185747144</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.119361984450201</v>
+        <v>2.168035245607927</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.9424443681945049</v>
+        <v>0.9602433742646979</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.565407965137235</v>
+        <v>4.57608736877935</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539104</v>
+        <v>3.699424827539107</v>
       </c>
       <c r="C2056" t="n">
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.807482886519309</v>
+        <v>-4.685799733624995</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.073885004456696</v>
+        <v>2.122558265614422</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.8355188203166536</v>
+        <v>0.8533178263868465</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.498545875568159</v>
+        <v>4.509225279210275</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983734</v>
+        <v>3.689962785983737</v>
       </c>
       <c r="C2057" t="n">
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.952501445026558</v>
+        <v>-4.830818292132244</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.017306383197031</v>
+        <v>2.065979644354757</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.690500261809405</v>
+        <v>0.708299267879598</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.412963542607044</v>
+        <v>4.42364294624916</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969745</v>
+        <v>3.711872614969749</v>
       </c>
       <c r="C2058" t="n">
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-5.070843210811275</v>
+        <v>-4.949160057916961</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.069900916140897</v>
+        <v>2.118574177298623</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.7011863003722951</v>
+        <v>0.718985306442488</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.519306405002531</v>
+        <v>4.529985808644647</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073535</v>
+        <v>3.714899237073539</v>
       </c>
       <c r="C2059" t="n">
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.122253633131983</v>
+        <v>-5.000570480237669</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.047122444338552</v>
+        <v>2.095795705496278</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.7011863003722951</v>
+        <v>0.718985306442488</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.51709210212847</v>
+        <v>4.527771505770586</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720063</v>
+        <v>3.704778134720066</v>
       </c>
       <c r="C2060" t="n">
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.201673084339735</v>
+        <v>-5.079989931445421</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.015257791929741</v>
+        <v>2.063931053087467</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.7011863003722951</v>
+        <v>0.718985306442488</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.51699523020276</v>
+        <v>4.527674633844875</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.73682513758113</v>
+        <v>3.736825137581134</v>
       </c>
       <c r="C2061" t="n">
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.297136082256952</v>
+        <v>-5.175452929362638</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.977066486320898</v>
+        <v>2.025739747478623</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.7011863003722951</v>
+        <v>0.718985306442488</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.516989123760803</v>
+        <v>4.527668527402919</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715393145500732</v>
+        <v>3.715393145500736</v>
       </c>
       <c r="C2062" t="n">
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.337156080300736</v>
+        <v>-5.215472927406422</v>
       </c>
       <c r="E2062" t="n">
-        <v>1.959154883665995</v>
+        <v>2.007828144823721</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.6611663023285113</v>
+        <v>0.6789653083987042</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.491073521497143</v>
+        <v>4.501752925139259</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736109598636268</v>
+        <v>3.736109598636271</v>
       </c>
       <c r="C2063" t="n">
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.39252524243293</v>
+        <v>-5.270842089538616</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.942741036560844</v>
+        <v>1.99141429771857</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.6611663023285113</v>
+        <v>0.6789653083987042</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.49680733924487</v>
+        <v>4.507486742886986</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736843055396011</v>
+        <v>3.736843055396014</v>
       </c>
       <c r="C2064" t="n">
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.437963022263757</v>
+        <v>-5.316279869369443</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.924104287971446</v>
+        <v>1.972777549129172</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.6183213116503516</v>
+        <v>0.6361203177205446</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.470638708180907</v>
+        <v>4.481318111823023</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.79029268539642</v>
+        <v>3.790292685396423</v>
       </c>
       <c r="C2065" t="n">
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.349756188116179</v>
+        <v>-5.228073035221865</v>
       </c>
       <c r="E2065" t="n">
-        <v>1.979261414480796</v>
+        <v>2.027934675638522</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.6183213116503516</v>
+        <v>0.6361203177205446</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.490513101031226</v>
+        <v>4.501192504673342</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794507029299173</v>
+        <v>3.794507029299177</v>
       </c>
       <c r="C2066" t="n">
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.173465963510871</v>
+        <v>-5.051782810616557</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.033478204847647</v>
+        <v>2.082151466005373</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.6183213116503516</v>
+        <v>0.6361203177205446</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.474213801555954</v>
+        <v>4.48489320519807</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794725278590405</v>
+        <v>3.794725278590408</v>
       </c>
       <c r="C2067" t="n">
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.990254300377776</v>
+        <v>-4.868571147483462</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.109193819564931</v>
+        <v>2.157867080722657</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.6183213116503516</v>
+        <v>0.6361203177205446</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.476644751019999</v>
+        <v>4.487324154662115</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776866743146282</v>
+        <v>3.776866743146287</v>
       </c>
       <c r="C2068" t="n">
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.918532853363925</v>
+        <v>-4.799292375071952</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.10367358421836</v>
+        <v>2.15136977553515</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.6900427586642023</v>
+        <v>0.7053990901320553</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.485468805076199</v>
+        <v>4.494682603956911</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723809890676845</v>
+        <v>3.723809890676849</v>
       </c>
       <c r="C2069" t="n">
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-5.047911636003703</v>
+        <v>-4.928671157711729</v>
       </c>
       <c r="E2069" t="n">
-        <v>1.998837817083621</v>
+        <v>2.04653400840041</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.6479409859569989</v>
+        <v>0.663297317424852</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.407123487373049</v>
+        <v>4.416337286253761</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715627631739462</v>
+        <v>3.715627631739466</v>
       </c>
       <c r="C2070" t="n">
         <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-5.080927931914448</v>
+        <v>-4.961687453622474</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.170829503604679</v>
+        <v>2.218525694921468</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.5785036092902474</v>
+        <v>0.5938599407581004</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.550659266258354</v>
+        <v>4.559873065139065</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713782722166409</v>
+        <v>3.713782722166412</v>
       </c>
       <c r="C2071" t="n">
         <v>4.195478326512454</v>
       </c>
       <c r="D2071" t="n">
-        <v>-5.069400296264839</v>
+        <v>-4.950159817972866</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.167361783692771</v>
+        <v>2.21505797500956</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.6375042674916098</v>
+        <v>0.6528605989594629</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.577980887007421</v>
+        <v>4.587194685888132</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717170884519029</v>
+        <v>3.717170884519033</v>
       </c>
       <c r="C2072" t="n">
         <v>4.199146439034243</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.166741797607208</v>
+        <v>-5.047501319315234</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.132093295677612</v>
+        <v>2.179789486994402</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.5930840853261214</v>
+        <v>0.6084404167939745</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.554996890229916</v>
+        <v>4.564210689110627</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705221264710415</v>
+        <v>3.705221264710419</v>
       </c>
       <c r="C2073" t="n">
         <v>4.200397521227081</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.252597826947174</v>
+        <v>-5.133357348655201</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.099001966134464</v>
+        <v>2.146698157451253</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.5507080160999864</v>
+        <v>0.5660643475678395</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.530822330887073</v>
+        <v>4.540036129767785</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691855684893113</v>
+        <v>3.691855684893114</v>
       </c>
       <c r="C2074" t="n">
         <v>4.182816723047583</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.235788902547903</v>
+        <v>-5.11654842425593</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.088144737714674</v>
+        <v>2.135840929031463</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.5747741117883666</v>
+        <v>0.5901304432562197</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.527681190120603</v>
+        <v>4.536894989001315</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.850670066106093</v>
+        <v>3.865470038396633</v>
       </c>
       <c r="C2075" t="n">
-        <v>4.276067444493082</v>
+        <v>4.249271719999743</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.235788902547903</v>
+        <v>-5.146359743954807</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.088144737714674</v>
+        <v>2.190371398104073</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.5747741117883666</v>
+        <v>0.5901304432562197</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.26913124147945</v>
+        <v>4.603349985953475</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240902.xlsx
+++ b/tame_output/ON/bt/strategyON_20240902.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.3%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>10.2%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>94.7%</t>
+          <t>94.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>77.5%</t>
+          <t>80.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>113.3%</t>
+          <t>111.4%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.0%</t>
+          <t>-78.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.2%</t>
+          <t>108.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.9%</t>
+          <t>124.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.4%</t>
+          <t>90.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,12 +977,12 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-604.1%</t>
+          <t>-616.8%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-44.6%</t>
+          <t>-46.5%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.4%</t>
+          <t>-49.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.3%</t>
+          <t>-75.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.7%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>426.3%</t>
+          <t>418.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-676.2%</t>
+          <t>-665.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-242.0%</t>
+          <t>-247.1%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,47 +1150,47 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.0%</t>
+          <t>-34.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>22.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-21.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-157.2%</t>
+          <t>-155.0%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-13.3%</t>
+          <t>-11.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.20</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>72.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>589.8%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-307.3%</t>
+          <t>-310.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-165.0%</t>
+          <t>-150.1%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>92.6%</t>
+          <t>95.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>82.7%</t>
+          <t>88.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>-16.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>21.3%</t>
         </is>
       </c>
     </row>
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.5282982604764979</v>
+        <v>-0.6545912063460799</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.90965303382238</v>
+        <v>2.859135855474547</v>
       </c>
       <c r="F1845" t="n">
         <v>1.533058604805237</v>
@@ -44009,10 +44009,10 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.5169090238216965</v>
+        <v>-0.6432019696912785</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.91203352460354</v>
+        <v>2.861516346255708</v>
       </c>
       <c r="F1846" t="n">
         <v>1.544447841460039</v>
@@ -44032,10 +44032,10 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.7693869182411024</v>
+        <v>-0.8956798641106845</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.808969258340841</v>
+        <v>2.758452079993008</v>
       </c>
       <c r="F1847" t="n">
         <v>1.291969947040633</v>
@@ -44055,10 +44055,10 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.059518584846534</v>
+        <v>-1.185811530716116</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.69278280829759</v>
+        <v>2.642265629949757</v>
       </c>
       <c r="F1848" t="n">
         <v>1.316051741780813</v>
@@ -44072,16 +44072,16 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382189</v>
+        <v>3.27276013138219</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.267522643199611</v>
+        <v>-1.393815589069193</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.614473329510285</v>
+        <v>2.563956151162452</v>
       </c>
       <c r="F1849" t="n">
         <v>1.316051741780813</v>
@@ -44095,16 +44095,16 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.25147557607462</v>
+        <v>3.251475576074621</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.329701054360581</v>
+        <v>-1.455994000230163</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.584683421383885</v>
+        <v>2.534166243036052</v>
       </c>
       <c r="F1850" t="n">
         <v>1.253873330619843</v>
@@ -44118,16 +44118,16 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911637</v>
+        <v>3.233800325911638</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.695769781505234</v>
+        <v>-1.822062727374816</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.431340229832473</v>
+        <v>2.38082305148464</v>
       </c>
       <c r="F1851" t="n">
         <v>0.88780460347519</v>
@@ -44147,10 +44147,10 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.904260562956918</v>
+        <v>-2.0305535088265</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.368282206990567</v>
+        <v>2.317765028642734</v>
       </c>
       <c r="F1852" t="n">
         <v>0.6793138220235055</v>
@@ -44164,16 +44164,16 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416043</v>
+        <v>3.231167537416044</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.15146174772214</v>
+        <v>-2.277754693591722</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.277500483493047</v>
+        <v>2.226983305145214</v>
       </c>
       <c r="F1853" t="n">
         <v>0.699467175522318</v>
@@ -44187,16 +44187,16 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382326</v>
+        <v>3.235981977382327</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.643846775746237</v>
+        <v>-2.770139721615819</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.081652864327141</v>
+        <v>2.031135685979308</v>
       </c>
       <c r="F1854" t="n">
         <v>0.2070821474982212</v>
@@ -44210,16 +44210,16 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495496</v>
+        <v>3.278199702495497</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.02902716667631</v>
+        <v>-3.155320112545891</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.926123246767975</v>
+        <v>1.875606068420142</v>
       </c>
       <c r="F1855" t="n">
         <v>0.2070821474982212</v>
@@ -44233,16 +44233,16 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347051</v>
+        <v>3.299136146347053</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.278897846690891</v>
+        <v>-3.405190792560473</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.827944098216758</v>
+        <v>1.777426919868925</v>
       </c>
       <c r="F1856" t="n">
         <v>0.2433448673286845</v>
@@ -44256,16 +44256,16 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130014</v>
+        <v>3.287377576130015</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.485409623577913</v>
+        <v>-3.611702569447494</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.741445446118208</v>
+        <v>1.690928267770375</v>
       </c>
       <c r="F1857" t="n">
         <v>0.036833090441663</v>
@@ -44279,16 +44279,16 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178239</v>
+        <v>3.31588437417824</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.804753698658414</v>
+        <v>-3.931046644527996</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.615480742786267</v>
+        <v>1.564963564438434</v>
       </c>
       <c r="F1858" t="n">
         <v>0.036833090441663</v>
@@ -44302,16 +44302,16 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207809</v>
+        <v>3.30531679820781</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.190963529934189</v>
+        <v>-4.31725647580377</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.447329697743361</v>
+        <v>1.396812519395528</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.05393984927578033</v>
@@ -44325,16 +44325,16 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310977</v>
+        <v>3.284619513310978</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.425657524066741</v>
+        <v>-4.551950469936322</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.341736875092431</v>
+        <v>1.291219696744598</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.04760358204652515</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.761320171297194</v>
+        <v>-4.887613117166775</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.206052407856215</v>
+        <v>1.155535229508382</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.11553456753543</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.837764501500065</v>
+        <v>-4.964057447369647</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.181962236009308</v>
+        <v>1.131445057661475</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.03508905844176807</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.202891884138812</v>
+        <v>-5.329184830008393</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.035165797959641</v>
+        <v>0.9846486196118076</v>
       </c>
       <c r="F1863" t="n">
         <v>-0.3313998427407806</v>
@@ -44417,16 +44417,16 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330518</v>
+        <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.61148066131949</v>
+        <v>-5.737773607189072</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.8704918311021284</v>
+        <v>0.8199746527542953</v>
       </c>
       <c r="F1864" t="n">
         <v>-0.739988619921459</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.725241073342355</v>
+        <v>-5.851534019211937</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.8201730987644429</v>
+        <v>0.7696559204166098</v>
       </c>
       <c r="F1865" t="n">
         <v>-0.739988619921459</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.141632947629352</v>
+        <v>-6.267925893498934</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.6516103996585212</v>
+        <v>0.6010932213106881</v>
       </c>
       <c r="F1866" t="n">
         <v>-0.739988619921459</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.50280657744634</v>
+        <v>-6.629099523315922</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.5173996384004051</v>
+        <v>0.4668824600525721</v>
       </c>
       <c r="F1867" t="n">
         <v>-0.739988619921459</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094111</v>
+        <v>3.37443904309411</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.846065097089359</v>
+        <v>-6.972358042958941</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.3761957956888931</v>
+        <v>0.3256786173410595</v>
       </c>
       <c r="F1868" t="n">
         <v>-0.739988619921459</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.40596051119928</v>
+        <v>3.405960511199279</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.894267914331703</v>
+        <v>-7.020560860201285</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.3553195888469562</v>
+        <v>0.3048024104991232</v>
       </c>
       <c r="F1869" t="n">
         <v>-0.739988619921459</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969588</v>
+        <v>3.424633354969587</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.061076574306065</v>
+        <v>-7.187369520175647</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.2923751007864195</v>
+        <v>0.2418579224385864</v>
       </c>
       <c r="F1870" t="n">
         <v>-0.7822719436345955</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392308</v>
+        <v>3.419979433923079</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.247796282615368</v>
+        <v>-7.37408922848495</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.2136609129282956</v>
+        <v>0.1631437345804621</v>
       </c>
       <c r="F1871" t="n">
         <v>-0.7822719436345955</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297743</v>
+        <v>3.458100091297742</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.630797671357999</v>
+        <v>-7.757090617227581</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.06035825610965873</v>
+        <v>0.009841077761825634</v>
       </c>
       <c r="F1872" t="n">
         <v>-0.7822719436345955</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.44775050131761</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.635284116559387</v>
+        <v>-7.761577062428969</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.06113519400053358</v>
+        <v>0.01061801565270049</v>
       </c>
       <c r="F1873" t="n">
         <v>-0.7867583888359841</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737165</v>
+        <v>3.503515506737164</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.994814439063389</v>
+        <v>-8.121107384932973</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.07732663170301679</v>
+        <v>-0.1278438100508503</v>
       </c>
       <c r="F1874" t="n">
         <v>-0.7867583888359841</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341308</v>
+        <v>3.503170282341307</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.04516350251761</v>
+        <v>-8.171456448387195</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.08955023712752785</v>
+        <v>-0.1400674154753618</v>
       </c>
       <c r="F1875" t="n">
         <v>-0.8371074522902062</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539459</v>
+        <v>3.501052558539458</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.142782779939006</v>
+        <v>-8.269075725808591</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1255561974743173</v>
+        <v>-0.1760733758221513</v>
       </c>
       <c r="F1876" t="n">
         <v>-0.9347267297116029</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937497</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.196854279447365</v>
+        <v>-8.32314722531695</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1442912409560888</v>
+        <v>-0.1948084193039228</v>
       </c>
       <c r="F1877" t="n">
         <v>-0.9887982292199623</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.5027903991417</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.401112454777229</v>
+        <v>-8.527405400646813</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.2204813139693917</v>
+        <v>-0.2709984923172257</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.116437173833951</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.434765293285702</v>
+        <v>-8.561058239155287</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.2294598948883451</v>
+        <v>-0.279977073236179</v>
       </c>
       <c r="F1879" t="n">
         <v>-1.216850541750989</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440633</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.573851407904559</v>
+        <v>-8.700144353774144</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2697226392424668</v>
+        <v>-0.3202398175903007</v>
       </c>
       <c r="F1880" t="n">
         <v>-1.355936656369845</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.748975825291103</v>
+        <v>-8.875268771160687</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.3252171854495676</v>
+        <v>-0.3757343637974015</v>
       </c>
       <c r="F1881" t="n">
         <v>-1.531061073756389</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.983427919305592</v>
+        <v>-9.109720865175177</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.4262171879569592</v>
+        <v>-0.4767343663047932</v>
       </c>
       <c r="F1882" t="n">
         <v>-1.531061073756389</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.087802650332039</v>
+        <v>-9.214095596201624</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.4746392711415139</v>
+        <v>-0.5251564494893479</v>
       </c>
       <c r="F1883" t="n">
         <v>-1.635435804782835</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.250316116030623</v>
+        <v>-9.376609061900208</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5385288675823916</v>
+        <v>-0.5890460459302256</v>
       </c>
       <c r="F1884" t="n">
         <v>-1.733069235201522</v>
@@ -44906,10 +44906,10 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.376352909398912</v>
+        <v>-9.502645855268497</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5862498563005927</v>
+        <v>-0.6367670346484267</v>
       </c>
       <c r="F1885" t="n">
         <v>-1.707817612391779</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.319281137502982</v>
+        <v>-9.445574083372566</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5594308118558193</v>
+        <v>-0.6099479902036533</v>
       </c>
       <c r="F1886" t="n">
         <v>-1.707817612391779</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.460952979227102</v>
+        <v>-9.587245925096687</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6175747754442091</v>
+        <v>-0.6680919537920431</v>
       </c>
       <c r="F1887" t="n">
         <v>-1.707817612391779</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940717</v>
+        <v>3.691571733940716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.411362134802268</v>
+        <v>-9.537655080671852</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5826850275094033</v>
+        <v>-0.6332022058572373</v>
       </c>
       <c r="F1888" t="n">
         <v>-1.658226767966946</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770578</v>
+        <v>3.676841549770577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.262443800330411</v>
+        <v>-9.388736746199996</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5361688273673435</v>
+        <v>-0.5866860057151775</v>
       </c>
       <c r="F1889" t="n">
         <v>-1.626977177231772</v>
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.036598647611001</v>
+        <v>-9.355626577285125</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4362516932433711</v>
+        <v>-0.5638628651130206</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.585050501644609</v>
+        <v>-1.623776450955233</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.227713889128012</v>
+        <v>2.204478319541638</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812101</v>
+        <v>3.6848438238121</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.912019991273409</v>
+        <v>-9.231047920947534</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3852810861522751</v>
+        <v>-0.5128922580219251</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.585050501644609</v>
+        <v>-1.623776450955233</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.228853033684071</v>
+        <v>2.205617464097696</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646215</v>
+        <v>3.710935533646214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.886983309704899</v>
+        <v>-9.206011239379023</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3726326393627635</v>
+        <v>-0.5002438112324135</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.559721414093873</v>
+        <v>-1.598447363404497</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.24668426037662</v>
+        <v>2.223448690790246</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611567</v>
+        <v>3.768951674611565</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.814850134417018</v>
+        <v>-9.133878064091142</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3380456650089747</v>
+        <v>-0.4656568368786242</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.559721414093873</v>
+        <v>-1.598447363404497</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.252417964615256</v>
+        <v>2.229182395028882</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955327</v>
+        <v>3.728577929955325</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.743483741807371</v>
+        <v>-9.062511671481495</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.3192363703589809</v>
+        <v>-0.4468475422286309</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.488355021484225</v>
+        <v>-1.527080970794849</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.28550053778718</v>
+        <v>2.262264968200806</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232412</v>
+        <v>3.747702660232409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.650024707822146</v>
+        <v>-8.96905263749627</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2917362380777986</v>
+        <v>-0.4193474099474486</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.488355021484225</v>
+        <v>-1.527080970794849</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.275617056474272</v>
+        <v>2.252381486887898</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436228</v>
+        <v>3.766317079436226</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.639371526268715</v>
+        <v>-8.958399455942839</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2893095259557996</v>
+        <v>-0.4169206978254496</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.488355021484225</v>
+        <v>-1.527080970794849</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.273782495974899</v>
+        <v>2.250546926388524</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311948</v>
+        <v>3.784684521311945</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.541464487592224</v>
+        <v>-8.860492417266348</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.2504470254586644</v>
+        <v>-0.3780581973283144</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.420369271623669</v>
+        <v>-1.459095220934293</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.314273630917771</v>
+        <v>2.291038061331397</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.80082935409724</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.517510946616266</v>
+        <v>-8.83653887629039</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2401971029227874</v>
+        <v>-0.3678082747924374</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.396415730647711</v>
+        <v>-1.435141679958335</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.32931426164884</v>
+        <v>2.306078692062465</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.789311112017766</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.253451008293469</v>
+        <v>-8.572478937967594</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1478334437554212</v>
+        <v>-0.2754446156250707</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.132355792324915</v>
+        <v>-1.171081741635539</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.474489908480765</v>
+        <v>2.451254338894391</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839722</v>
+        <v>3.83325274783972</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.546371384788631</v>
+        <v>-7.865399314462755</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1322113719862132</v>
+        <v>0.004600200116563702</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.132355792324915</v>
+        <v>-1.171081741635539</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.471702874820465</v>
+        <v>2.44846730523409</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388726</v>
+        <v>3.839374447388724</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.50618708642244</v>
+        <v>-7.825215016096565</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1486287152205308</v>
+        <v>0.02101754335088124</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.092171493958724</v>
+        <v>-1.130897443269348</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.49615707772802</v>
+        <v>2.472921508141646</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.856161751626469</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.342787215483078</v>
+        <v>-7.661815145157203</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2133554848170327</v>
+        <v>0.08574431294738316</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.9287716230193617</v>
+        <v>-0.9674975723299855</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.593563821512395</v>
+        <v>2.57032825192602</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291813</v>
+        <v>3.78733042929181</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.109305993253479</v>
+        <v>-7.428333922927604</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3146724025467247</v>
+        <v>0.1870612306770747</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.6952904007897631</v>
+        <v>-0.7340163501003869</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.741576983688006</v>
+        <v>2.718341414101632</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785788</v>
+        <v>3.801637122785785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.959639602245964</v>
+        <v>-7.278667531920089</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.3716467486367714</v>
+        <v>0.2440355767671218</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.6023869095472272</v>
+        <v>-0.641112858857851</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.794426868120569</v>
+        <v>2.771191298534194</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390429</v>
+        <v>3.763182248390425</v>
       </c>
       <c r="C1905" t="n">
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.827364128615078</v>
+        <v>-7.146392058289202</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.325817724096281</v>
+        <v>0.198206552226631</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.4701114359163405</v>
+        <v>-0.5088373852269643</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.775052938306255</v>
+        <v>2.751817368719881</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105954</v>
+        <v>3.784718794105951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.671625796055336</v>
+        <v>-6.990653725729461</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.3909281178078143</v>
+        <v>0.2633169459381643</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.314373103356599</v>
+        <v>-0.3530990526672227</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.871310998529737</v>
+        <v>2.848075428943363</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960987</v>
+        <v>3.753882571960983</v>
       </c>
       <c r="C1907" t="n">
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.586661129326016</v>
+        <v>-6.905689059000141</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.4378203257232012</v>
+        <v>0.3102091538535512</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.2294084366272794</v>
+        <v>-0.2681343859379032</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.935196139790988</v>
+        <v>2.911960570204613</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607641</v>
       </c>
       <c r="C1908" t="n">
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.692251119099121</v>
+        <v>-7.011279048773245</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.2676084002147405</v>
+        <v>0.1399972283450905</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.3349984264003837</v>
+        <v>-0.3737243757110075</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.743866216327906</v>
+        <v>2.720630646741532</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.770422583987899</v>
       </c>
       <c r="C1909" t="n">
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.624016534473693</v>
+        <v>-6.943044464147818</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3434465759419978</v>
+        <v>0.2158354040723482</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.3165831035278477</v>
+        <v>-0.3553090528384715</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.803459751928514</v>
+        <v>2.78022418234214</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710813</v>
+        <v>3.760333686710809</v>
       </c>
       <c r="C1910" t="n">
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.476076493066094</v>
+        <v>-6.795104422740218</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.2860017838666304</v>
+        <v>0.1583906119969809</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.2962621876192902</v>
+        <v>-0.334988136929914</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.699031492835242</v>
+        <v>2.675795923248867</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409201</v>
       </c>
       <c r="C1911" t="n">
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.423106970812105</v>
+        <v>-6.74213490048623</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.2984756065147476</v>
+        <v>0.170864434645098</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.2432926653653013</v>
+        <v>-0.2820186146759251</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.722099219934157</v>
+        <v>2.698863650347783</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098109</v>
+        <v>3.729969716098106</v>
       </c>
       <c r="C1912" t="n">
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.257318774851814</v>
+        <v>-6.576346704525939</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.357830272803771</v>
+        <v>0.230219100934121</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.2432926653653013</v>
+        <v>-0.2820186146759251</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.715138607839064</v>
+        <v>2.691903038252689</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.78292253349342</v>
+        <v>3.782922533493417</v>
       </c>
       <c r="C1913" t="n">
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.223955568373046</v>
+        <v>-6.54298349804717</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.3856379097764213</v>
+        <v>0.2580267379067718</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.2432926653653013</v>
+        <v>-0.2820186146759251</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.729600962220207</v>
+        <v>2.706365392633832</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722818</v>
+        <v>3.828551486722814</v>
       </c>
       <c r="C1914" t="n">
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.115696431250524</v>
+        <v>-6.434724360924649</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.423473685084625</v>
+        <v>0.2958625132149755</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.2432926653653013</v>
+        <v>-0.2820186146759251</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.724133082679402</v>
+        <v>2.700897513093028</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792043</v>
       </c>
       <c r="C1915" t="n">
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.992405296433393</v>
+        <v>-6.311433226107518</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.4702882330220546</v>
+        <v>0.3426770611524046</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.1200015305481708</v>
+        <v>-0.1587274798587946</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.795605857580257</v>
+        <v>2.772370287993883</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919903</v>
       </c>
       <c r="C1916" t="n">
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.939708429302102</v>
+        <v>-6.258736358976226</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.4990679581118962</v>
+        <v>0.3714567862422462</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.06730466341687963</v>
+        <v>-0.1060306127275034</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.834924956096357</v>
+        <v>2.811689386509983</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318092</v>
+        <v>3.748328408318089</v>
       </c>
       <c r="C1917" t="n">
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.695942987318658</v>
+        <v>-6.014970916992782</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.5923548432523247</v>
+        <v>0.4647436713826747</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.06730466341687963</v>
+        <v>-0.1060306127275034</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.830705664443407</v>
+        <v>2.807470094857033</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057524</v>
+        <v>3.824311233057522</v>
       </c>
       <c r="C1918" t="n">
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.606167314942185</v>
+        <v>-5.92519524461631</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6303894261229295</v>
+        <v>0.5027782542532795</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.005705218502569609</v>
+        <v>-0.0444311678131934</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.86978964531201</v>
+        <v>2.846554075725635</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279183</v>
+        <v>3.82635497427918</v>
       </c>
       <c r="C1919" t="n">
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.356316920993111</v>
+        <v>-5.675344850667235</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7230716586862616</v>
+        <v>0.5954604868166116</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.005705218502569609</v>
+        <v>-0.0444311678131934</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.862531720295712</v>
+        <v>2.839296150709337</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011495</v>
+        <v>3.835957987011493</v>
       </c>
       <c r="C1920" t="n">
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.180424828525679</v>
+        <v>-5.499452758199803</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.7970276191938832</v>
+        <v>0.6694164473242332</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.005705218502569609</v>
+        <v>-0.0444311678131934</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.86613084381636</v>
+        <v>2.842895274229986</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392983</v>
+        <v>3.780933911392981</v>
       </c>
       <c r="C1921" t="n">
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.008978365503215</v>
+        <v>-5.32800629517734</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8789337104574222</v>
+        <v>0.7513225385877722</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.1657412445198935</v>
+        <v>0.1270152952092697</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.982326227684392</v>
+        <v>2.959090658098018</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632777</v>
+        <v>3.773765222632775</v>
       </c>
       <c r="C1922" t="n">
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.928956078394094</v>
+        <v>-5.247984008068219</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9099631029173674</v>
+        <v>0.7823519310477178</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.2457635316290145</v>
+        <v>0.2070375823183907</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.029360077566162</v>
+        <v>3.006124507979787</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.76461787988307</v>
+        <v>3.764617879883068</v>
       </c>
       <c r="C1923" t="n">
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.86532033616016</v>
+        <v>-5.184348265834284</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9401122008652585</v>
+        <v>0.8125010289956087</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.309399273862949</v>
+        <v>0.2706733245523252</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.072236323960839</v>
+        <v>3.049000754374465</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074779</v>
+        <v>3.798814771074777</v>
       </c>
       <c r="C1924" t="n">
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.771623017943765</v>
+        <v>-5.090650947617889</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9587853869356122</v>
+        <v>0.8311742150659622</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.309399273862949</v>
+        <v>0.2706733245523252</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.053430582744635</v>
+        <v>3.030195013158261</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.79769488424229</v>
+        <v>3.797694884242288</v>
       </c>
       <c r="C1925" t="n">
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.782125641009054</v>
+        <v>-5.101153570683178</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9563274143343741</v>
+        <v>0.8287162424647243</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.2988966507976601</v>
+        <v>0.2601707014870364</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.048872085530339</v>
+        <v>3.025636515943965</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367679</v>
       </c>
       <c r="C1926" t="n">
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.709883072837859</v>
+        <v>-5.028911002511983</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9891537554376721</v>
+        <v>0.8615425835680224</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.2988966507976601</v>
+        <v>0.2601707014870364</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.052801399365159</v>
+        <v>3.029565829778785</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879961</v>
+        <v>3.822326997879959</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.692169385959994</v>
+        <v>-5.011197315634118</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9969178141061583</v>
+        <v>0.8693066422365083</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.3020779796945769</v>
+        <v>0.2633520303839532</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.055388780620649</v>
+        <v>3.032153211034275</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502333</v>
+        <v>3.848616626502331</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.568695114646975</v>
+        <v>-4.8877230443211</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.043305593851359</v>
+        <v>0.9156944219817091</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.3020779796945769</v>
+        <v>0.2633520303839532</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.052386851840643</v>
+        <v>3.029151282254269</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675935</v>
+        <v>3.818668951675932</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.348674316609965</v>
+        <v>-4.667702246284089</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.132892950076777</v>
+        <v>1.005281778207127</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.4432978247625572</v>
+        <v>0.4045718754519334</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.138697795892045</v>
+        <v>3.115462226305671</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539947</v>
+        <v>3.843274527539943</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.215806627546687</v>
+        <v>-4.534834557220812</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.201934208503912</v>
+        <v>1.074323036634262</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.4432978247625572</v>
+        <v>0.4045718754519334</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.154591978693869</v>
+        <v>3.131356409107494</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496256</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.095633544182189</v>
+        <v>-4.414661473856313</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.251149286290013</v>
+        <v>1.123538114420363</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.5634709081270561</v>
+        <v>0.5247449588164323</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.22784167315287</v>
+        <v>3.204606103566495</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576997</v>
+        <v>3.791273551576993</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.960380182852211</v>
+        <v>-4.279408112526336</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.315338733383444</v>
+        <v>1.187727561513794</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.6987242694570333</v>
+        <v>0.6599983201464095</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.319081792512296</v>
+        <v>3.295846222925921</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942099</v>
       </c>
       <c r="C1933" t="n">
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.020255010209904</v>
+        <v>-4.339282939884028</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.277426293841793</v>
+        <v>1.149815121972143</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.6388494420993411</v>
+        <v>0.6001234927887173</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.269194387499106</v>
+        <v>3.245958817912732</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674513</v>
+        <v>3.762647477674508</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.900434779299066</v>
+        <v>-4.219462708973191</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.340643555440336</v>
+        <v>1.213032383570686</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.6388494420993411</v>
+        <v>0.6001234927887173</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.284483556733315</v>
+        <v>3.261247987146941</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430691</v>
+        <v>3.729146398430688</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.902904485760872</v>
+        <v>-4.221932415434997</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.247299872178055</v>
+        <v>1.119688700308405</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.6363797356375349</v>
+        <v>0.5976537863269111</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.190645932178673</v>
+        <v>3.167410362592299</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003599</v>
+        <v>3.743220196003596</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.971274672084882</v>
+        <v>-4.290302601759008</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.139213659133753</v>
+        <v>1.011602487264103</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.6456554346737499</v>
+        <v>0.6069294853631261</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.115473213085703</v>
+        <v>3.092237643499329</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508367</v>
+        <v>3.714179139508363</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.083146951711033</v>
+        <v>-4.402174881385158</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.084901455915184</v>
+        <v>0.9572902840455337</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.6456554346737499</v>
+        <v>0.6069294853631261</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.105909921717594</v>
+        <v>3.08267435213122</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417702</v>
+        <v>3.710906731417698</v>
       </c>
       <c r="C1938" t="n">
         <v>2.855547497605547</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.138667027603622</v>
+        <v>-4.457694957277748</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.19972426225035</v>
+        <v>1.0721130903807</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.6456554346737499</v>
+        <v>0.6069294853631261</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.242940758409797</v>
+        <v>3.219705188823422</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205896</v>
+        <v>3.746042526205891</v>
       </c>
       <c r="C1939" t="n">
         <v>2.860114729597334</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.963192767811153</v>
+        <v>-4.282220697485279</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.274481198159126</v>
+        <v>1.146870026289476</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.6456554346737499</v>
+        <v>0.6069294853631261</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.247507990401584</v>
+        <v>3.22427242081521</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.76502432322544</v>
+        <v>3.765024323225435</v>
       </c>
       <c r="C1940" t="n">
         <v>2.835856758358541</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.955268393226239</v>
+        <v>-4.274296322900365</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.253392976754299</v>
+        <v>1.125781804884648</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.6456554346737499</v>
+        <v>0.6069294853631261</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.223250019162792</v>
+        <v>3.200014449576417</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111289</v>
       </c>
       <c r="C1941" t="n">
         <v>2.764395071759991</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.94899019065639</v>
+        <v>-4.268018120330516</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.184442571183688</v>
+        <v>1.056831399314038</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.6519336372435989</v>
+        <v>0.6132076879329751</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.155555254106151</v>
+        <v>3.132319684519777</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264159</v>
       </c>
       <c r="C1942" t="n">
         <v>2.774567458192124</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.889137571452667</v>
+        <v>-4.208165501126793</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.21855600529731</v>
+        <v>1.090944833427659</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.6519336372435989</v>
+        <v>0.6132076879329751</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.165727640538283</v>
+        <v>3.142492070951909</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.786949957742295</v>
       </c>
       <c r="C1943" t="n">
         <v>2.769513728765984</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.802894108426289</v>
+        <v>-4.121922038100415</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.247999661081721</v>
+        <v>1.120388489212071</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.6519336372435989</v>
+        <v>0.6132076879329751</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.160673911112144</v>
+        <v>3.137438341525769</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316042</v>
       </c>
       <c r="C1944" t="n">
         <v>2.761289504210509</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.848200927825269</v>
+        <v>-4.167228857499395</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.221652708766654</v>
+        <v>1.094041536897004</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.6111234742343681</v>
+        <v>0.5723975249237443</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.127963588751131</v>
+        <v>3.104728019164756</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803187</v>
       </c>
       <c r="C1945" t="n">
         <v>2.761841377243611</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.877234032527571</v>
+        <v>-4.196261962201696</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.210591339918835</v>
+        <v>1.082980168049185</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.6111234742343681</v>
+        <v>0.5723975249237443</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.128515461784232</v>
+        <v>3.105279892197858</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809498</v>
+        <v>3.733390600809495</v>
       </c>
       <c r="C1946" t="n">
         <v>2.691114069134977</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.784423551076712</v>
+        <v>-4.103451480750836</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.176988224390545</v>
+        <v>1.049377052520895</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.7039339556852274</v>
+        <v>0.6652080063746036</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.113474442546113</v>
+        <v>3.090238872959739</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560425</v>
+        <v>3.748285816560421</v>
       </c>
       <c r="C1947" t="n">
         <v>2.692987545059577</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.828813020406139</v>
+        <v>-4.147840950080264</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.161105912583374</v>
+        <v>1.033494740713725</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.6595444863557998</v>
+        <v>0.620818537045176</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.088714236873058</v>
+        <v>3.065478667286683</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.721077195472732</v>
       </c>
       <c r="C1948" t="n">
         <v>2.6880632535713</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.945354625511482</v>
+        <v>-4.264382555185606</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.10956497905296</v>
+        <v>0.9819538071833107</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.543002881250457</v>
+        <v>0.5042769319398333</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.013864982321575</v>
+        <v>2.990629412735201</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798532</v>
       </c>
       <c r="C1949" t="n">
         <v>2.693554549401968</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.985278720094054</v>
+        <v>-4.304306649768178</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.099086637050599</v>
+        <v>0.9714754651809492</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.543002881250457</v>
+        <v>0.5042769319398333</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.019356278152242</v>
+        <v>2.996120708565868</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498862</v>
+        <v>3.689597840498859</v>
       </c>
       <c r="C1950" t="n">
         <v>2.705051751170507</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.013059117995406</v>
+        <v>-4.332087047669531</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.099471679658597</v>
+        <v>0.9718605077889471</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.5152224833491039</v>
+        <v>0.4764965340384802</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.014185241179969</v>
+        <v>2.990949671593595</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.64306962170532</v>
       </c>
       <c r="C1951" t="n">
         <v>2.54340747117116</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.131439790725545</v>
+        <v>-4.369814938727063</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8904751305671947</v>
+        <v>0.7951250713665876</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.4480046311981277</v>
+        <v>0.4808898562672012</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.812210249890037</v>
+        <v>2.831941384931481</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729266</v>
+        <v>3.682716310729264</v>
       </c>
       <c r="C1952" t="n">
         <v>2.663557131890366</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.240053869168876</v>
+        <v>-4.478429017170394</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.967179159909068</v>
+        <v>0.8718291007084606</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.4480046311981277</v>
+        <v>0.4808898562672012</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.932359910609243</v>
+        <v>2.952091045650687</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190765</v>
+        <v>3.733012441190763</v>
       </c>
       <c r="C1953" t="n">
         <v>2.678070157992689</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.204644830920733</v>
+        <v>-4.443019978922251</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9958558013106482</v>
+        <v>0.9005057421100409</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.4480046311981277</v>
+        <v>0.4808898562672012</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.946872936711566</v>
+        <v>2.96660407175301</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.74117406991342</v>
       </c>
       <c r="C1954" t="n">
         <v>2.675489599335057</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.166261168362582</v>
+        <v>-4.4046363163641</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.008628707676277</v>
+        <v>0.9132786484756701</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.4863882937562789</v>
+        <v>0.5192735188253523</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.967322575588825</v>
+        <v>2.987053710630269</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532484</v>
+        <v>3.75114719753248</v>
       </c>
       <c r="C1955" t="n">
         <v>2.672218628180359</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.989144838327416</v>
+        <v>-4.227519986328934</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.076204268535646</v>
+        <v>0.9808542093350383</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.4863882937562789</v>
+        <v>0.5192735188253523</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.964051604434127</v>
+        <v>2.983782739475571</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793896</v>
       </c>
       <c r="C1956" t="n">
         <v>2.672902019942272</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.034237083160962</v>
+        <v>-4.27261223116248</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.05885076236414</v>
+        <v>0.9635007031635332</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.4244922505868891</v>
+        <v>0.4573774756559625</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.927597370294406</v>
+        <v>2.94732850533585</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011227</v>
       </c>
       <c r="C1957" t="n">
         <v>2.666688995248687</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.854861661922194</v>
+        <v>-4.093236809923712</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.124387906166062</v>
+        <v>1.029037846965455</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.5812690087576078</v>
+        <v>0.6141542338266812</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.015450400503252</v>
+        <v>3.035181535544696</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982227</v>
+        <v>3.716991718982221</v>
       </c>
       <c r="C1958" t="n">
         <v>2.647496450580276</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.8998758754428</v>
+        <v>-4.138251023444319</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.087189676089409</v>
+        <v>0.9918396168888017</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.5509201134430032</v>
+        <v>0.5838053385120766</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.978048518646079</v>
+        <v>2.997779653687523</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509535</v>
+        <v>3.73702660850953</v>
       </c>
       <c r="C1959" t="n">
         <v>2.653188012919222</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.166880385715236</v>
+        <v>-4.405255533716754</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9860794343193806</v>
+        <v>0.8907293751187735</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.3565570754000546</v>
+        <v>0.389442300469128</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.867122258159255</v>
+        <v>2.886853393200699</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.702309454760806</v>
       </c>
       <c r="C1960" t="n">
         <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.268078167152408</v>
+        <v>-4.506453315153927</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9448042436410131</v>
+        <v>0.8494541844404058</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.2881482618547354</v>
+        <v>0.3210334869238088</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.825280891928565</v>
+        <v>2.845012026970009</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815451</v>
       </c>
       <c r="C1961" t="n">
         <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.261567200538096</v>
+        <v>-4.499942348539614</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9450085918410549</v>
+        <v>0.8496585326404476</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.2881482618547354</v>
+        <v>0.3210334869238088</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.822880853482882</v>
+        <v>2.842611988524326</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.709510443378097</v>
       </c>
       <c r="C1962" t="n">
         <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.242529072830798</v>
+        <v>-4.480904220832317</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9491485621322187</v>
+        <v>0.8537985029316113</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.2299646505235409</v>
+        <v>0.2628498755926143</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.78449540589241</v>
+        <v>2.804226540933854</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131244</v>
       </c>
       <c r="C1963" t="n">
         <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.295044875105619</v>
+        <v>-4.533420023107137</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.047436642856481</v>
+        <v>0.9520865836558736</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.2299646505235409</v>
+        <v>0.2628498755926143</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.9037898075266</v>
+        <v>2.923520942568044</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067859</v>
       </c>
       <c r="C1964" t="n">
         <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.308911636439537</v>
+        <v>-4.547286784441055</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.042723267309047</v>
+        <v>0.9473732081084401</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.1921067337897179</v>
+        <v>0.2249919588587914</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.88190838647244</v>
+        <v>2.901639521513884</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789116</v>
       </c>
       <c r="C1965" t="n">
         <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.264107464899607</v>
+        <v>-4.502482612901125</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.066653466321945</v>
+        <v>0.9713034071213378</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.1921067337897179</v>
+        <v>0.2249919588587914</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.887916916869366</v>
+        <v>2.90764805191081</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519902</v>
       </c>
       <c r="C1966" t="n">
         <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.116364494664604</v>
+        <v>-4.354739642666122</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.023700875693146</v>
+        <v>0.9283508164925385</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.3599140910246011</v>
+        <v>0.3927993160936745</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.886551552487496</v>
+        <v>2.90628268752894</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.802245929181163</v>
       </c>
       <c r="C1967" t="n">
         <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.200185715939303</v>
+        <v>-4.438560863940821</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9929660087147472</v>
+        <v>0.89761594951414</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.3599140910246011</v>
+        <v>0.3927993160936745</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.889345174018977</v>
+        <v>2.909076309060421</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394728</v>
+        <v>3.805608985394723</v>
       </c>
       <c r="C1968" t="n">
         <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.194033009886518</v>
+        <v>-4.432408157888037</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9960894395275193</v>
+        <v>0.9007393803269121</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.3660667970773854</v>
+        <v>0.3989520221464588</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.893699146042306</v>
+        <v>2.91343028108375</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890612</v>
+        <v>3.798239794890606</v>
       </c>
       <c r="C1969" t="n">
         <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.21084230803702</v>
+        <v>-4.449217456038538</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9884461970074288</v>
+        <v>0.8930961378068216</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.3492574989268837</v>
+        <v>0.3821427239959572</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.882694043892115</v>
+        <v>2.902425178933559</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798425</v>
+        <v>3.86736263679842</v>
       </c>
       <c r="C1970" t="n">
         <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.148544309260898</v>
+        <v>-4.386919457262416</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.079700950314699</v>
+        <v>0.9843508911140915</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.3945517632013258</v>
+        <v>0.4274369882703992</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.976206156253601</v>
+        <v>2.995937291295045</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.84872913999219</v>
+        <v>3.848729139992185</v>
       </c>
       <c r="C1971" t="n">
         <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.94675411159574</v>
+        <v>-4.185129259597258</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9627090310948889</v>
+        <v>0.8673589718942816</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.5925699553704802</v>
+        <v>0.6254551804395536</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.89730907326922</v>
+        <v>2.917040208310665</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852423</v>
+        <v>3.841444817852419</v>
       </c>
       <c r="C1972" t="n">
         <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.997640824281935</v>
+        <v>-4.236015972283453</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.012644578342586</v>
+        <v>0.917294519141979</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.5416832426842857</v>
+        <v>0.5745684677533591</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.937067277979679</v>
+        <v>2.956798413021123</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319542</v>
+        <v>3.819063300319538</v>
       </c>
       <c r="C1973" t="n">
         <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.911030081632128</v>
+        <v>-4.149405229633646</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.061916611518553</v>
+        <v>0.9665665523179454</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.6203089738894439</v>
+        <v>0.6531941989585174</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.998870452818818</v>
+        <v>3.018601587860262</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489382</v>
+        <v>3.831819032489378</v>
       </c>
       <c r="C1974" t="n">
         <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.971239379637412</v>
+        <v>-4.209614527638931</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.036368873141111</v>
+        <v>0.9410188139405031</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.5600996758841594</v>
+        <v>0.5929849009532329</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.961280854840318</v>
+        <v>2.981011989881763</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397792</v>
+        <v>3.836411672397787</v>
       </c>
       <c r="C1975" t="n">
         <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.922052730953061</v>
+        <v>-4.16042787895458</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.05453515065478</v>
+        <v>0.9591850914541722</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.5600996758841594</v>
+        <v>0.5929849009532329</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.959772472880247</v>
+        <v>2.979503607921691</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316246</v>
+        <v>3.833513460316242</v>
       </c>
       <c r="C1976" t="n">
         <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.877679599314492</v>
+        <v>-4.116054747316011</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.072147270745643</v>
+        <v>0.9767972115450358</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.604472807522728</v>
+        <v>0.6373580325918015</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.986259219298824</v>
+        <v>3.005990354340268</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105965</v>
+        <v>3.821562117105961</v>
       </c>
       <c r="C1977" t="n">
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.900159950173377</v>
+        <v>-4.138535098174896</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.05754892454068</v>
+        <v>0.9621988653400724</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.604472807522728</v>
+        <v>0.6373580325918015</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.980653013437415</v>
+        <v>3.000384148478859</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190323</v>
+        <v>3.833011148190319</v>
       </c>
       <c r="C1978" t="n">
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.852504219612321</v>
+        <v>-4.09087936761384</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.082992973792907</v>
+        <v>0.9876429145922994</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.6521285380837837</v>
+        <v>0.6850137631528571</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.015628208801853</v>
+        <v>3.035359343843297</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569616</v>
+        <v>3.822678210569611</v>
       </c>
       <c r="C1979" t="n">
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.751986061113566</v>
+        <v>-3.990361209115085</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.128092610567134</v>
+        <v>1.032742551366526</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.7526466965825382</v>
+        <v>0.7855319216516117</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.080831477275831</v>
+        <v>3.100562612317275</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557292</v>
+        <v>3.828808877557288</v>
       </c>
       <c r="C1980" t="n">
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.736080731681214</v>
+        <v>-3.974455879682733</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.121209414815947</v>
+        <v>1.025859355615339</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.6735340358732993</v>
+        <v>0.7064192609423727</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.02011855332616</v>
+        <v>3.039849688367604</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932767</v>
+        <v>3.816837033932763</v>
       </c>
       <c r="C1981" t="n">
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.691242330072816</v>
+        <v>-3.929617478074335</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.143242478069935</v>
+        <v>1.047892418869327</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.6780774688181688</v>
+        <v>0.7109626938872422</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.02694231570371</v>
+        <v>3.046673450745154</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.817932354917045</v>
       </c>
       <c r="C1982" t="n">
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.710740786314824</v>
+        <v>-3.949115934316343</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.139604035204209</v>
+        <v>1.044253976003602</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.6299928275382645</v>
+        <v>0.6628780526073379</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.002252470566845</v>
+        <v>3.021983605608289</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405954</v>
       </c>
       <c r="C1983" t="n">
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.666537949228923</v>
+        <v>-3.904913097230442</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.163164772566407</v>
+        <v>1.067814713365799</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.6741956646241649</v>
+        <v>0.7070808896932383</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.034653775346222</v>
+        <v>3.054384910387667</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265643</v>
+        <v>3.838199629265638</v>
       </c>
       <c r="C1984" t="n">
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.67409761506597</v>
+        <v>-3.863999895280393</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.158550906700835</v>
+        <v>1.082589994615067</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.7289990686339842</v>
+        <v>0.7810472685974298</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.065945818221362</v>
+        <v>3.097174738199429</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.863895080284873</v>
       </c>
       <c r="C1985" t="n">
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.515806197526698</v>
+        <v>-3.70570847774112</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.273115238899584</v>
+        <v>1.197154326813815</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.7289990686339842</v>
+        <v>0.7810472685974298</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.117193583404402</v>
+        <v>3.148422503382469</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321017</v>
       </c>
       <c r="C1986" t="n">
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.308164193892222</v>
+        <v>-3.498066474106644</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.354612744947628</v>
+        <v>1.278651832861859</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.9366410722684604</v>
+        <v>0.9886892722319058</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.24021949017934</v>
+        <v>3.271448410157408</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475133</v>
       </c>
       <c r="C1987" t="n">
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.257132101169694</v>
+        <v>-3.447034381384116</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.369973810274909</v>
+        <v>1.29401289818914</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.9876731649909883</v>
+        <v>1.039721364954434</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.265786974051127</v>
+        <v>3.297015894029194</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.842547360404848</v>
       </c>
       <c r="C1988" t="n">
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.191907920042488</v>
+        <v>-3.38181020025691</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.413250886818496</v>
+        <v>1.337289974732727</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.052897346118194</v>
+        <v>1.10494554608164</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.322108886820155</v>
+        <v>3.353337806798223</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882555</v>
+        <v>3.840061186882551</v>
       </c>
       <c r="C1989" t="n">
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.154480899971354</v>
+        <v>-3.344383180185777</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.42418266714623</v>
+        <v>1.348221755060461</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.058148884147375</v>
+        <v>1.110197084110821</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.321220781936944</v>
+        <v>3.352449701915012</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992658</v>
+        <v>3.845169808992654</v>
       </c>
       <c r="C1990" t="n">
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.174592556006063</v>
+        <v>-3.364494836220485</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.417394797063587</v>
+        <v>1.341433884977818</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.069176229144795</v>
+        <v>1.12122442910824</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.329093981266636</v>
+        <v>3.360322901244704</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636285</v>
+        <v>3.82866144563628</v>
       </c>
       <c r="C1991" t="n">
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.146179292906179</v>
+        <v>-3.336081573120601</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.589317873324751</v>
+        <v>1.513356961238982</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.010200666398366</v>
+        <v>1.062248866361812</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.45426641463999</v>
+        <v>3.485495334618057</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957623</v>
+        <v>3.813222820957619</v>
       </c>
       <c r="C1992" t="n">
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.071397031881166</v>
+        <v>-3.261299312095589</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.739343686952574</v>
+        <v>1.663382774866805</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.084982927423378</v>
+        <v>1.137031127386824</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.619248680472815</v>
+        <v>3.650477600450882</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998754</v>
+        <v>3.81423072799875</v>
       </c>
       <c r="C1993" t="n">
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.045312947617358</v>
+        <v>-3.235215227831781</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.741485296671956</v>
+        <v>1.665524384586187</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.084982927423378</v>
+        <v>1.137031127386824</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.610956656486674</v>
+        <v>3.642185576464741</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896924</v>
       </c>
       <c r="C1994" t="n">
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.957435034508238</v>
+        <v>-3.14733731472266</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.774829657499383</v>
+        <v>1.698868745413614</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.200908569846729</v>
+        <v>1.252956769810175</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.678705237524464</v>
+        <v>3.709934157502531</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959856</v>
+        <v>3.796264143959852</v>
       </c>
       <c r="C1995" t="n">
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.948542573114954</v>
+        <v>-3.138444853329377</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.795941047783488</v>
+        <v>1.719980135697719</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.200908569846729</v>
+        <v>1.252956769810175</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.696259643251255</v>
+        <v>3.727488563229322</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945365</v>
+        <v>3.794424941945361</v>
       </c>
       <c r="C1996" t="n">
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.117018690084832</v>
+        <v>-3.128159887974516</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.720405648400121</v>
+        <v>1.715949169244247</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.172960734130149</v>
+        <v>1.319541058012167</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.671345989225891</v>
+        <v>3.759294183555101</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782704</v>
       </c>
       <c r="C1997" t="n">
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.670762497455392</v>
+        <v>-2.681903695345076</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.880177822639759</v>
+        <v>1.875721343483885</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.078242064460516</v>
+        <v>1.224822388342534</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.595784484611973</v>
+        <v>3.683732678941184</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632635</v>
+        <v>3.784671345632632</v>
       </c>
       <c r="C1998" t="n">
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.64804139377224</v>
+        <v>-2.659182591661923</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.879930286609924</v>
+        <v>1.875473807454051</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.078242064460516</v>
+        <v>1.224822388342534</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.586448507108877</v>
+        <v>3.674396701438088</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777672</v>
+        <v>3.783205696777668</v>
       </c>
       <c r="C1999" t="n">
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.777243207066282</v>
+        <v>-2.788384404955966</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.987155687143476</v>
+        <v>1.982699207987603</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.9490402511664737</v>
+        <v>1.095620575048492</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.667833544983621</v>
+        <v>3.755781739312832</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644411</v>
+        <v>3.779933725644407</v>
       </c>
       <c r="C2000" t="n">
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.803117605540308</v>
+        <v>-2.814258803429992</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.013883750247513</v>
+        <v>2.009427271091639</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.9939518598782149</v>
+        <v>1.140532183760233</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.731858332704312</v>
+        <v>3.819806527033523</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799963</v>
+        <v>3.76944361979996</v>
       </c>
       <c r="C2001" t="n">
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.796062915325134</v>
+        <v>-2.807204113214818</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.013380982323127</v>
+        <v>2.008924503167254</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.001006550093389</v>
+        <v>1.147586873975407</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.732766502822962</v>
+        <v>3.820714697152173</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331115</v>
+        <v>3.766673496331112</v>
       </c>
       <c r="C2002" t="n">
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.769111690998646</v>
+        <v>-2.78025288888833</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.034167625698464</v>
+        <v>2.02971114654259</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.015886896121108</v>
+        <v>1.162467220003126</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.751700864084335</v>
+        <v>3.839649058413546</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784106</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.905064699054963</v>
+        <v>-2.916205896944646</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.163889554620897</v>
+        <v>2.159433075465023</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.015886896121108</v>
+        <v>1.162467220003126</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.935803996229295</v>
+        <v>4.023752190558505</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714424</v>
+        <v>3.743925505714422</v>
       </c>
       <c r="C2004" t="n">
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.927472816859835</v>
+        <v>-2.938614014749518</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.147043002401942</v>
+        <v>2.142586523246068</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.015886896121108</v>
+        <v>1.162467220003126</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.927920691132288</v>
+        <v>4.015868885461498</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.71911862715503</v>
+        <v>3.719118627155028</v>
       </c>
       <c r="C2005" t="n">
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.955697052437435</v>
+        <v>-2.966838250327119</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.137807307720539</v>
+        <v>2.133350828564665</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.033863648572416</v>
+        <v>1.180443972454434</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.94076074215271</v>
+        <v>4.028708936481921</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161974</v>
+        <v>3.729452285161972</v>
       </c>
       <c r="C2006" t="n">
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.965137978325965</v>
+        <v>-2.976279176215649</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.190284655086974</v>
+        <v>2.185828175931101</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.156290766115808</v>
+        <v>1.302871089997826</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.070470730400592</v>
+        <v>4.158418924729803</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321631</v>
+        <v>3.714941193321629</v>
       </c>
       <c r="C2007" t="n">
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-3.017411585661606</v>
+        <v>-3.02855278355129</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.172266306698019</v>
+        <v>2.167809827542145</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.104017158780167</v>
+        <v>1.250597482662184</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.041997660544508</v>
+        <v>4.129945854873719</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347701</v>
+        <v>3.7278981863477</v>
       </c>
       <c r="C2008" t="n">
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.093741563262512</v>
+        <v>-3.104882761152196</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.139846128551431</v>
+        <v>2.135389649395558</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.104017158780167</v>
+        <v>1.250597482662184</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.040109473438283</v>
+        <v>4.128057667767494</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887746</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.187405507940054</v>
+        <v>-3.198546705829737</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.097200780283277</v>
+        <v>2.092744301127404</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.010353214102625</v>
+        <v>1.156933537984643</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.978731336234621</v>
+        <v>4.066679530563832</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343065</v>
+        <v>3.712897612343063</v>
       </c>
       <c r="C2010" t="n">
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.348973933467309</v>
+        <v>-3.360115131356992</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.031007420282527</v>
+        <v>2.026550941126654</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.8835702903047459</v>
+        <v>1.030150614186764</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.901095592166046</v>
+        <v>3.989043786495256</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389347</v>
+        <v>3.754596135389345</v>
       </c>
       <c r="C2011" t="n">
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.457274595337428</v>
+        <v>-3.468415793227112</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.000760562400398</v>
+        <v>1.996304083244524</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.8835702903047459</v>
+        <v>1.030150614186764</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.914168999031965</v>
+        <v>4.002117193361175</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74988269137839</v>
+        <v>3.749882691378389</v>
       </c>
       <c r="C2012" t="n">
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.550422066640795</v>
+        <v>-3.561563264530478</v>
       </c>
       <c r="E2012" t="n">
-        <v>1.955506770661991</v>
+        <v>1.951050291506118</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7607410790222131</v>
+        <v>0.9073214029042308</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.832476669045385</v>
+        <v>3.920424863374596</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006974</v>
+        <v>3.715819895006972</v>
       </c>
       <c r="C2013" t="n">
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.578322853750268</v>
+        <v>-3.589464051639951</v>
       </c>
       <c r="E2013" t="n">
-        <v>1.942870496945204</v>
+        <v>1.938414017789331</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7261441548792783</v>
+        <v>0.872724478761296</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.810242555686626</v>
+        <v>3.898190750015837</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787386</v>
+        <v>3.684895778787384</v>
       </c>
       <c r="C2014" t="n">
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.700848956453162</v>
+        <v>-3.711990154342845</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.890624499841245</v>
+        <v>1.886168020685372</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.6036180521763844</v>
+        <v>0.7501983760584021</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.733491338042088</v>
+        <v>3.821439532371299</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585937</v>
+        <v>3.619348081585934</v>
       </c>
       <c r="C2015" t="n">
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.931363452638751</v>
+        <v>-3.942504650528434</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.865124660957513</v>
+        <v>1.86066818180164</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.3731035559907957</v>
+        <v>0.5196838798728134</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.661888599921239</v>
+        <v>3.749836794250449</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814664</v>
+        <v>3.640750087814663</v>
       </c>
       <c r="C2016" t="n">
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.280108537863194</v>
+        <v>-4.291249735752878</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.865938345869583</v>
+        <v>1.86148186671371</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.2643556020718979</v>
+        <v>0.4109359259539156</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.736951546571747</v>
+        <v>3.824899740900958</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.434094955639335</v>
+        <v>-4.445236153529018</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.873324047904767</v>
+        <v>1.868867568748893</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.2643556020718979</v>
+        <v>0.4109359259539156</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.805931815717387</v>
+        <v>3.893880010046598</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.383573051811669</v>
+        <v>-4.394714249701352</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.879584011555954</v>
+        <v>1.87512753240008</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.2643556020718979</v>
+        <v>0.4109359259539156</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.791983017837508</v>
+        <v>3.879931212166718</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.636048205819393</v>
+        <v>-4.647189403709077</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.790464439008278</v>
+        <v>1.786007959852405</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.2643556020718979</v>
+        <v>0.4109359259539156</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.803853506892922</v>
+        <v>3.891801701222132</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973156</v>
+        <v>3.674028535973155</v>
       </c>
       <c r="C2020" t="n">
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.928943962298805</v>
+        <v>-4.940085160188489</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.674516670935457</v>
+        <v>1.670060191779584</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.2643556020718979</v>
+        <v>0.4109359259539156</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.805064041411865</v>
+        <v>3.893012235741076</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251945</v>
+        <v>3.663509457251943</v>
       </c>
       <c r="C2021" t="n">
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-5.115608090433613</v>
+        <v>-5.126749288323297</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.603972761908855</v>
+        <v>1.599516282752982</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.237616631247338</v>
+        <v>0.3841969551293557</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.793142401144451</v>
+        <v>3.881090595473661</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.6521491529162</v>
+        <v>3.652149152916199</v>
       </c>
       <c r="C2022" t="n">
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.261628777347576</v>
+        <v>-5.272769975237259</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.54064233987946</v>
+        <v>1.536185860723586</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.228533539453481</v>
+        <v>0.3751138633354987</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.782770398804326</v>
+        <v>3.870718593133537</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830327</v>
+        <v>3.667962306830326</v>
       </c>
       <c r="C2023" t="n">
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.35334278645716</v>
+        <v>-5.364483984346844</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.66616079293467</v>
+        <v>1.661704313778797</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.228533539453481</v>
+        <v>0.3751138633354987</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.94497445550337</v>
+        <v>4.032922649832581</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071549</v>
+        <v>3.696539468071548</v>
       </c>
       <c r="C2024" t="n">
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.38499444551713</v>
+        <v>-5.396135643406813</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.648346767274496</v>
+        <v>1.643890288118623</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.2233650822090408</v>
+        <v>0.3699454060910585</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.93672001912052</v>
+        <v>4.024668213449731</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868144</v>
+        <v>3.750044015868143</v>
       </c>
       <c r="C2025" t="n">
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.466929263786013</v>
+        <v>-5.478070461675697</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.625802257535434</v>
+        <v>1.621345778379561</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.2134303366219606</v>
+        <v>0.3600106605039783</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.940988589336763</v>
+        <v>4.028936783665974</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332689</v>
+        <v>3.783632867332688</v>
       </c>
       <c r="C2026" t="n">
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.56890538603442</v>
+        <v>-5.580046583924104</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.593937447091974</v>
+        <v>1.5894809679361</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.1114542143735531</v>
+        <v>0.2580345382555708</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.888728554443621</v>
+        <v>3.976676748772832</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231806</v>
+        <v>3.798296784231805</v>
       </c>
       <c r="C2027" t="n">
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.458899102557199</v>
+        <v>-5.470040300446882</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.630092847727038</v>
+        <v>1.625636368571164</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.1346587862908283</v>
+        <v>0.281239110172846</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.894804184838162</v>
+        <v>3.982752379167373</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.78556392481852</v>
+        <v>3.785563924818519</v>
       </c>
       <c r="C2028" t="n">
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.315839526816273</v>
+        <v>-5.326980724705956</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.691566688745382</v>
+        <v>1.687110209589509</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.1426722128808076</v>
+        <v>0.2892525367628253</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.903862251514123</v>
+        <v>3.991810445843334</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051786</v>
+        <v>3.777237412051785</v>
       </c>
       <c r="C2029" t="n">
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-5.014392801344435</v>
+        <v>-5.025533999234119</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.819406261816654</v>
+        <v>1.81494978266078</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.4441189383526448</v>
+        <v>0.5906992622346625</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.091991169679762</v>
+        <v>4.179939364008972</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679623</v>
+        <v>3.812635940679622</v>
       </c>
       <c r="C2030" t="n">
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-5.038983045579619</v>
+        <v>-5.050124243469303</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.81054134187529</v>
+        <v>1.806084862719417</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.4441189383526448</v>
+        <v>0.5906992622346625</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.092962347432472</v>
+        <v>4.180910541761683</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474157</v>
+        <v>3.821184182474156</v>
       </c>
       <c r="C2031" t="n">
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.987944669573099</v>
+        <v>-4.999085867462782</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.831799596657654</v>
+        <v>1.827343117501781</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.4441189383526448</v>
+        <v>0.5906992622346625</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.093805251812228</v>
+        <v>4.181753446141439</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969541</v>
+        <v>3.83173451696954</v>
       </c>
       <c r="C2032" t="n">
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.946805374706468</v>
+        <v>-4.957946572596152</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.867293413478452</v>
+        <v>1.862836934322579</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.4852582332192756</v>
+        <v>0.6318385571012933</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.137526927606352</v>
+        <v>4.225475121935562</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700476</v>
+        <v>3.825752932700475</v>
       </c>
       <c r="C2033" t="n">
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.850170462687828</v>
+        <v>-4.861311660577512</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.722131374409843</v>
+        <v>1.717674895253969</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.5818931452379156</v>
+        <v>0.7284734691199333</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.011691870941471</v>
+        <v>4.099640065270681</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077638</v>
+        <v>3.804688961077637</v>
       </c>
       <c r="C2034" t="n">
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.98075119721867</v>
+        <v>-4.991892395108354</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.67340112467147</v>
+        <v>1.668944645515596</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.4513124107070731</v>
+        <v>0.5978927345890908</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.936845474296929</v>
+        <v>4.02479366862614</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833457</v>
+        <v>3.775028860833455</v>
       </c>
       <c r="C2035" t="n">
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.816254863027709</v>
+        <v>-4.827396060917392</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.723626477423937</v>
+        <v>1.719169998268063</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.6158087448980349</v>
+        <v>0.7623890687800526</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.019970093887589</v>
+        <v>4.107918288216799</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077628</v>
+        <v>3.821030660077626</v>
       </c>
       <c r="C2036" t="n">
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.843624795712141</v>
+        <v>-4.854765993601824</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.711866214786594</v>
+        <v>1.70740973563072</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.6158087448980349</v>
+        <v>0.7623890687800526</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.019157804324019</v>
+        <v>4.107105998653229</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147909</v>
+        <v>3.832307024147907</v>
       </c>
       <c r="C2037" t="n">
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.85400999060203</v>
+        <v>-4.865151188491714</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.71758091595571</v>
+        <v>1.713124436799837</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.6054235500081456</v>
+        <v>0.7520038738901633</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.022795466515158</v>
+        <v>4.110743660844368</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.83441549373528</v>
+        <v>3.834415493735277</v>
       </c>
       <c r="C2038" t="n">
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.872598149324255</v>
+        <v>-4.883739347213939</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.780982658243246</v>
+        <v>1.776526179087372</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.5868353912859203</v>
+        <v>0.7334157151679379</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.082479577058248</v>
+        <v>4.170427771387458</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496553</v>
+        <v>3.855120535496551</v>
       </c>
       <c r="C2039" t="n">
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.872896696020291</v>
+        <v>-4.884037893909975</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.77773225038313</v>
+        <v>1.773275771227256</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.5865368445898844</v>
+        <v>0.733117168471902</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.079169459858925</v>
+        <v>4.167117654188135</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108856</v>
+        <v>3.815643212108853</v>
       </c>
       <c r="C2040" t="n">
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.772073562329863</v>
+        <v>-4.783214760219547</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.822592398798692</v>
+        <v>1.818135919642819</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.5990010600742383</v>
+        <v>0.7455813839562558</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.091178884088928</v>
+        <v>4.179127078418139</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121466</v>
+        <v>3.807356168121462</v>
       </c>
       <c r="C2041" t="n">
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.581292201577456</v>
+        <v>-4.59243339946714</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.899034196578198</v>
+        <v>1.894577717422325</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.7897824208266456</v>
+        <v>0.9363627447086632</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.205776954018916</v>
+        <v>4.293725148348126</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906079</v>
+        <v>3.775233033906075</v>
       </c>
       <c r="C2042" t="n">
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.474328843728035</v>
+        <v>-4.485470041617718</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.921656385455563</v>
+        <v>1.91719990629969</v>
       </c>
       <c r="F2042" t="n">
-        <v>0.8482470287864471</v>
+        <v>0.9948273526684646</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.220692564532393</v>
+        <v>4.308640758861603</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912984</v>
+        <v>3.785761685912981</v>
       </c>
       <c r="C2043" t="n">
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.418998255826272</v>
+        <v>-4.430139453715956</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.978755557228327</v>
+        <v>1.974299078072454</v>
       </c>
       <c r="F2043" t="n">
-        <v>0.9035776166882092</v>
+        <v>1.050157940570227</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.288857853885509</v>
+        <v>4.37680604821472</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539894</v>
+        <v>3.74376795653989</v>
       </c>
       <c r="C2044" t="n">
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.40694412891331</v>
+        <v>-4.418085326802993</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.97726377589495</v>
+        <v>1.972807296739076</v>
       </c>
       <c r="F2044" t="n">
-        <v>0.9156317436011721</v>
+        <v>1.062212067483189</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.289776897934725</v>
+        <v>4.377725092263935</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811008</v>
+        <v>3.725010844811004</v>
       </c>
       <c r="C2045" t="n">
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.44809924848153</v>
+        <v>-4.459240446371214</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.962682358251797</v>
+        <v>1.958225879095924</v>
       </c>
       <c r="F2045" t="n">
-        <v>0.8744766240329511</v>
+        <v>1.021056947914968</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.266964456377927</v>
+        <v>4.354912650707139</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382919</v>
+        <v>3.612322444382915</v>
       </c>
       <c r="C2046" t="n">
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.380050685790001</v>
+        <v>-4.391191883679684</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.002752809206291</v>
+        <v>1.998296330050418</v>
       </c>
       <c r="F2046" t="n">
-        <v>0.9425251867244809</v>
+        <v>1.089105510606498</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.320644619870728</v>
+        <v>4.408592814199938</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.646857607760315</v>
+        <v>3.646857607760311</v>
       </c>
       <c r="C2047" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.611651078959501</v>
+        <v>-4.622792276849185</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.930315322112086</v>
+        <v>1.925858842956212</v>
       </c>
       <c r="F2047" t="n">
-        <v>0.9425251867244809</v>
+        <v>1.089105510606498</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.340847290044322</v>
+        <v>4.428795484373532</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666767386781705</v>
+        <v>3.666767386781701</v>
       </c>
       <c r="C2048" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.629723587251113</v>
+        <v>-4.640864785140796</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.923086318795441</v>
+        <v>1.918629839639568</v>
       </c>
       <c r="F2048" t="n">
-        <v>0.9425251867244809</v>
+        <v>1.089105510606498</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.340847290044322</v>
+        <v>4.428795484373532</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670068888082834</v>
+        <v>3.67006888808283</v>
       </c>
       <c r="C2049" t="n">
         <v>3.7355840916031</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.804830419827558</v>
+        <v>-4.815971617717242</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.813295499358329</v>
+        <v>1.808839020202456</v>
       </c>
       <c r="F2049" t="n">
-        <v>0.9425251867244809</v>
+        <v>1.089105510606498</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.301099203637789</v>
+        <v>4.389047397966999</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745593333943585</v>
+        <v>3.745593333943582</v>
       </c>
       <c r="C2050" t="n">
         <v>3.74260671060004</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.773544399287103</v>
+        <v>-4.784685597176787</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.832832526571452</v>
+        <v>1.828376047415578</v>
       </c>
       <c r="F2050" t="n">
-        <v>0.9738112072649363</v>
+        <v>1.120391531146954</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.326893434959002</v>
+        <v>4.414841629288213</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730590658677823</v>
+        <v>3.730590658677819</v>
       </c>
       <c r="C2051" t="n">
         <v>3.841777710172944</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.620519007173819</v>
+        <v>-4.631660205063502</v>
       </c>
       <c r="E2051" t="n">
-        <v>1.99321368298967</v>
+        <v>1.988757203833796</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.12683659937822</v>
+        <v>1.273416923260238</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.517879669799877</v>
+        <v>4.605827864129087</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741298518073883</v>
+        <v>3.74129851807388</v>
       </c>
       <c r="C2052" t="n">
         <v>4.029243935081237</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.614591320471618</v>
+        <v>-4.659967518936773</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.183050982578842</v>
+        <v>2.16490050319278</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.12683659937822</v>
+        <v>1.273416923260238</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.705345894708169</v>
+        <v>4.79329408903738</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699135800903168</v>
+        <v>3.699135800903165</v>
       </c>
       <c r="C2053" t="n">
         <v>3.998646886435319</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.78118454558514</v>
+        <v>-4.826560744050295</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.085816643887515</v>
+        <v>2.067666164501453</v>
       </c>
       <c r="F2053" t="n">
-        <v>0.9602433742646979</v>
+        <v>1.106823698146715</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.574792910994137</v>
+        <v>4.662741105323348</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708202704568382</v>
+        <v>3.708202704568379</v>
       </c>
       <c r="C2054" t="n">
         <v>4.002323289097037</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.60812016620284</v>
+        <v>-4.653496364667995</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.158718798302153</v>
+        <v>2.140568318916091</v>
       </c>
       <c r="F2054" t="n">
-        <v>0.9602433742646979</v>
+        <v>1.106823698146715</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.578469313655855</v>
+        <v>4.666417507985066</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740601586682204</v>
+        <v>3.7406015866822</v>
       </c>
       <c r="C2055" t="n">
         <v>3.999941344220532</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.578874185747144</v>
+        <v>-4.624250384212298</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.168035245607927</v>
+        <v>2.149884766221865</v>
       </c>
       <c r="F2055" t="n">
-        <v>0.9602433742646979</v>
+        <v>1.106823698146715</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.57608736877935</v>
+        <v>4.664035563108561</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699424827539107</v>
+        <v>3.699424827539103</v>
       </c>
       <c r="C2056" t="n">
         <v>3.997234583378167</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.685799733624995</v>
+        <v>-4.731175932090149</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.122558265614422</v>
+        <v>2.10440778622836</v>
       </c>
       <c r="F2056" t="n">
-        <v>0.8533178263868465</v>
+        <v>0.999898150268864</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.509225279210275</v>
+        <v>4.597173473539486</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689962785983737</v>
+        <v>3.689962785983733</v>
       </c>
       <c r="C2057" t="n">
         <v>3.998663385521401</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.830818292132244</v>
+        <v>-4.876194490597398</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.065979644354757</v>
+        <v>2.047829164968695</v>
       </c>
       <c r="F2057" t="n">
-        <v>0.708299267879598</v>
+        <v>0.8548795917616154</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.42364294624916</v>
+        <v>4.51159114057837</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711872614969749</v>
+        <v>3.711872614969744</v>
       </c>
       <c r="C2058" t="n">
         <v>4.098594624779154</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.949160057916961</v>
+        <v>-4.994536256382116</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.118574177298623</v>
+        <v>2.100423697912561</v>
       </c>
       <c r="F2058" t="n">
-        <v>0.718985306442488</v>
+        <v>0.8655656303245055</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.529985808644647</v>
+        <v>4.617934002973858</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714899237073539</v>
+        <v>3.714899237073534</v>
       </c>
       <c r="C2059" t="n">
         <v>4.096380321905093</v>
       </c>
       <c r="D2059" t="n">
-        <v>-5.000570480237669</v>
+        <v>-5.045946678702824</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.095795705496278</v>
+        <v>2.077645226110216</v>
       </c>
       <c r="F2059" t="n">
-        <v>0.718985306442488</v>
+        <v>0.8655656303245055</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.527771505770586</v>
+        <v>4.615719700099796</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704778134720066</v>
+        <v>3.704778134720062</v>
       </c>
       <c r="C2060" t="n">
         <v>4.096283449979382</v>
       </c>
       <c r="D2060" t="n">
-        <v>-5.079989931445421</v>
+        <v>-5.125366129910575</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.063931053087467</v>
+        <v>2.045780573701405</v>
       </c>
       <c r="F2060" t="n">
-        <v>0.718985306442488</v>
+        <v>0.8655656303245055</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.527674633844875</v>
+        <v>4.615622828174086</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736825137581134</v>
+        <v>3.736825137581129</v>
       </c>
       <c r="C2061" t="n">
         <v>4.096277343537426</v>
       </c>
       <c r="D2061" t="n">
-        <v>-5.175452929362638</v>
+        <v>-5.220829127827793</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.025739747478623</v>
+        <v>2.007589268092561</v>
       </c>
       <c r="F2061" t="n">
-        <v>0.718985306442488</v>
+        <v>0.8655656303245055</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.527668527402919</v>
+        <v>4.615616721732129</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715393145500736</v>
+        <v>3.715393145500731</v>
       </c>
       <c r="C2062" t="n">
         <v>4.094373740100036</v>
       </c>
       <c r="D2062" t="n">
-        <v>-5.215472927406422</v>
+        <v>-5.260849125871577</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.007828144823721</v>
+        <v>1.989677665437659</v>
       </c>
       <c r="F2062" t="n">
-        <v>0.6789653083987042</v>
+        <v>0.8255456322807218</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.501752925139259</v>
+        <v>4.58970111946847</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736109598636271</v>
+        <v>3.736109598636267</v>
       </c>
       <c r="C2063" t="n">
         <v>4.100107557847763</v>
       </c>
       <c r="D2063" t="n">
-        <v>-5.270842089538616</v>
+        <v>-5.31621828800377</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.99141429771857</v>
+        <v>1.973263818332508</v>
       </c>
       <c r="F2063" t="n">
-        <v>0.6789653083987042</v>
+        <v>0.8255456322807218</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.507486742886986</v>
+        <v>4.595434937216196</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736843055396014</v>
+        <v>3.73684305539601</v>
       </c>
       <c r="C2064" t="n">
         <v>4.099645921190696</v>
       </c>
       <c r="D2064" t="n">
-        <v>-5.316279869369443</v>
+        <v>-5.361656067834597</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.972777549129172</v>
+        <v>1.95462706974311</v>
       </c>
       <c r="F2064" t="n">
-        <v>0.6361203177205446</v>
+        <v>0.7827006416025621</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.481318111823023</v>
+        <v>4.569266306152233</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790292685396423</v>
+        <v>3.790292685396419</v>
       </c>
       <c r="C2065" t="n">
         <v>4.119520314041015</v>
       </c>
       <c r="D2065" t="n">
-        <v>-5.228073035221865</v>
+        <v>-5.273449233687019</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.027934675638522</v>
+        <v>2.00978419625246</v>
       </c>
       <c r="F2065" t="n">
-        <v>0.6361203177205446</v>
+        <v>0.7827006416025621</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.501192504673342</v>
+        <v>4.589140699002552</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794507029299177</v>
+        <v>3.794507029299172</v>
       </c>
       <c r="C2066" t="n">
         <v>4.103221014565743</v>
       </c>
       <c r="D2066" t="n">
-        <v>-5.051782810616557</v>
+        <v>-5.097159009081712</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.082151466005373</v>
+        <v>2.064000986619311</v>
       </c>
       <c r="F2066" t="n">
-        <v>0.6361203177205446</v>
+        <v>0.7827006416025621</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.48489320519807</v>
+        <v>4.57284139952728</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794725278590408</v>
+        <v>3.794725278590404</v>
       </c>
       <c r="C2067" t="n">
         <v>4.105651964029788</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.868571147483462</v>
+        <v>-4.913947345948617</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.157867080722657</v>
+        <v>2.139716601336595</v>
       </c>
       <c r="F2067" t="n">
-        <v>0.6361203177205446</v>
+        <v>0.7827006416025621</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.487324154662115</v>
+        <v>4.575272348991326</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776866743146287</v>
+        <v>3.776866743146284</v>
       </c>
       <c r="C2068" t="n">
         <v>4.071443149877678</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.799292375071952</v>
+        <v>-4.842225898934766</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.15136977553515</v>
+        <v>2.134196365990024</v>
       </c>
       <c r="F2068" t="n">
-        <v>0.7053990901320553</v>
+        <v>0.8544220886164128</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.494682603956911</v>
+        <v>4.584096403047526</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723809890676849</v>
+        <v>3.723809890676845</v>
       </c>
       <c r="C2069" t="n">
         <v>4.018358895798849</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.928671157711729</v>
+        <v>-4.971604681574544</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.04653400840041</v>
+        <v>2.029360598855285</v>
       </c>
       <c r="F2069" t="n">
-        <v>0.663297317424852</v>
+        <v>0.8123203159092094</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.416337286253761</v>
+        <v>4.505751085344375</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715627631739466</v>
+        <v>3.715627631739462</v>
       </c>
       <c r="C2070" t="n">
         <v>4.203557100684205</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.961687453622474</v>
+        <v>-5.004620977485288</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.218525694921468</v>
+        <v>2.201352285376342</v>
       </c>
       <c r="F2070" t="n">
-        <v>0.5938599407581004</v>
+        <v>0.7428829392424579</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.559873065139065</v>
+        <v>4.64928686422968</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713782722166412</v>
+        <v>3.713782722166409</v>
       </c>
       <c r="C2071" t="n">
         <v>4.195478326512454</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.950159817972866</v>
+        <v>-4.99309334183568</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.21505797500956</v>
+        <v>2.197884565464435</v>
       </c>
       <c r="F2071" t="n">
-        <v>0.6528605989594629</v>
+        <v>0.8018835974438203</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.587194685888132</v>
+        <v>4.676608484978747</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717170884519033</v>
+        <v>3.717170884519029</v>
       </c>
       <c r="C2072" t="n">
         <v>4.199146439034243</v>
       </c>
       <c r="D2072" t="n">
-        <v>-5.047501319315234</v>
+        <v>-5.090434843178048</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.179789486994402</v>
+        <v>2.162616077449276</v>
       </c>
       <c r="F2072" t="n">
-        <v>0.6084404167939745</v>
+        <v>0.7574634152783319</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.564210689110627</v>
+        <v>4.653624488201242</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705221264710419</v>
+        <v>3.705221264710415</v>
       </c>
       <c r="C2073" t="n">
         <v>4.200397521227081</v>
       </c>
       <c r="D2073" t="n">
-        <v>-5.133357348655201</v>
+        <v>-5.176290872518015</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.146698157451253</v>
+        <v>2.129524747906128</v>
       </c>
       <c r="F2073" t="n">
-        <v>0.5660643475678395</v>
+        <v>0.7150873460521969</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.540036129767785</v>
+        <v>4.629449928858399</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691855684893114</v>
+        <v>3.691855684893113</v>
       </c>
       <c r="C2074" t="n">
         <v>4.182816723047583</v>
       </c>
       <c r="D2074" t="n">
-        <v>-5.11654842425593</v>
+        <v>-5.159481948118744</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.135840929031463</v>
+        <v>2.118667519486338</v>
       </c>
       <c r="F2074" t="n">
-        <v>0.5901304432562197</v>
+        <v>0.7391534417405771</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.536894989001315</v>
+        <v>4.626308788091929</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.865470038396633</v>
+        <v>3.38281876202934</v>
       </c>
       <c r="C2075" t="n">
-        <v>4.249271719999743</v>
+        <v>4.230218260964604</v>
       </c>
       <c r="D2075" t="n">
-        <v>-5.146359743954807</v>
+        <v>-5.042987635450931</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.190371398104073</v>
+        <v>2.212666782470484</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.5901304432562197</v>
+        <v>0.7391534417405771</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.603349985953475</v>
+        <v>4.67371032600895</v>
       </c>
     </row>
   </sheetData>
